--- a/hspa-test.xlsx
+++ b/hspa-test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jonas.grabbe\tafi_test-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD448A40-33CF-4539-88B4-61D006271E08}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B06402A9-96CB-4472-9210-B5D59DFD9329}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28770" windowHeight="12030" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28770" windowHeight="12030" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Amud" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5811" uniqueCount="641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5839" uniqueCount="665">
   <si>
     <t>Amud I</t>
   </si>
@@ -1687,9 +1687,6 @@
     <t>Brno II</t>
   </si>
   <si>
-    <t>2-0</t>
-  </si>
-  <si>
     <t>Upper Paleolithic</t>
   </si>
   <si>
@@ -1744,9 +1741,6 @@
     <t>El Mirón Cave</t>
   </si>
   <si>
-    <t>4-0</t>
-  </si>
-  <si>
     <t>Level 114</t>
   </si>
   <si>
@@ -1766,9 +1760,6 @@
   </si>
   <si>
     <t>Errtxorta</t>
-  </si>
-  <si>
-    <t>5-0</t>
   </si>
   <si>
     <t>Holocene</t>
@@ -1952,6 +1943,87 @@
   </si>
   <si>
     <t>element</t>
+  </si>
+  <si>
+    <t>3_2</t>
+  </si>
+  <si>
+    <t>3_1</t>
+  </si>
+  <si>
+    <t>3_3</t>
+  </si>
+  <si>
+    <t>3_4</t>
+  </si>
+  <si>
+    <t>4_3</t>
+  </si>
+  <si>
+    <t>1_1</t>
+  </si>
+  <si>
+    <t>1_2</t>
+  </si>
+  <si>
+    <t>1_3</t>
+  </si>
+  <si>
+    <t>2_0</t>
+  </si>
+  <si>
+    <t>4_0</t>
+  </si>
+  <si>
+    <t>5_0</t>
+  </si>
+  <si>
+    <t>6_1</t>
+  </si>
+  <si>
+    <t>6_2</t>
+  </si>
+  <si>
+    <t>6_3</t>
+  </si>
+  <si>
+    <t>6_4</t>
+  </si>
+  <si>
+    <t>6_5</t>
+  </si>
+  <si>
+    <t>6_6</t>
+  </si>
+  <si>
+    <t>6_7</t>
+  </si>
+  <si>
+    <t>7_1</t>
+  </si>
+  <si>
+    <t>7_2</t>
+  </si>
+  <si>
+    <t>7_3</t>
+  </si>
+  <si>
+    <t>8_1</t>
+  </si>
+  <si>
+    <t>8_2</t>
+  </si>
+  <si>
+    <t>9_1</t>
+  </si>
+  <si>
+    <t>9_2</t>
+  </si>
+  <si>
+    <t>10_1</t>
+  </si>
+  <si>
+    <t>10_2</t>
   </si>
 </sst>
 </file>
@@ -2269,7 +2341,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -2281,7 +2353,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
@@ -2295,21 +2367,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="6">
-        <v>46023</v>
-      </c>
-      <c r="C3" s="6">
-        <v>46054</v>
-      </c>
-      <c r="D3" s="6">
-        <v>46082</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
+        <v>643</v>
+      </c>
+      <c r="C3" t="s">
+        <v>644</v>
+      </c>
+      <c r="D3" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -2323,7 +2395,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -2337,7 +2409,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>9</v>
       </c>
@@ -2351,7 +2423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>10</v>
       </c>
@@ -2365,7 +2437,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>12</v>
       </c>
@@ -2379,7 +2451,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>14</v>
       </c>
@@ -2393,7 +2465,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>16</v>
       </c>
@@ -2407,7 +2479,7 @@
         <v>70000</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>17</v>
       </c>
@@ -2421,21 +2493,21 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="9">
-        <v>46085</v>
-      </c>
-      <c r="C12" s="9">
-        <v>46086</v>
-      </c>
-      <c r="D12" s="9">
-        <v>46087</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B12" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>19</v>
       </c>
@@ -2449,7 +2521,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>21</v>
       </c>
@@ -2463,7 +2535,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>23</v>
       </c>
@@ -2477,7 +2549,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>24</v>
       </c>
@@ -2491,7 +2563,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>25</v>
       </c>
@@ -2505,7 +2577,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>27</v>
       </c>
@@ -2519,7 +2591,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>29</v>
       </c>
@@ -2533,7 +2605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>30</v>
       </c>
@@ -2547,7 +2619,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>33</v>
       </c>
@@ -2561,7 +2633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>34</v>
       </c>
@@ -2575,7 +2647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>35</v>
       </c>
@@ -2589,7 +2661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>36</v>
       </c>
@@ -2603,7 +2675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>37</v>
       </c>
@@ -2617,7 +2689,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>41</v>
       </c>
@@ -2631,7 +2703,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>43</v>
       </c>
@@ -2645,7 +2717,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>45</v>
       </c>
@@ -2659,7 +2731,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>47</v>
       </c>
@@ -2673,7 +2745,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>49</v>
       </c>
@@ -2687,7 +2759,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>51</v>
       </c>
@@ -2699,7 +2771,7 @@
       </c>
       <c r="D31" s="1"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>54</v>
       </c>
@@ -2713,7 +2785,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>56</v>
       </c>
@@ -2725,7 +2797,7 @@
       </c>
       <c r="D33" s="1"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>57</v>
       </c>
@@ -2733,7 +2805,7 @@
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
         <v>58</v>
       </c>
@@ -2741,7 +2813,7 @@
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
         <v>59</v>
       </c>
@@ -2749,7 +2821,7 @@
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>60</v>
       </c>
@@ -9834,16 +9906,16 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
@@ -9854,29 +9926,29 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="6">
-        <v>46032</v>
-      </c>
-      <c r="C3" s="6">
-        <v>46063</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B3" s="6" t="s">
+        <v>663</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -9887,7 +9959,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>9</v>
       </c>
@@ -9898,40 +9970,40 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>16</v>
       </c>
@@ -9942,7 +10014,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>17</v>
       </c>
@@ -9953,7 +10025,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>18</v>
       </c>
@@ -9964,7 +10036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>19</v>
       </c>
@@ -9975,7 +10047,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>21</v>
       </c>
@@ -9986,7 +10058,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>23</v>
       </c>
@@ -9997,7 +10069,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>24</v>
       </c>
@@ -10008,29 +10080,29 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>25</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>27</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>29</v>
       </c>
@@ -10041,7 +10113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>30</v>
       </c>
@@ -10052,7 +10124,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>33</v>
       </c>
@@ -10063,7 +10135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>34</v>
       </c>
@@ -10074,7 +10146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>35</v>
       </c>
@@ -10085,7 +10157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>36</v>
       </c>
@@ -10096,7 +10168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>37</v>
       </c>
@@ -10107,7 +10179,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>41</v>
       </c>
@@ -10118,18 +10190,18 @@
         <v>42</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>43</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>45</v>
       </c>
@@ -10140,7 +10212,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>47</v>
       </c>
@@ -10151,57 +10223,57 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>49</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>51</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>54</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>56</v>
       </c>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>57</v>
       </c>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
         <v>58</v>
       </c>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
         <v>59</v>
       </c>
@@ -10210,7 +10282,7 @@
       </c>
       <c r="C36" s="1"/>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>60</v>
       </c>
@@ -16528,7 +16600,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="B1" s="12" t="s">
         <v>551</v>
@@ -16547,7 +16619,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>552</v>
+        <v>646</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -16587,7 +16659,7 @@
         <v>12</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -16595,7 +16667,7 @@
         <v>14</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -16643,7 +16715,7 @@
         <v>23</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
@@ -16659,7 +16731,7 @@
         <v>25</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
@@ -16667,7 +16739,7 @@
         <v>27</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -16747,7 +16819,7 @@
         <v>45</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
@@ -16763,7 +16835,7 @@
         <v>49</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
@@ -16777,7 +16849,7 @@
         <v>54</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
@@ -18066,7 +18138,7 @@
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A246" s="4" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B246" s="1"/>
     </row>
@@ -21685,19 +21757,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="B1" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="C1" s="12" t="s">
         <v>562</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>563</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>564</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -21721,17 +21793,17 @@
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="6">
-        <v>46025</v>
-      </c>
-      <c r="C3" s="6">
-        <v>46056</v>
-      </c>
-      <c r="D3" s="6">
-        <v>46084</v>
-      </c>
-      <c r="E3" s="6">
-        <v>46115</v>
+      <c r="B3" s="6" t="s">
+        <v>639</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>638</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>640</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>641</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -21739,16 +21811,16 @@
         <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -21807,16 +21879,16 @@
         <v>12</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -21824,16 +21896,16 @@
         <v>14</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
@@ -21926,16 +21998,16 @@
         <v>23</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
@@ -21960,16 +22032,16 @@
         <v>25</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
@@ -21977,16 +22049,16 @@
         <v>27</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
@@ -22130,16 +22202,16 @@
         <v>43</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
@@ -22181,16 +22253,16 @@
         <v>49</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
@@ -22207,16 +22279,16 @@
         <v>54</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
@@ -24318,7 +24390,7 @@
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A246" s="4" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -30779,10 +30851,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -30798,7 +30870,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>571</v>
+        <v>647</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -30806,7 +30878,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -30814,7 +30886,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -30838,7 +30910,7 @@
         <v>12</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -30846,7 +30918,7 @@
         <v>14</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -30910,7 +30982,7 @@
         <v>25</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
@@ -30918,7 +30990,7 @@
         <v>27</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -31014,7 +31086,7 @@
         <v>49</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
@@ -31022,7 +31094,7 @@
         <v>51</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
@@ -31030,7 +31102,7 @@
         <v>54</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
@@ -35916,10 +35988,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -35935,7 +36007,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>579</v>
+        <v>648</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -35943,7 +36015,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -35967,7 +36039,7 @@
         <v>10</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -35975,7 +36047,7 @@
         <v>12</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -36047,7 +36119,7 @@
         <v>25</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
@@ -36055,7 +36127,7 @@
         <v>27</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -36071,7 +36143,7 @@
         <v>30</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
@@ -36119,7 +36191,7 @@
         <v>41</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
@@ -36151,7 +36223,7 @@
         <v>49</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
@@ -36159,7 +36231,7 @@
         <v>51</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
@@ -36167,7 +36239,7 @@
         <v>54</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
@@ -41086,28 +41158,28 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="B1" s="12" t="s">
+        <v>583</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>584</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>585</v>
+      </c>
+      <c r="E1" s="12" t="s">
         <v>586</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="F1" s="12" t="s">
         <v>587</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="G1" s="12" t="s">
         <v>588</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="H1" s="12" t="s">
         <v>589</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>590</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>591</v>
-      </c>
-      <c r="H1" s="12" t="s">
-        <v>592</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -41140,26 +41212,26 @@
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="6">
-        <v>46028</v>
-      </c>
-      <c r="C3" s="6">
-        <v>46059</v>
-      </c>
-      <c r="D3" s="6">
-        <v>46087</v>
-      </c>
-      <c r="E3" s="6">
-        <v>46118</v>
-      </c>
-      <c r="F3" s="6">
-        <v>46148</v>
-      </c>
-      <c r="G3" s="6">
-        <v>46179</v>
-      </c>
-      <c r="H3" s="6">
-        <v>46209</v>
+      <c r="B3" s="6" t="s">
+        <v>649</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>650</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>651</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>652</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>653</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>654</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>655</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -41167,25 +41239,25 @@
         <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
@@ -41271,25 +41343,25 @@
         <v>12</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
@@ -41297,25 +41369,25 @@
         <v>14</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -41505,25 +41577,25 @@
         <v>25</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
@@ -41531,25 +41603,25 @@
         <v>27</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
@@ -41586,10 +41658,10 @@
         <v>32</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>31</v>
@@ -41739,25 +41811,25 @@
         <v>41</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
@@ -41817,25 +41889,25 @@
         <v>47</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
@@ -41843,25 +41915,25 @@
         <v>49</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
@@ -41869,13 +41941,13 @@
         <v>51</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
@@ -41887,25 +41959,25 @@
         <v>54</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
@@ -52750,16 +52822,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -52780,14 +52852,14 @@
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="6">
-        <v>46029</v>
-      </c>
-      <c r="C3" s="6">
-        <v>46060</v>
-      </c>
-      <c r="D3" s="6">
-        <v>46088</v>
+      <c r="B3" s="6" t="s">
+        <v>656</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>657</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>658</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -52795,13 +52867,13 @@
         <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -52809,13 +52881,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -52837,13 +52909,13 @@
         <v>10</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -52851,13 +52923,13 @@
         <v>12</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -52865,13 +52937,13 @@
         <v>14</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -52949,13 +53021,13 @@
         <v>23</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
@@ -52963,13 +53035,13 @@
         <v>24</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
@@ -52977,13 +53049,13 @@
         <v>25</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
@@ -52991,13 +53063,13 @@
         <v>27</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -53022,7 +53094,7 @@
         <v>31</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>32</v>
@@ -53103,13 +53175,13 @@
         <v>41</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
@@ -53159,13 +53231,13 @@
         <v>49</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
@@ -53173,13 +53245,13 @@
         <v>51</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
@@ -53187,13 +53259,13 @@
         <v>54</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
@@ -60111,13 +60183,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -60135,11 +60207,11 @@
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="6">
-        <v>46030</v>
-      </c>
-      <c r="C3" s="6">
-        <v>46061</v>
+      <c r="B3" s="6" t="s">
+        <v>659</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>660</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -60147,10 +60219,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -60158,10 +60230,10 @@
         <v>7</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -60202,10 +60274,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -60234,11 +60306,11 @@
       <c r="A12" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="9">
-        <v>46085</v>
-      </c>
-      <c r="C12" s="9">
-        <v>46086</v>
+      <c r="B12" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>642</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -60290,10 +60362,10 @@
         <v>25</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -60301,10 +60373,10 @@
         <v>27</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -60326,7 +60398,7 @@
         <v>31</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -60445,7 +60517,7 @@
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="4" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -60453,10 +60525,10 @@
         <v>54</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -66483,13 +66555,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -66507,11 +66579,11 @@
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="6">
-        <v>46031</v>
-      </c>
-      <c r="C3" s="6">
-        <v>46062</v>
+      <c r="B3" s="6" t="s">
+        <v>661</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>662</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -66519,10 +66591,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -66530,10 +66602,10 @@
         <v>7</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -66563,10 +66635,10 @@
         <v>12</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -66629,10 +66701,10 @@
         <v>21</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -66662,10 +66734,10 @@
         <v>25</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -66673,10 +66745,10 @@
         <v>27</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -66761,10 +66833,10 @@
         <v>41</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -66817,7 +66889,7 @@
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="4" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -66825,7 +66897,7 @@
         <v>54</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="C32" s="1"/>
     </row>

--- a/hspa-test.xlsx
+++ b/hspa-test.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jonas.grabbe\tafi_test-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B06402A9-96CB-4472-9210-B5D59DFD9329}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C5E7C10-9398-436B-98D4-C0963D352B35}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28770" windowHeight="12030" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28770" windowHeight="12030" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Amud" sheetId="1" r:id="rId1"/>
     <sheet name="Brno II" sheetId="2" r:id="rId2"/>
     <sheet name="Dolni" sheetId="3" r:id="rId3"/>
-    <sheet name="Miron cave" sheetId="4" r:id="rId4"/>
+    <sheet name="El Miron" sheetId="4" r:id="rId4"/>
     <sheet name="Errtxorta" sheetId="5" r:id="rId5"/>
     <sheet name="G Cave" sheetId="6" r:id="rId6"/>
     <sheet name="Herx D" sheetId="7" r:id="rId7"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5839" uniqueCount="665">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5839" uniqueCount="698">
   <si>
     <t>Amud I</t>
   </si>
@@ -1738,25 +1738,10 @@
     <t>1) NSB: Data 2) Trinkaus, E., &amp; Svoboda, J. (Eds.). (2006). Early Modern Human Evolution in Central Europe: The People of Dolní Věstonice and Pavlov. Oxford University Press. 3) Formicola, V., Pontrandolfi, A., &amp; Svoboda, J. (2001). The Upper Paleolithic triple burial of Dolní Vestonice: pathology and funerary behavior. American Journal of Physical Anthropology, 115(4), 372-374. Mittnik, A., Wang, C. C., Svoboda, J., &amp; Krause, J. (2016). A molecular approach to the sexing of the triple burial at the Upper Paleolithic site of Dolní Věstonice. PloS one, 11(10), e0163019.</t>
   </si>
   <si>
-    <t>El Mirón Cave</t>
-  </si>
-  <si>
-    <t>Level 114</t>
-  </si>
-  <si>
-    <t>Lower Magdalenian</t>
-  </si>
-  <si>
     <t>West Europe</t>
   </si>
   <si>
     <t>Spain</t>
-  </si>
-  <si>
-    <t>Ribs: 5 definite, 2 uncertain</t>
-  </si>
-  <si>
-    <t>Smith, J., Doe, A., &amp; Lee, B. (2020). Title of the paper. *Journal Name*, 15(3), 123–145. https://doi.org/10.xxxx</t>
   </si>
   <si>
     <t>Errtxorta</t>
@@ -1972,9 +1957,6 @@
     <t>2_0</t>
   </si>
   <si>
-    <t>4_0</t>
-  </si>
-  <si>
     <t>5_0</t>
   </si>
   <si>
@@ -2025,6 +2007,123 @@
   <si>
     <t>10_2</t>
   </si>
+  <si>
+    <t>El Mirador MIR4</t>
+  </si>
+  <si>
+    <t>El Mirador</t>
+  </si>
+  <si>
+    <t>MIR4</t>
+  </si>
+  <si>
+    <t>geological_period</t>
+  </si>
+  <si>
+    <t>cultural_period</t>
+  </si>
+  <si>
+    <t>culture_period_2</t>
+  </si>
+  <si>
+    <t>start_date_cal_bp</t>
+  </si>
+  <si>
+    <t>end_date_cal_bp</t>
+  </si>
+  <si>
+    <t>mis_stage</t>
+  </si>
+  <si>
+    <t>karstic_system</t>
+  </si>
+  <si>
+    <t>karstic_system_2</t>
+  </si>
+  <si>
+    <t>open_air_site</t>
+  </si>
+  <si>
+    <t>open_air_site_2</t>
+  </si>
+  <si>
+    <t>n_infant</t>
+  </si>
+  <si>
+    <t>n_juvenil</t>
+  </si>
+  <si>
+    <t>taphonomic_context</t>
+  </si>
+  <si>
+    <t>funerary_context</t>
+  </si>
+  <si>
+    <t>discovery_context</t>
+  </si>
+  <si>
+    <t>degree_of_excavation</t>
+  </si>
+  <si>
+    <t>Cáceres, I., Lozano, M., &amp; Saladié, P. (2007). Evidence for bronze age cannibalism in El Mirador cave (Sierra de Atapuerca, Burgos, Spain). American Journal of Physical Anthropology: The Official Publication of the American Association of Physical Anthropologists, 133(3), 899-917.</t>
+  </si>
+  <si>
+    <t>ribs_right</t>
+  </si>
+  <si>
+    <t>ribs_left</t>
+  </si>
+  <si>
+    <t>rib_1_indet</t>
+  </si>
+  <si>
+    <t>rib_2_indet</t>
+  </si>
+  <si>
+    <t>rib_3_indet</t>
+  </si>
+  <si>
+    <t>rib_4_indet</t>
+  </si>
+  <si>
+    <t>rib_5_indet</t>
+  </si>
+  <si>
+    <t>rib_6_indet</t>
+  </si>
+  <si>
+    <t>rib_7_indet</t>
+  </si>
+  <si>
+    <t>rib_8_indet</t>
+  </si>
+  <si>
+    <t>rib_9_indet</t>
+  </si>
+  <si>
+    <t>rib_10_indet</t>
+  </si>
+  <si>
+    <t>rib_11_indet</t>
+  </si>
+  <si>
+    <t>rib_12_indet</t>
+  </si>
+  <si>
+    <t>hand_phalanx_proximal</t>
+  </si>
+  <si>
+    <t>hand_phalanx_middle</t>
+  </si>
+  <si>
+    <t>foot_phalanx_proximal</t>
+  </si>
+  <si>
+    <t>foot_phalanx_middle</t>
+  </si>
+  <si>
+    <t>4_0</t>
+  </si>
 </sst>
 </file>
 
@@ -2034,7 +2133,7 @@
     <numFmt numFmtId="164" formatCode="d\-m"/>
     <numFmt numFmtId="165" formatCode="d/m"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2063,6 +2162,26 @@
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -2078,7 +2197,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -2086,11 +2205,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -2111,8 +2245,23 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2341,7 +2490,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -2372,13 +2521,13 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="C3" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="D3" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2498,13 +2647,13 @@
         <v>18</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -9906,13 +10055,13 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
@@ -9931,10 +10080,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
@@ -9942,10 +10091,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
@@ -9975,10 +10124,10 @@
         <v>10</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
@@ -9986,10 +10135,10 @@
         <v>12</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
@@ -9997,10 +10146,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
@@ -10085,10 +10234,10 @@
         <v>25</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
@@ -10096,10 +10245,10 @@
         <v>27</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
@@ -10195,10 +10344,10 @@
         <v>43</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
@@ -10246,10 +10395,10 @@
         <v>54</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
@@ -16600,7 +16749,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="B1" s="12" t="s">
         <v>551</v>
@@ -16619,7 +16768,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -21757,7 +21906,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="B1" s="12" t="s">
         <v>561</v>
@@ -21794,16 +21943,16 @@
         <v>4</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -30848,5133 +30997,5187 @@
   </sheetPr>
   <dimension ref="A1:B1002"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="2" width="12.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>637</v>
-      </c>
-      <c r="B1" s="12" t="s">
+    <row r="1" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
+        <v>632</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="16" t="s">
+        <v>662</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="16" t="s">
+        <v>663</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="16" t="s">
+        <v>664</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="16" t="s">
+        <v>665</v>
+      </c>
+      <c r="B10" s="18">
+        <v>4400</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="16" t="s">
+        <v>666</v>
+      </c>
+      <c r="B11" s="18">
+        <v>4100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
+        <v>667</v>
+      </c>
+      <c r="B12" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="16" t="s">
+        <v>668</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="16" t="s">
+        <v>669</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="16" t="s">
+        <v>670</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="16" t="s">
+        <v>671</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="16" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+    <row r="18" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="18">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="16" t="s">
+        <v>672</v>
+      </c>
+      <c r="B21" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="16" t="s">
+        <v>673</v>
+      </c>
+      <c r="B22" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" s="18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="18">
         <v>3</v>
       </c>
-      <c r="B2" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
+    </row>
+    <row r="25" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="16" t="s">
+        <v>674</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="16" t="s">
+        <v>675</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="16" t="s">
+        <v>676</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="16" t="s">
+        <v>677</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B31" s="14"/>
+    </row>
+    <row r="32" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="B33" s="18">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B34" s="14"/>
+    </row>
+    <row r="35" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B35" s="14"/>
+    </row>
+    <row r="36" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B36" s="14"/>
+    </row>
+    <row r="37" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B37" s="14"/>
+    </row>
+    <row r="38" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B38" s="14"/>
+    </row>
+    <row r="39" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="B39" s="14"/>
+    </row>
+    <row r="40" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B40" s="14"/>
+    </row>
+    <row r="41" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="B41" s="14"/>
+    </row>
+    <row r="42" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="B42" s="14"/>
+    </row>
+    <row r="43" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="B43" s="14"/>
+    </row>
+    <row r="44" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B44" s="14"/>
+    </row>
+    <row r="45" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="B45" s="14"/>
+    </row>
+    <row r="46" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="B46" s="14"/>
+    </row>
+    <row r="47" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="B47" s="14"/>
+    </row>
+    <row r="48" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B48" s="14"/>
+    </row>
+    <row r="49" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="B49" s="14"/>
+    </row>
+    <row r="50" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="B50" s="18">
         <v>5</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="8">
-        <v>19000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="8">
-        <v>19000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="8">
+    </row>
+    <row r="51" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="B51" s="14"/>
+    </row>
+    <row r="52" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="B52" s="14"/>
+    </row>
+    <row r="53" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="B53" s="14"/>
+    </row>
+    <row r="54" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="B54" s="14"/>
+    </row>
+    <row r="55" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="B55" s="14"/>
+    </row>
+    <row r="56" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="B56" s="14"/>
+    </row>
+    <row r="57" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="B57" s="14"/>
+    </row>
+    <row r="58" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="B58" s="14"/>
+    </row>
+    <row r="59" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="B59" s="14"/>
+    </row>
+    <row r="60" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="B60" s="14"/>
+    </row>
+    <row r="61" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="B61" s="14"/>
+    </row>
+    <row r="62" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="B62" s="14"/>
+    </row>
+    <row r="63" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="B63" s="14"/>
+    </row>
+    <row r="64" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="B64" s="14"/>
+    </row>
+    <row r="65" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="B65" s="14"/>
+    </row>
+    <row r="66" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B66" s="14"/>
+    </row>
+    <row r="67" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="B67" s="14"/>
+    </row>
+    <row r="68" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="B68" s="14"/>
+    </row>
+    <row r="69" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="B69" s="14"/>
+    </row>
+    <row r="70" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="B70" s="14"/>
+    </row>
+    <row r="71" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="B71" s="14"/>
+    </row>
+    <row r="72" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="B72" s="14"/>
+    </row>
+    <row r="73" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="B73" s="14"/>
+    </row>
+    <row r="74" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="B74" s="18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="B75" s="14"/>
+    </row>
+    <row r="76" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="B76" s="14"/>
+    </row>
+    <row r="77" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="B77" s="14"/>
+    </row>
+    <row r="78" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="B78" s="14"/>
+    </row>
+    <row r="79" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="B79" s="14"/>
+    </row>
+    <row r="80" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="B80" s="14"/>
+    </row>
+    <row r="81" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="B81" s="14"/>
+    </row>
+    <row r="82" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="B82" s="14"/>
+    </row>
+    <row r="83" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="B83" s="14"/>
+    </row>
+    <row r="84" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="B84" s="14"/>
+    </row>
+    <row r="85" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="B85" s="14"/>
+    </row>
+    <row r="86" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="B86" s="14"/>
+    </row>
+    <row r="87" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="B87" s="14"/>
+    </row>
+    <row r="88" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="B88" s="14"/>
+    </row>
+    <row r="89" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="B89" s="14"/>
+    </row>
+    <row r="90" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="B90" s="14"/>
+    </row>
+    <row r="91" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="B91" s="14"/>
+    </row>
+    <row r="92" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="B92" s="14"/>
+    </row>
+    <row r="93" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="B93" s="14"/>
+    </row>
+    <row r="94" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="B94" s="14"/>
+    </row>
+    <row r="95" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="B95" s="14"/>
+    </row>
+    <row r="96" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="B96" s="14"/>
+    </row>
+    <row r="97" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="B97" s="14"/>
+    </row>
+    <row r="98" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="B98" s="14"/>
+    </row>
+    <row r="99" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="B99" s="14"/>
+    </row>
+    <row r="100" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="B100" s="14"/>
+    </row>
+    <row r="101" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="B101" s="14"/>
+    </row>
+    <row r="102" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="B102" s="14"/>
+    </row>
+    <row r="103" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="B103" s="14"/>
+    </row>
+    <row r="104" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="B104" s="14"/>
+    </row>
+    <row r="105" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="B105" s="14"/>
+    </row>
+    <row r="106" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="B106" s="14"/>
+    </row>
+    <row r="107" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="B107" s="14"/>
+    </row>
+    <row r="108" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="B108" s="14"/>
+    </row>
+    <row r="109" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="B109" s="14"/>
+    </row>
+    <row r="110" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="B110" s="14"/>
+    </row>
+    <row r="111" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="B111" s="14"/>
+    </row>
+    <row r="112" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="B112" s="14"/>
+    </row>
+    <row r="113" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="B113" s="14"/>
+    </row>
+    <row r="114" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="B114" s="14"/>
+    </row>
+    <row r="115" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="B115" s="14"/>
+    </row>
+    <row r="116" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="B116" s="14"/>
+    </row>
+    <row r="117" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="B117" s="14"/>
+    </row>
+    <row r="118" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="B118" s="14"/>
+    </row>
+    <row r="119" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="B119" s="14"/>
+    </row>
+    <row r="120" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="B120" s="14"/>
+    </row>
+    <row r="121" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="B121" s="14"/>
+    </row>
+    <row r="122" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="B122" s="14"/>
+    </row>
+    <row r="123" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="B123" s="14"/>
+    </row>
+    <row r="124" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="B124" s="14"/>
+    </row>
+    <row r="125" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="B125" s="14"/>
+    </row>
+    <row r="126" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="B126" s="14"/>
+    </row>
+    <row r="127" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="B127" s="14"/>
+    </row>
+    <row r="128" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="B128" s="14"/>
+    </row>
+    <row r="129" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="B129" s="14"/>
+    </row>
+    <row r="130" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="B130" s="14"/>
+    </row>
+    <row r="131" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="B131" s="14"/>
+    </row>
+    <row r="132" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="B132" s="14"/>
+    </row>
+    <row r="133" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="B133" s="14"/>
+    </row>
+    <row r="134" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="B134" s="14"/>
+    </row>
+    <row r="135" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A135" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="B135" s="14"/>
+    </row>
+    <row r="136" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="B136" s="14"/>
+    </row>
+    <row r="137" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A137" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="B137" s="14"/>
+    </row>
+    <row r="138" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="B138" s="14"/>
+    </row>
+    <row r="139" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="B139" s="14"/>
+    </row>
+    <row r="140" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="B140" s="14"/>
+    </row>
+    <row r="141" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="B141" s="14"/>
+    </row>
+    <row r="142" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A142" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="B142" s="14"/>
+    </row>
+    <row r="143" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="B143" s="14"/>
+    </row>
+    <row r="144" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="B144" s="14"/>
+    </row>
+    <row r="145" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="B145" s="14"/>
+    </row>
+    <row r="146" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="B146" s="14"/>
+    </row>
+    <row r="147" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="B147" s="14"/>
+    </row>
+    <row r="148" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="B148" s="14"/>
+    </row>
+    <row r="149" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="B149" s="14"/>
+    </row>
+    <row r="150" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="B150" s="14"/>
+    </row>
+    <row r="151" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="B151" s="14"/>
+    </row>
+    <row r="152" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="B152" s="14"/>
+    </row>
+    <row r="153" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="B153" s="14"/>
+    </row>
+    <row r="154" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="B154" s="14"/>
+    </row>
+    <row r="155" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A155" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="B155" s="14"/>
+    </row>
+    <row r="156" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="B156" s="14"/>
+    </row>
+    <row r="157" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="B157" s="14"/>
+    </row>
+    <row r="158" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A158" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="B158" s="14"/>
+    </row>
+    <row r="159" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A159" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="B159" s="14"/>
+    </row>
+    <row r="160" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B160" s="14"/>
+    </row>
+    <row r="161" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="B161" s="14"/>
+    </row>
+    <row r="162" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="B162" s="14"/>
+    </row>
+    <row r="163" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A163" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="B163" s="14"/>
+    </row>
+    <row r="164" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A164" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="B164" s="14"/>
+    </row>
+    <row r="165" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="B165" s="14"/>
+    </row>
+    <row r="166" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="B166" s="14"/>
+    </row>
+    <row r="167" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A167" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="B167" s="14"/>
+    </row>
+    <row r="168" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A168" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="B168" s="14"/>
+    </row>
+    <row r="169" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A169" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="B169" s="14"/>
+    </row>
+    <row r="170" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A170" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="B170" s="14"/>
+    </row>
+    <row r="171" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A171" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="B171" s="14"/>
+    </row>
+    <row r="172" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A172" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="B172" s="14"/>
+    </row>
+    <row r="173" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A173" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="B173" s="14"/>
+    </row>
+    <row r="174" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A174" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="B174" s="14"/>
+    </row>
+    <row r="175" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A175" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="B175" s="14"/>
+    </row>
+    <row r="176" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A176" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="B176" s="14"/>
+    </row>
+    <row r="177" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A177" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="B177" s="14"/>
+    </row>
+    <row r="178" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A178" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="B178" s="14"/>
+    </row>
+    <row r="179" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A179" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="B179" s="14"/>
+    </row>
+    <row r="180" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A180" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="B180" s="14"/>
+    </row>
+    <row r="181" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A181" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="B181" s="14"/>
+    </row>
+    <row r="182" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A182" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="B182" s="14"/>
+    </row>
+    <row r="183" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A183" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="B183" s="14"/>
+    </row>
+    <row r="184" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A184" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="B184" s="14"/>
+    </row>
+    <row r="185" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A185" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="B185" s="14"/>
+    </row>
+    <row r="186" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A186" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="B186" s="14"/>
+    </row>
+    <row r="187" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A187" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="B187" s="14"/>
+    </row>
+    <row r="188" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A188" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="B188" s="14"/>
+    </row>
+    <row r="189" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A189" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="B189" s="14"/>
+    </row>
+    <row r="190" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A190" s="16" t="s">
+        <v>215</v>
+      </c>
+      <c r="B190" s="14"/>
+    </row>
+    <row r="191" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A191" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="B191" s="14"/>
+    </row>
+    <row r="192" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A192" s="16" t="s">
+        <v>217</v>
+      </c>
+      <c r="B192" s="14"/>
+    </row>
+    <row r="193" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A193" s="16" t="s">
+        <v>218</v>
+      </c>
+      <c r="B193" s="14"/>
+    </row>
+    <row r="194" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A194" s="16" t="s">
+        <v>219</v>
+      </c>
+      <c r="B194" s="14"/>
+    </row>
+    <row r="195" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A195" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="B195" s="14"/>
+    </row>
+    <row r="196" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A196" s="16" t="s">
+        <v>221</v>
+      </c>
+      <c r="B196" s="14"/>
+    </row>
+    <row r="197" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A197" s="16" t="s">
+        <v>222</v>
+      </c>
+      <c r="B197" s="14"/>
+    </row>
+    <row r="198" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A198" s="16" t="s">
+        <v>223</v>
+      </c>
+      <c r="B198" s="14"/>
+    </row>
+    <row r="199" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A199" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="B199" s="14"/>
+    </row>
+    <row r="200" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A200" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="B200" s="14"/>
+    </row>
+    <row r="201" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A201" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="B201" s="14"/>
+    </row>
+    <row r="202" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A202" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="B202" s="14"/>
+    </row>
+    <row r="203" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A203" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="B203" s="14"/>
+    </row>
+    <row r="204" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A204" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="B204" s="14"/>
+    </row>
+    <row r="205" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A205" s="16" t="s">
+        <v>230</v>
+      </c>
+      <c r="B205" s="14"/>
+    </row>
+    <row r="206" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A206" s="16" t="s">
+        <v>231</v>
+      </c>
+      <c r="B206" s="14"/>
+    </row>
+    <row r="207" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A207" s="16" t="s">
+        <v>232</v>
+      </c>
+      <c r="B207" s="14"/>
+    </row>
+    <row r="208" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A208" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="B208" s="14"/>
+    </row>
+    <row r="209" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A209" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="B209" s="14"/>
+    </row>
+    <row r="210" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A210" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="B210" s="14"/>
+    </row>
+    <row r="211" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A211" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="B211" s="14"/>
+    </row>
+    <row r="212" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A212" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="B212" s="14"/>
+    </row>
+    <row r="213" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A213" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="B213" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A214" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="B214" s="14"/>
+    </row>
+    <row r="215" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A215" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="B215" s="14"/>
+    </row>
+    <row r="216" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A216" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="B216" s="14"/>
+    </row>
+    <row r="217" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A217" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="B217" s="14"/>
+    </row>
+    <row r="218" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A218" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="B218" s="14"/>
+    </row>
+    <row r="219" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A219" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="B219" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A220" s="16" t="s">
+        <v>245</v>
+      </c>
+      <c r="B220" s="14"/>
+    </row>
+    <row r="221" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A221" s="16" t="s">
+        <v>246</v>
+      </c>
+      <c r="B221" s="18">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A222" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="B222" s="14"/>
+    </row>
+    <row r="223" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A223" s="16" t="s">
+        <v>248</v>
+      </c>
+      <c r="B223" s="14"/>
+    </row>
+    <row r="224" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A224" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="B224" s="14"/>
+    </row>
+    <row r="225" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A225" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="B225" s="14"/>
+    </row>
+    <row r="226" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A226" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="B226" s="14"/>
+    </row>
+    <row r="227" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A227" s="16" t="s">
+        <v>252</v>
+      </c>
+      <c r="B227" s="14"/>
+    </row>
+    <row r="228" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A228" s="16" t="s">
+        <v>253</v>
+      </c>
+      <c r="B228" s="14"/>
+    </row>
+    <row r="229" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A229" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="B229" s="14"/>
+    </row>
+    <row r="230" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A230" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="B230" s="14"/>
+    </row>
+    <row r="231" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A231" s="16" t="s">
+        <v>256</v>
+      </c>
+      <c r="B231" s="14"/>
+    </row>
+    <row r="232" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A232" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="B232" s="14"/>
+    </row>
+    <row r="233" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A233" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="B233" s="14"/>
+    </row>
+    <row r="234" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A234" s="16" t="s">
+        <v>259</v>
+      </c>
+      <c r="B234" s="14"/>
+    </row>
+    <row r="235" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A235" s="16" t="s">
+        <v>260</v>
+      </c>
+      <c r="B235" s="18">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B21" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B22" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B23" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B24" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A30" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A31" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A32" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A33" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B33" s="1"/>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A34" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B34" s="1"/>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B35" s="1"/>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A36" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B36" s="1"/>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A37" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B37" s="1"/>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A38" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B38" s="1"/>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A39" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B39" s="1"/>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A40" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B40" s="1"/>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A41" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B41" s="1"/>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A42" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B42" s="1"/>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A43" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B43" s="1"/>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A44" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B44" s="1"/>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A45" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="B45" s="1"/>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A46" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B46" s="1"/>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A47" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B47" s="1"/>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A48" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B48" s="1"/>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A49" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="B49" s="1"/>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A50" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B50" s="1"/>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A51" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B51" s="1"/>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A52" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B52" s="1"/>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A53" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="B53" s="1"/>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A54" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B54" s="1"/>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A55" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B55" s="1"/>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A56" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B56" s="1"/>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A57" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B57" s="1"/>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A58" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B58" s="1"/>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A59" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="B59" s="1"/>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A60" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B60" s="1"/>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A61" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="B61" s="1"/>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A62" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B62" s="1"/>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A63" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B63" s="1"/>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A64" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B64" s="1"/>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A65" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B65" s="1"/>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A66" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B66" s="1"/>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A67" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B67" s="1"/>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A68" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B68" s="1"/>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A69" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B69" s="1"/>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A70" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B70" s="1"/>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A71" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B71" s="1"/>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A72" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B72" s="1"/>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A73" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B73" s="1"/>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A74" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B74" s="1"/>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A75" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B75" s="1"/>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A76" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="B76" s="1"/>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A77" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B77" s="1"/>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A78" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B78" s="1"/>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A79" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B79" s="1"/>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A80" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B80" s="1"/>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A81" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B81" s="1"/>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A82" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="B82" s="1"/>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A83" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="B83" s="1"/>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A84" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="B84" s="1"/>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A85" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="B85" s="1"/>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A86" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B86" s="1"/>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A87" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B87" s="1"/>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A88" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B88" s="1"/>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A89" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B89" s="1"/>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A90" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="B90" s="1"/>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A91" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B91" s="1"/>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A92" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B92" s="1"/>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A93" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B93" s="1"/>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A94" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B94" s="1"/>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A95" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B95" s="1"/>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A96" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="B96" s="1"/>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A97" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="B97" s="1"/>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A98" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="B98" s="1"/>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A99" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B99" s="1"/>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A100" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B100" s="1"/>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A101" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B101" s="1"/>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A102" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B102" s="1"/>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A103" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B103" s="1"/>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A104" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B104" s="1"/>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A105" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="B105" s="1"/>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A106" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="B106" s="1"/>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A107" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="B107" s="1"/>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A108" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="B108" s="1"/>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A109" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="B109" s="1"/>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A110" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B110" s="1"/>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A111" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="B111" s="1"/>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A112" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="B112" s="1"/>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A113" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="B113" s="1"/>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A114" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="B114" s="1"/>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A115" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="B115" s="1"/>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A116" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="B116" s="1"/>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A117" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="B117" s="1"/>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A118" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="B118" s="1"/>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A119" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="B119" s="1"/>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A120" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="B120" s="1"/>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A121" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="B121" s="1"/>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A122" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="B122" s="1"/>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A123" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="B123" s="1"/>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A124" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="B124" s="1"/>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A125" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="B125" s="1"/>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A126" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="B126" s="1"/>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A127" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="B127" s="1"/>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A128" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="B128" s="1"/>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A129" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="B129" s="1"/>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A130" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="B130" s="1"/>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A131" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="B131" s="1"/>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A132" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="B132" s="1"/>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A133" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="B133" s="1"/>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A134" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="B134" s="1"/>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A135" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="B135" s="1"/>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A136" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="B136" s="1"/>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A137" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="B137" s="1"/>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A138" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="B138" s="1"/>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A139" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="B139" s="1"/>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A140" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="B140" s="1"/>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A141" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="B141" s="1"/>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A142" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="B142" s="1"/>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A143" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B143" s="1"/>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A144" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="B144" s="1"/>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A145" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="B145" s="1"/>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A146" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="B146" s="1"/>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A147" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="B147" s="1"/>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A148" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="B148" s="1"/>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A149" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B149" s="1"/>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A150" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="B150" s="1"/>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A151" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="B151" s="1"/>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A152" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="B152" s="1"/>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A153" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="B153" s="1"/>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A154" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="B154" s="1"/>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A155" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="B155" s="1"/>
-    </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A156" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="B156" s="1"/>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A157" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="B157" s="1"/>
-    </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A158" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="B158" s="1"/>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A159" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="B159" s="1"/>
-    </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A160" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="B160" s="1"/>
-    </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A161" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="B161" s="1"/>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A162" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="B162" s="1"/>
-    </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A163" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="B163" s="1"/>
-    </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A164" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="B164" s="1"/>
-    </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A165" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="B165" s="1"/>
-    </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A166" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="B166" s="1"/>
-    </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A167" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="B167" s="1"/>
-    </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A168" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="B168" s="1"/>
-    </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A169" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="B169" s="1"/>
-    </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A170" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="B170" s="1"/>
-    </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A171" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="B171" s="1"/>
-    </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A172" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="B172" s="1"/>
-    </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A173" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="B173" s="1"/>
-    </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A174" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="B174" s="1"/>
-    </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A175" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="B175" s="1"/>
-    </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A176" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="B176" s="1"/>
-    </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A177" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="B177" s="1"/>
-    </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A178" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="B178" s="1"/>
-    </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A179" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="B179" s="1"/>
-    </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A180" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="B180" s="1"/>
-    </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A181" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="B181" s="1"/>
-    </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A182" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="B182" s="1"/>
-    </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A183" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="B183" s="1"/>
-    </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A184" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="B184" s="1"/>
-    </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A185" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="B185" s="1"/>
-    </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A186" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="B186" s="1"/>
-    </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A187" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="B187" s="1"/>
-    </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A188" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="B188" s="1"/>
-    </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A189" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="B189" s="1"/>
-    </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A190" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="B190" s="1"/>
-    </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A191" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="B191" s="1"/>
-    </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A192" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="B192" s="1"/>
-    </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A193" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="B193" s="1"/>
-    </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A194" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="B194" s="1"/>
-    </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A195" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="B195" s="1"/>
-    </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A196" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="B196" s="1"/>
-    </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A197" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="B197" s="1"/>
-    </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A198" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="B198" s="1"/>
-    </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A199" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="B199" s="1"/>
-    </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A200" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="B200" s="1"/>
-    </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A201" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="B201" s="1"/>
-    </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A202" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="B202" s="1"/>
-    </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A203" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="B203" s="1"/>
-    </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A204" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="B204" s="1"/>
-    </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A205" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="B205" s="1"/>
-    </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A206" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="B206" s="1"/>
-    </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A207" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="B207" s="1"/>
-    </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A208" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="B208" s="1"/>
-    </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A209" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="B209" s="1"/>
-    </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A210" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="B210" s="1"/>
-    </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A211" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="B211" s="1"/>
-    </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A212" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="B212" s="1"/>
-    </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A213" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B213" s="1"/>
-    </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A214" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="B214" s="1"/>
-    </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A215" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="B215" s="1"/>
-    </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A216" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="B216" s="1"/>
-    </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A217" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="B217" s="1"/>
-    </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A218" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="B218" s="1"/>
-    </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A219" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="B219" s="1"/>
-    </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A220" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="B220" s="1"/>
-    </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A221" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="B221" s="1"/>
-    </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A222" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="B222" s="1"/>
-    </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A223" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="B223" s="1"/>
-    </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A224" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="B224" s="1"/>
-    </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A225" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="B225" s="1"/>
-    </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A226" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="B226" s="1"/>
-    </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A227" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="B227" s="1"/>
-    </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A228" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="B228" s="1"/>
-    </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A229" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="B229" s="1"/>
-    </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A230" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="B230" s="1"/>
-    </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A231" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="B231" s="1"/>
-    </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A232" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="B232" s="1"/>
-    </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A233" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="B233" s="1"/>
-    </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A234" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="B234" s="1"/>
-    </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A235" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="B235" s="1"/>
-    </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A236" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="B236" s="1"/>
-    </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A237" s="4" t="s">
+    <row r="236" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A236" s="16" t="s">
         <v>261</v>
       </c>
-      <c r="B237" s="1"/>
-    </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A238" s="4" t="s">
+      <c r="B236" s="14"/>
+    </row>
+    <row r="237" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A237" s="16" t="s">
         <v>262</v>
       </c>
-      <c r="B238" s="1"/>
-    </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A239" s="4" t="s">
+      <c r="B237" s="14"/>
+    </row>
+    <row r="238" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A238" s="16" t="s">
         <v>263</v>
       </c>
-      <c r="B239" s="1"/>
-    </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A240" s="4" t="s">
+      <c r="B238" s="14"/>
+    </row>
+    <row r="239" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A239" s="16" t="s">
         <v>264</v>
       </c>
-      <c r="B240" s="1"/>
-    </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A241" s="4" t="s">
+      <c r="B239" s="14"/>
+    </row>
+    <row r="240" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A240" s="16" t="s">
         <v>265</v>
       </c>
-      <c r="B241" s="1"/>
-    </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A242" s="4" t="s">
+      <c r="B240" s="14"/>
+    </row>
+    <row r="241" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A241" s="16" t="s">
         <v>266</v>
       </c>
-      <c r="B242" s="1"/>
-    </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A243" s="4" t="s">
+      <c r="B241" s="14"/>
+    </row>
+    <row r="242" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A242" s="16" t="s">
         <v>267</v>
       </c>
-      <c r="B243" s="1"/>
-    </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A244" s="4" t="s">
+      <c r="B242" s="14"/>
+    </row>
+    <row r="243" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A243" s="16" t="s">
         <v>268</v>
       </c>
-      <c r="B244" s="1"/>
-    </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A245" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="B245" s="1"/>
-    </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A246" s="4" t="s">
+      <c r="B243" s="14"/>
+    </row>
+    <row r="244" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A244" s="16" t="s">
+        <v>560</v>
+      </c>
+      <c r="B244" s="14"/>
+    </row>
+    <row r="245" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A245" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="B245" s="18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A246" s="16" t="s">
         <v>270</v>
       </c>
-      <c r="B246" s="1"/>
-    </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A247" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="B247" s="1"/>
-    </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A248" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="B248" s="1"/>
-    </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A249" s="4" t="s">
+      <c r="B246" s="14"/>
+    </row>
+    <row r="247" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A247" s="16" t="s">
+        <v>679</v>
+      </c>
+      <c r="B247" s="14"/>
+    </row>
+    <row r="248" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A248" s="16" t="s">
+        <v>680</v>
+      </c>
+      <c r="B248" s="14"/>
+    </row>
+    <row r="249" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A249" s="16" t="s">
+        <v>681</v>
+      </c>
+      <c r="B249" s="14"/>
+    </row>
+    <row r="250" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A250" s="16" t="s">
         <v>273</v>
       </c>
-      <c r="B249" s="1"/>
-    </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A250" s="4" t="s">
+      <c r="B250" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A251" s="16" t="s">
         <v>274</v>
       </c>
-      <c r="B250" s="1"/>
-    </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A251" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="B251" s="1"/>
-    </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A252" s="4" t="s">
+      <c r="B251" s="14"/>
+    </row>
+    <row r="252" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A252" s="16" t="s">
+        <v>682</v>
+      </c>
+      <c r="B252" s="14"/>
+    </row>
+    <row r="253" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A253" s="16" t="s">
         <v>276</v>
       </c>
-      <c r="B252" s="1"/>
-    </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A253" s="4" t="s">
+      <c r="B253" s="14"/>
+    </row>
+    <row r="254" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A254" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="B253" s="1"/>
-    </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A254" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="B254" s="1"/>
-    </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A255" s="4" t="s">
+      <c r="B254" s="14"/>
+    </row>
+    <row r="255" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A255" s="16" t="s">
+        <v>683</v>
+      </c>
+      <c r="B255" s="14"/>
+    </row>
+    <row r="256" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A256" s="16" t="s">
         <v>279</v>
       </c>
-      <c r="B255" s="1"/>
-    </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A256" s="4" t="s">
+      <c r="B256" s="14"/>
+    </row>
+    <row r="257" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A257" s="16" t="s">
         <v>280</v>
       </c>
-      <c r="B256" s="1"/>
-    </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A257" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="B257" s="1"/>
-    </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A258" s="4" t="s">
+      <c r="B257" s="14"/>
+    </row>
+    <row r="258" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A258" s="16" t="s">
+        <v>684</v>
+      </c>
+      <c r="B258" s="14"/>
+    </row>
+    <row r="259" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A259" s="16" t="s">
         <v>282</v>
       </c>
-      <c r="B258" s="1"/>
-    </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A259" s="4" t="s">
+      <c r="B259" s="14"/>
+    </row>
+    <row r="260" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A260" s="16" t="s">
         <v>283</v>
       </c>
-      <c r="B259" s="1"/>
-    </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A260" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="B260" s="1"/>
-    </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A261" s="4" t="s">
+      <c r="B260" s="14"/>
+    </row>
+    <row r="261" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A261" s="16" t="s">
+        <v>685</v>
+      </c>
+      <c r="B261" s="14"/>
+    </row>
+    <row r="262" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A262" s="16" t="s">
         <v>285</v>
       </c>
-      <c r="B261" s="1"/>
-    </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A262" s="4" t="s">
+      <c r="B262" s="14"/>
+    </row>
+    <row r="263" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A263" s="16" t="s">
         <v>286</v>
       </c>
-      <c r="B262" s="1"/>
-    </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A263" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="B263" s="1"/>
-    </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A264" s="4" t="s">
+      <c r="B263" s="14"/>
+    </row>
+    <row r="264" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A264" s="16" t="s">
+        <v>686</v>
+      </c>
+      <c r="B264" s="14"/>
+    </row>
+    <row r="265" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A265" s="16" t="s">
         <v>288</v>
       </c>
-      <c r="B264" s="1"/>
-    </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A265" s="4" t="s">
+      <c r="B265" s="14"/>
+    </row>
+    <row r="266" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A266" s="16" t="s">
         <v>289</v>
       </c>
-      <c r="B265" s="1"/>
-    </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A266" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="B266" s="1"/>
-    </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A267" s="4" t="s">
+      <c r="B266" s="14"/>
+    </row>
+    <row r="267" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A267" s="16" t="s">
+        <v>687</v>
+      </c>
+      <c r="B267" s="14"/>
+    </row>
+    <row r="268" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A268" s="16" t="s">
         <v>291</v>
       </c>
-      <c r="B267" s="1"/>
-    </row>
-    <row r="268" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A268" s="4" t="s">
+      <c r="B268" s="14"/>
+    </row>
+    <row r="269" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A269" s="16" t="s">
         <v>292</v>
       </c>
-      <c r="B268" s="1"/>
-    </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A269" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="B269" s="1"/>
-    </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A270" s="4" t="s">
+      <c r="B269" s="14"/>
+    </row>
+    <row r="270" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A270" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="B270" s="14"/>
+    </row>
+    <row r="271" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A271" s="16" t="s">
         <v>294</v>
       </c>
-      <c r="B270" s="1"/>
-    </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A271" s="4" t="s">
+      <c r="B271" s="14"/>
+    </row>
+    <row r="272" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A272" s="16" t="s">
         <v>295</v>
       </c>
-      <c r="B271" s="1"/>
-    </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A272" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="B272" s="1"/>
-    </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A273" s="4" t="s">
+      <c r="B272" s="14"/>
+    </row>
+    <row r="273" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A273" s="16" t="s">
+        <v>689</v>
+      </c>
+      <c r="B273" s="14"/>
+    </row>
+    <row r="274" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A274" s="16" t="s">
         <v>297</v>
       </c>
-      <c r="B273" s="1"/>
-    </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A274" s="4" t="s">
+      <c r="B274" s="14"/>
+    </row>
+    <row r="275" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A275" s="16" t="s">
         <v>298</v>
       </c>
-      <c r="B274" s="1"/>
-    </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A275" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="B275" s="1"/>
-    </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A276" s="4" t="s">
+      <c r="B275" s="14"/>
+    </row>
+    <row r="276" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A276" s="16" t="s">
+        <v>690</v>
+      </c>
+      <c r="B276" s="14"/>
+    </row>
+    <row r="277" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A277" s="16" t="s">
         <v>300</v>
       </c>
-      <c r="B276" s="1"/>
-    </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A277" s="4" t="s">
+      <c r="B277" s="14"/>
+    </row>
+    <row r="278" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A278" s="16" t="s">
         <v>301</v>
       </c>
-      <c r="B277" s="1"/>
-    </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A278" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="B278" s="1"/>
-    </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A279" s="4" t="s">
+      <c r="B278" s="14"/>
+    </row>
+    <row r="279" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A279" s="16" t="s">
+        <v>691</v>
+      </c>
+      <c r="B279" s="14"/>
+    </row>
+    <row r="280" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A280" s="16" t="s">
         <v>303</v>
       </c>
-      <c r="B279" s="1"/>
-    </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A280" s="4" t="s">
+      <c r="B280" s="14"/>
+    </row>
+    <row r="281" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A281" s="16" t="s">
         <v>304</v>
       </c>
-      <c r="B280" s="1"/>
-    </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A281" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="B281" s="1"/>
-    </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A282" s="4" t="s">
+      <c r="B281" s="14"/>
+    </row>
+    <row r="282" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A282" s="16" t="s">
+        <v>692</v>
+      </c>
+      <c r="B282" s="14"/>
+    </row>
+    <row r="283" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A283" s="16" t="s">
         <v>306</v>
       </c>
-      <c r="B282" s="1"/>
-    </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A283" s="4" t="s">
+      <c r="B283" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A284" s="16" t="s">
         <v>307</v>
       </c>
-      <c r="B283" s="1"/>
-    </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A284" s="4" t="s">
+      <c r="B284" s="14"/>
+    </row>
+    <row r="285" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A285" s="16" t="s">
         <v>308</v>
       </c>
-      <c r="B284" s="1"/>
-    </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A285" s="4" t="s">
+      <c r="B285" s="14"/>
+    </row>
+    <row r="286" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A286" s="16" t="s">
         <v>309</v>
       </c>
-      <c r="B285" s="1"/>
-    </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A286" s="4" t="s">
+      <c r="B286" s="14"/>
+    </row>
+    <row r="287" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A287" s="16" t="s">
         <v>310</v>
       </c>
-      <c r="B286" s="1"/>
-    </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A287" s="4" t="s">
+      <c r="B287" s="14"/>
+    </row>
+    <row r="288" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A288" s="16" t="s">
         <v>311</v>
       </c>
-      <c r="B287" s="1"/>
-    </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A288" s="4" t="s">
+      <c r="B288" s="14"/>
+    </row>
+    <row r="289" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A289" s="16" t="s">
         <v>312</v>
       </c>
-      <c r="B288" s="1"/>
-    </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A289" s="4" t="s">
+      <c r="B289" s="14"/>
+    </row>
+    <row r="290" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A290" s="16" t="s">
         <v>313</v>
       </c>
-      <c r="B289" s="1"/>
-    </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A290" s="4" t="s">
+      <c r="B290" s="14"/>
+    </row>
+    <row r="291" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A291" s="16" t="s">
         <v>314</v>
       </c>
-      <c r="B290" s="1"/>
-    </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A291" s="4" t="s">
+      <c r="B291" s="14"/>
+    </row>
+    <row r="292" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A292" s="16" t="s">
         <v>315</v>
       </c>
-      <c r="B291" s="1"/>
-    </row>
-    <row r="292" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A292" s="4" t="s">
+      <c r="B292" s="14"/>
+    </row>
+    <row r="293" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A293" s="16" t="s">
         <v>316</v>
       </c>
-      <c r="B292" s="1"/>
-    </row>
-    <row r="293" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A293" s="4" t="s">
+      <c r="B293" s="14"/>
+    </row>
+    <row r="294" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A294" s="16" t="s">
         <v>317</v>
       </c>
-      <c r="B293" s="1"/>
-    </row>
-    <row r="294" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A294" s="4" t="s">
+      <c r="B294" s="18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A295" s="16" t="s">
         <v>318</v>
       </c>
-      <c r="B294" s="1"/>
-    </row>
-    <row r="295" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A295" s="4" t="s">
+      <c r="B295" s="14"/>
+    </row>
+    <row r="296" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A296" s="16" t="s">
         <v>319</v>
       </c>
-      <c r="B295" s="1"/>
-    </row>
-    <row r="296" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A296" s="4" t="s">
+      <c r="B296" s="14"/>
+    </row>
+    <row r="297" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A297" s="16" t="s">
         <v>320</v>
       </c>
-      <c r="B296" s="1"/>
-    </row>
-    <row r="297" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A297" s="4" t="s">
+      <c r="B297" s="14"/>
+    </row>
+    <row r="298" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A298" s="16" t="s">
         <v>321</v>
       </c>
-      <c r="B297" s="1"/>
-    </row>
-    <row r="298" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A298" s="4" t="s">
+      <c r="B298" s="14"/>
+    </row>
+    <row r="299" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A299" s="16" t="s">
         <v>322</v>
       </c>
-      <c r="B298" s="1"/>
-    </row>
-    <row r="299" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A299" s="4" t="s">
+      <c r="B299" s="14"/>
+    </row>
+    <row r="300" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A300" s="16" t="s">
         <v>323</v>
       </c>
-      <c r="B299" s="1"/>
-    </row>
-    <row r="300" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A300" s="4" t="s">
+      <c r="B300" s="18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A301" s="16" t="s">
         <v>324</v>
       </c>
-      <c r="B300" s="1"/>
-    </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A301" s="4" t="s">
+      <c r="B301" s="14"/>
+    </row>
+    <row r="302" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A302" s="16" t="s">
         <v>325</v>
       </c>
-      <c r="B301" s="1"/>
-    </row>
-    <row r="302" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A302" s="4" t="s">
+      <c r="B302" s="14"/>
+    </row>
+    <row r="303" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A303" s="16" t="s">
         <v>326</v>
       </c>
-      <c r="B302" s="1"/>
-    </row>
-    <row r="303" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A303" s="4" t="s">
+      <c r="B303" s="14"/>
+    </row>
+    <row r="304" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A304" s="16" t="s">
         <v>327</v>
       </c>
-      <c r="B303" s="1"/>
-    </row>
-    <row r="304" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A304" s="4" t="s">
+      <c r="B304" s="14"/>
+    </row>
+    <row r="305" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A305" s="16" t="s">
         <v>328</v>
       </c>
-      <c r="B304" s="1"/>
-    </row>
-    <row r="305" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A305" s="4" t="s">
+      <c r="B305" s="14"/>
+    </row>
+    <row r="306" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A306" s="16" t="s">
         <v>329</v>
       </c>
-      <c r="B305" s="1"/>
-    </row>
-    <row r="306" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A306" s="4" t="s">
+      <c r="B306" s="14"/>
+    </row>
+    <row r="307" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A307" s="16" t="s">
         <v>330</v>
       </c>
-      <c r="B306" s="1"/>
-    </row>
-    <row r="307" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A307" s="4" t="s">
+      <c r="B307" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A308" s="16" t="s">
         <v>331</v>
       </c>
-      <c r="B307" s="1"/>
-    </row>
-    <row r="308" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A308" s="4" t="s">
+      <c r="B308" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A309" s="16" t="s">
         <v>332</v>
       </c>
-      <c r="B308" s="1"/>
-    </row>
-    <row r="309" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A309" s="4" t="s">
+      <c r="B309" s="14"/>
+    </row>
+    <row r="310" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A310" s="16" t="s">
         <v>333</v>
       </c>
-      <c r="B309" s="1"/>
-    </row>
-    <row r="310" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A310" s="4" t="s">
+      <c r="B310" s="14"/>
+    </row>
+    <row r="311" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A311" s="16" t="s">
         <v>334</v>
       </c>
-      <c r="B310" s="1"/>
-    </row>
-    <row r="311" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A311" s="4" t="s">
+      <c r="B311" s="14"/>
+    </row>
+    <row r="312" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A312" s="16" t="s">
         <v>335</v>
       </c>
-      <c r="B311" s="1"/>
-    </row>
-    <row r="312" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A312" s="4" t="s">
+      <c r="B312" s="14"/>
+    </row>
+    <row r="313" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A313" s="16" t="s">
         <v>336</v>
       </c>
-      <c r="B312" s="1"/>
-    </row>
-    <row r="313" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A313" s="4" t="s">
+      <c r="B313" s="14"/>
+    </row>
+    <row r="314" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A314" s="16" t="s">
         <v>337</v>
       </c>
-      <c r="B313" s="1"/>
-    </row>
-    <row r="314" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A314" s="4" t="s">
+      <c r="B314" s="14"/>
+    </row>
+    <row r="315" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A315" s="16" t="s">
         <v>338</v>
       </c>
-      <c r="B314" s="1"/>
-    </row>
-    <row r="315" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A315" s="4" t="s">
+      <c r="B315" s="14"/>
+    </row>
+    <row r="316" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A316" s="16" t="s">
         <v>339</v>
       </c>
-      <c r="B315" s="1"/>
-    </row>
-    <row r="316" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A316" s="4" t="s">
+      <c r="B316" s="14"/>
+    </row>
+    <row r="317" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A317" s="16" t="s">
         <v>340</v>
       </c>
-      <c r="B316" s="1"/>
-    </row>
-    <row r="317" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A317" s="4" t="s">
+      <c r="B317" s="14"/>
+    </row>
+    <row r="318" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A318" s="16" t="s">
         <v>341</v>
       </c>
-      <c r="B317" s="1"/>
-    </row>
-    <row r="318" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A318" s="4" t="s">
+      <c r="B318" s="14"/>
+    </row>
+    <row r="319" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A319" s="16" t="s">
         <v>342</v>
       </c>
-      <c r="B318" s="1"/>
-    </row>
-    <row r="319" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A319" s="4" t="s">
+      <c r="B319" s="14"/>
+    </row>
+    <row r="320" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A320" s="16" t="s">
         <v>343</v>
       </c>
-      <c r="B319" s="1"/>
-    </row>
-    <row r="320" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A320" s="4" t="s">
+      <c r="B320" s="14"/>
+    </row>
+    <row r="321" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A321" s="16" t="s">
         <v>344</v>
       </c>
-      <c r="B320" s="1"/>
-    </row>
-    <row r="321" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A321" s="4" t="s">
+      <c r="B321" s="14"/>
+    </row>
+    <row r="322" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A322" s="16" t="s">
         <v>345</v>
       </c>
-      <c r="B321" s="1"/>
-    </row>
-    <row r="322" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A322" s="4" t="s">
+      <c r="B322" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A323" s="16" t="s">
         <v>346</v>
       </c>
-      <c r="B322" s="1"/>
-    </row>
-    <row r="323" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A323" s="4" t="s">
+      <c r="B323" s="14"/>
+    </row>
+    <row r="324" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A324" s="16" t="s">
         <v>347</v>
       </c>
-      <c r="B323" s="1"/>
-    </row>
-    <row r="324" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A324" s="4" t="s">
+      <c r="B324" s="14"/>
+    </row>
+    <row r="325" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A325" s="16" t="s">
         <v>348</v>
       </c>
-      <c r="B324" s="1"/>
-    </row>
-    <row r="325" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A325" s="4" t="s">
+      <c r="B325" s="14"/>
+    </row>
+    <row r="326" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A326" s="16" t="s">
         <v>349</v>
       </c>
-      <c r="B325" s="1"/>
-    </row>
-    <row r="326" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A326" s="4" t="s">
+      <c r="B326" s="14"/>
+    </row>
+    <row r="327" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A327" s="16" t="s">
         <v>350</v>
       </c>
-      <c r="B326" s="1"/>
-    </row>
-    <row r="327" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A327" s="4" t="s">
+      <c r="B327" s="14"/>
+    </row>
+    <row r="328" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A328" s="16" t="s">
         <v>351</v>
       </c>
-      <c r="B327" s="1"/>
-    </row>
-    <row r="328" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A328" s="4" t="s">
+      <c r="B328" s="14"/>
+    </row>
+    <row r="329" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A329" s="16" t="s">
         <v>352</v>
       </c>
-      <c r="B328" s="1"/>
-    </row>
-    <row r="329" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A329" s="4" t="s">
+      <c r="B329" s="14"/>
+    </row>
+    <row r="330" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A330" s="16" t="s">
         <v>353</v>
       </c>
-      <c r="B329" s="1"/>
-    </row>
-    <row r="330" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A330" s="4" t="s">
+      <c r="B330" s="14"/>
+    </row>
+    <row r="331" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A331" s="16" t="s">
         <v>354</v>
       </c>
-      <c r="B330" s="1"/>
-    </row>
-    <row r="331" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A331" s="4" t="s">
+      <c r="B331" s="14"/>
+    </row>
+    <row r="332" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A332" s="16" t="s">
         <v>355</v>
       </c>
-      <c r="B331" s="1"/>
-    </row>
-    <row r="332" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A332" s="4" t="s">
+      <c r="B332" s="14"/>
+    </row>
+    <row r="333" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A333" s="16" t="s">
         <v>356</v>
       </c>
-      <c r="B332" s="1"/>
-    </row>
-    <row r="333" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A333" s="4" t="s">
+      <c r="B333" s="14"/>
+    </row>
+    <row r="334" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A334" s="16" t="s">
         <v>357</v>
       </c>
-      <c r="B333" s="1"/>
-    </row>
-    <row r="334" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A334" s="4" t="s">
+      <c r="B334" s="14"/>
+    </row>
+    <row r="335" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A335" s="16" t="s">
         <v>358</v>
       </c>
-      <c r="B334" s="1"/>
-    </row>
-    <row r="335" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A335" s="4" t="s">
+      <c r="B335" s="14"/>
+    </row>
+    <row r="336" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A336" s="16" t="s">
         <v>359</v>
       </c>
-      <c r="B335" s="1"/>
-    </row>
-    <row r="336" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A336" s="4" t="s">
+      <c r="B336" s="14"/>
+    </row>
+    <row r="337" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A337" s="16" t="s">
         <v>360</v>
       </c>
-      <c r="B336" s="1"/>
-    </row>
-    <row r="337" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A337" s="4" t="s">
+      <c r="B337" s="14"/>
+    </row>
+    <row r="338" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A338" s="16" t="s">
         <v>361</v>
       </c>
-      <c r="B337" s="1"/>
-    </row>
-    <row r="338" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A338" s="4" t="s">
+      <c r="B338" s="14"/>
+    </row>
+    <row r="339" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A339" s="16" t="s">
         <v>362</v>
       </c>
-      <c r="B338" s="1"/>
-    </row>
-    <row r="339" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A339" s="4" t="s">
+      <c r="B339" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A340" s="16" t="s">
         <v>363</v>
       </c>
-      <c r="B339" s="1"/>
-    </row>
-    <row r="340" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A340" s="4" t="s">
+      <c r="B340" s="14"/>
+    </row>
+    <row r="341" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A341" s="16" t="s">
         <v>364</v>
       </c>
-      <c r="B340" s="1"/>
-    </row>
-    <row r="341" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A341" s="4" t="s">
+      <c r="B341" s="14"/>
+    </row>
+    <row r="342" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A342" s="16" t="s">
         <v>365</v>
       </c>
-      <c r="B341" s="1"/>
-    </row>
-    <row r="342" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A342" s="4" t="s">
+      <c r="B342" s="14"/>
+    </row>
+    <row r="343" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A343" s="16" t="s">
         <v>366</v>
       </c>
-      <c r="B342" s="1"/>
-    </row>
-    <row r="343" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A343" s="4" t="s">
+      <c r="B343" s="14"/>
+    </row>
+    <row r="344" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A344" s="16" t="s">
         <v>367</v>
       </c>
-      <c r="B343" s="1"/>
-    </row>
-    <row r="344" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A344" s="4" t="s">
+      <c r="B344" s="14"/>
+    </row>
+    <row r="345" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A345" s="16" t="s">
         <v>368</v>
       </c>
-      <c r="B344" s="1"/>
-    </row>
-    <row r="345" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A345" s="4" t="s">
+      <c r="B345" s="14"/>
+    </row>
+    <row r="346" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A346" s="16" t="s">
         <v>369</v>
       </c>
-      <c r="B345" s="1"/>
-    </row>
-    <row r="346" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A346" s="4" t="s">
+      <c r="B346" s="14"/>
+    </row>
+    <row r="347" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A347" s="16" t="s">
         <v>370</v>
       </c>
-      <c r="B346" s="1"/>
-    </row>
-    <row r="347" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A347" s="4" t="s">
+      <c r="B347" s="14"/>
+    </row>
+    <row r="348" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A348" s="16" t="s">
         <v>371</v>
       </c>
-      <c r="B347" s="1"/>
-    </row>
-    <row r="348" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A348" s="4" t="s">
+      <c r="B348" s="14"/>
+    </row>
+    <row r="349" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A349" s="16" t="s">
         <v>372</v>
       </c>
-      <c r="B348" s="1"/>
-    </row>
-    <row r="349" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A349" s="4" t="s">
+      <c r="B349" s="14"/>
+    </row>
+    <row r="350" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A350" s="16" t="s">
         <v>373</v>
       </c>
-      <c r="B349" s="1"/>
-    </row>
-    <row r="350" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A350" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="B350" s="1"/>
-    </row>
-    <row r="351" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A351" s="4" t="s">
+      <c r="B350" s="14"/>
+    </row>
+    <row r="351" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A351" s="16" t="s">
+        <v>693</v>
+      </c>
+      <c r="B351" s="14"/>
+    </row>
+    <row r="352" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A352" s="16" t="s">
         <v>375</v>
       </c>
-      <c r="B351" s="1"/>
-    </row>
-    <row r="352" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A352" s="4" t="s">
+      <c r="B352" s="14"/>
+    </row>
+    <row r="353" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A353" s="16" t="s">
         <v>376</v>
       </c>
-      <c r="B352" s="1"/>
-    </row>
-    <row r="353" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A353" s="4" t="s">
+      <c r="B353" s="14"/>
+    </row>
+    <row r="354" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A354" s="16" t="s">
         <v>377</v>
       </c>
-      <c r="B353" s="1"/>
-    </row>
-    <row r="354" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A354" s="4" t="s">
+      <c r="B354" s="14"/>
+    </row>
+    <row r="355" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A355" s="16" t="s">
         <v>378</v>
       </c>
-      <c r="B354" s="1"/>
-    </row>
-    <row r="355" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A355" s="4" t="s">
+      <c r="B355" s="14"/>
+    </row>
+    <row r="356" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A356" s="16" t="s">
         <v>379</v>
       </c>
-      <c r="B355" s="1"/>
-    </row>
-    <row r="356" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A356" s="4" t="s">
+      <c r="B356" s="14"/>
+    </row>
+    <row r="357" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A357" s="16" t="s">
         <v>380</v>
       </c>
-      <c r="B356" s="1"/>
-    </row>
-    <row r="357" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A357" s="4" t="s">
+      <c r="B357" s="14"/>
+    </row>
+    <row r="358" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A358" s="16" t="s">
         <v>381</v>
       </c>
-      <c r="B357" s="1"/>
-    </row>
-    <row r="358" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A358" s="4" t="s">
+      <c r="B358" s="14"/>
+    </row>
+    <row r="359" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A359" s="16" t="s">
         <v>382</v>
       </c>
-      <c r="B358" s="1"/>
-    </row>
-    <row r="359" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A359" s="4" t="s">
+      <c r="B359" s="14"/>
+    </row>
+    <row r="360" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A360" s="16" t="s">
         <v>383</v>
       </c>
-      <c r="B359" s="1"/>
-    </row>
-    <row r="360" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A360" s="4" t="s">
+      <c r="B360" s="14"/>
+    </row>
+    <row r="361" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A361" s="16" t="s">
         <v>384</v>
       </c>
-      <c r="B360" s="1"/>
-    </row>
-    <row r="361" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A361" s="4" t="s">
+      <c r="B361" s="14"/>
+    </row>
+    <row r="362" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A362" s="16" t="s">
         <v>385</v>
       </c>
-      <c r="B361" s="1"/>
-    </row>
-    <row r="362" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A362" s="4" t="s">
+      <c r="B362" s="14"/>
+    </row>
+    <row r="363" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A363" s="16" t="s">
         <v>386</v>
       </c>
-      <c r="B362" s="1"/>
-    </row>
-    <row r="363" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A363" s="4" t="s">
+      <c r="B363" s="14"/>
+    </row>
+    <row r="364" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A364" s="16" t="s">
         <v>387</v>
       </c>
-      <c r="B363" s="1"/>
-    </row>
-    <row r="364" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A364" s="4" t="s">
+      <c r="B364" s="14"/>
+    </row>
+    <row r="365" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A365" s="16" t="s">
         <v>388</v>
       </c>
-      <c r="B364" s="1"/>
-    </row>
-    <row r="365" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A365" s="4" t="s">
+      <c r="B365" s="14"/>
+    </row>
+    <row r="366" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A366" s="16" t="s">
         <v>389</v>
       </c>
-      <c r="B365" s="1"/>
-    </row>
-    <row r="366" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A366" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="B366" s="1"/>
-    </row>
-    <row r="367" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A367" s="4" t="s">
+      <c r="B366" s="14"/>
+    </row>
+    <row r="367" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A367" s="16" t="s">
+        <v>694</v>
+      </c>
+      <c r="B367" s="14"/>
+    </row>
+    <row r="368" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A368" s="16" t="s">
         <v>391</v>
       </c>
-      <c r="B367" s="1"/>
-    </row>
-    <row r="368" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A368" s="4" t="s">
+      <c r="B368" s="18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A369" s="16" t="s">
         <v>392</v>
       </c>
-      <c r="B368" s="1"/>
-    </row>
-    <row r="369" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A369" s="4" t="s">
+      <c r="B369" s="14"/>
+    </row>
+    <row r="370" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A370" s="16" t="s">
         <v>393</v>
       </c>
-      <c r="B369" s="1"/>
-    </row>
-    <row r="370" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A370" s="4" t="s">
+      <c r="B370" s="14"/>
+    </row>
+    <row r="371" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A371" s="16" t="s">
         <v>394</v>
       </c>
-      <c r="B370" s="1"/>
-    </row>
-    <row r="371" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A371" s="4" t="s">
+      <c r="B371" s="14"/>
+    </row>
+    <row r="372" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A372" s="16" t="s">
         <v>395</v>
       </c>
-      <c r="B371" s="1"/>
-    </row>
-    <row r="372" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A372" s="4" t="s">
+      <c r="B372" s="14"/>
+    </row>
+    <row r="373" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A373" s="16" t="s">
         <v>396</v>
       </c>
-      <c r="B372" s="1"/>
-    </row>
-    <row r="373" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A373" s="4" t="s">
+      <c r="B373" s="14"/>
+    </row>
+    <row r="374" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A374" s="16" t="s">
         <v>397</v>
       </c>
-      <c r="B373" s="1"/>
-    </row>
-    <row r="374" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A374" s="4" t="s">
+      <c r="B374" s="14"/>
+    </row>
+    <row r="375" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A375" s="16" t="s">
         <v>398</v>
       </c>
-      <c r="B374" s="1"/>
-    </row>
-    <row r="375" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A375" s="4" t="s">
+      <c r="B375" s="14"/>
+    </row>
+    <row r="376" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A376" s="16" t="s">
         <v>399</v>
       </c>
-      <c r="B375" s="1"/>
-    </row>
-    <row r="376" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A376" s="4" t="s">
+      <c r="B376" s="14"/>
+    </row>
+    <row r="377" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A377" s="16" t="s">
         <v>400</v>
       </c>
-      <c r="B376" s="1"/>
-    </row>
-    <row r="377" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A377" s="4" t="s">
+      <c r="B377" s="14"/>
+    </row>
+    <row r="378" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A378" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="B377" s="1"/>
-    </row>
-    <row r="378" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A378" s="4" t="s">
+      <c r="B378" s="14"/>
+    </row>
+    <row r="379" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A379" s="16" t="s">
         <v>402</v>
       </c>
-      <c r="B378" s="1"/>
-    </row>
-    <row r="379" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A379" s="4" t="s">
+      <c r="B379" s="14"/>
+    </row>
+    <row r="380" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A380" s="16" t="s">
         <v>403</v>
       </c>
-      <c r="B379" s="1"/>
-    </row>
-    <row r="380" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A380" s="4" t="s">
+      <c r="B380" s="14"/>
+    </row>
+    <row r="381" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A381" s="16" t="s">
         <v>404</v>
       </c>
-      <c r="B380" s="1"/>
-    </row>
-    <row r="381" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A381" s="4" t="s">
+      <c r="B381" s="14"/>
+    </row>
+    <row r="382" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A382" s="16" t="s">
         <v>405</v>
       </c>
-      <c r="B381" s="1"/>
-    </row>
-    <row r="382" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A382" s="4" t="s">
+      <c r="B382" s="14"/>
+    </row>
+    <row r="383" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A383" s="16" t="s">
         <v>406</v>
       </c>
-      <c r="B382" s="1"/>
-    </row>
-    <row r="383" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A383" s="4" t="s">
+      <c r="B383" s="14"/>
+    </row>
+    <row r="384" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A384" s="16" t="s">
         <v>407</v>
       </c>
-      <c r="B383" s="1"/>
-    </row>
-    <row r="384" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A384" s="4" t="s">
+      <c r="B384" s="14"/>
+    </row>
+    <row r="385" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A385" s="16" t="s">
         <v>408</v>
       </c>
-      <c r="B384" s="1"/>
-    </row>
-    <row r="385" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A385" s="4" t="s">
+      <c r="B385" s="14"/>
+    </row>
+    <row r="386" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A386" s="16" t="s">
         <v>409</v>
       </c>
-      <c r="B385" s="1"/>
-    </row>
-    <row r="386" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A386" s="4" t="s">
+      <c r="B386" s="14"/>
+    </row>
+    <row r="387" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A387" s="16" t="s">
         <v>410</v>
       </c>
-      <c r="B386" s="1"/>
-    </row>
-    <row r="387" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A387" s="4" t="s">
+      <c r="B387" s="14"/>
+    </row>
+    <row r="388" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A388" s="16" t="s">
         <v>411</v>
       </c>
-      <c r="B387" s="1"/>
-    </row>
-    <row r="388" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A388" s="4" t="s">
+      <c r="B388" s="14"/>
+    </row>
+    <row r="389" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A389" s="16" t="s">
         <v>412</v>
       </c>
-      <c r="B388" s="1"/>
-    </row>
-    <row r="389" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A389" s="4" t="s">
+      <c r="B389" s="14"/>
+    </row>
+    <row r="390" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A390" s="16" t="s">
         <v>413</v>
       </c>
-      <c r="B389" s="1"/>
-    </row>
-    <row r="390" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A390" s="4" t="s">
+      <c r="B390" s="14"/>
+    </row>
+    <row r="391" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A391" s="16" t="s">
         <v>414</v>
       </c>
-      <c r="B390" s="1"/>
-    </row>
-    <row r="391" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A391" s="4" t="s">
+      <c r="B391" s="14"/>
+    </row>
+    <row r="392" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A392" s="16" t="s">
         <v>415</v>
       </c>
-      <c r="B391" s="1"/>
-    </row>
-    <row r="392" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A392" s="4" t="s">
+      <c r="B392" s="14"/>
+    </row>
+    <row r="393" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A393" s="16" t="s">
         <v>416</v>
       </c>
-      <c r="B392" s="1"/>
-    </row>
-    <row r="393" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A393" s="4" t="s">
+      <c r="B393" s="14"/>
+    </row>
+    <row r="394" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A394" s="16" t="s">
         <v>417</v>
       </c>
-      <c r="B393" s="1"/>
-    </row>
-    <row r="394" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A394" s="4" t="s">
+      <c r="B394" s="14"/>
+    </row>
+    <row r="395" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A395" s="16" t="s">
         <v>418</v>
       </c>
-      <c r="B394" s="1"/>
-    </row>
-    <row r="395" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A395" s="4" t="s">
+      <c r="B395" s="14"/>
+    </row>
+    <row r="396" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A396" s="16" t="s">
         <v>419</v>
       </c>
-      <c r="B395" s="1"/>
-    </row>
-    <row r="396" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A396" s="4" t="s">
+      <c r="B396" s="14"/>
+    </row>
+    <row r="397" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A397" s="16" t="s">
         <v>420</v>
       </c>
-      <c r="B396" s="1"/>
-    </row>
-    <row r="397" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A397" s="4" t="s">
+      <c r="B397" s="14"/>
+    </row>
+    <row r="398" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A398" s="16" t="s">
         <v>421</v>
       </c>
-      <c r="B397" s="1"/>
-    </row>
-    <row r="398" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A398" s="4" t="s">
+      <c r="B398" s="14"/>
+    </row>
+    <row r="399" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A399" s="16" t="s">
         <v>422</v>
       </c>
-      <c r="B398" s="1"/>
-    </row>
-    <row r="399" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A399" s="4" t="s">
+      <c r="B399" s="14"/>
+    </row>
+    <row r="400" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A400" s="16" t="s">
         <v>423</v>
       </c>
-      <c r="B399" s="1"/>
-    </row>
-    <row r="400" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A400" s="4" t="s">
+      <c r="B400" s="14"/>
+    </row>
+    <row r="401" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A401" s="16" t="s">
         <v>424</v>
       </c>
-      <c r="B400" s="1"/>
-    </row>
-    <row r="401" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A401" s="4" t="s">
+      <c r="B401" s="14"/>
+    </row>
+    <row r="402" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A402" s="16" t="s">
         <v>425</v>
       </c>
-      <c r="B401" s="1"/>
-    </row>
-    <row r="402" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A402" s="4" t="s">
+      <c r="B402" s="14"/>
+    </row>
+    <row r="403" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A403" s="16" t="s">
         <v>426</v>
       </c>
-      <c r="B402" s="1"/>
-    </row>
-    <row r="403" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A403" s="4" t="s">
+      <c r="B403" s="14"/>
+    </row>
+    <row r="404" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A404" s="16" t="s">
         <v>427</v>
       </c>
-      <c r="B403" s="1"/>
-    </row>
-    <row r="404" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A404" s="4" t="s">
+      <c r="B404" s="14"/>
+    </row>
+    <row r="405" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A405" s="16" t="s">
         <v>428</v>
       </c>
-      <c r="B404" s="1"/>
-    </row>
-    <row r="405" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A405" s="4" t="s">
+      <c r="B405" s="14"/>
+    </row>
+    <row r="406" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A406" s="16" t="s">
         <v>429</v>
       </c>
-      <c r="B405" s="1"/>
-    </row>
-    <row r="406" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A406" s="4" t="s">
+      <c r="B406" s="14"/>
+    </row>
+    <row r="407" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A407" s="16" t="s">
         <v>430</v>
       </c>
-      <c r="B406" s="1"/>
-    </row>
-    <row r="407" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A407" s="4" t="s">
+      <c r="B407" s="14"/>
+    </row>
+    <row r="408" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A408" s="16" t="s">
         <v>431</v>
       </c>
-      <c r="B407" s="1"/>
-    </row>
-    <row r="408" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A408" s="4" t="s">
+      <c r="B408" s="14"/>
+    </row>
+    <row r="409" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A409" s="16" t="s">
         <v>432</v>
       </c>
-      <c r="B408" s="1"/>
-    </row>
-    <row r="409" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A409" s="4" t="s">
+      <c r="B409" s="14"/>
+    </row>
+    <row r="410" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A410" s="16" t="s">
         <v>433</v>
       </c>
-      <c r="B409" s="1"/>
-    </row>
-    <row r="410" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A410" s="4" t="s">
+      <c r="B410" s="14"/>
+    </row>
+    <row r="411" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A411" s="16" t="s">
         <v>434</v>
       </c>
-      <c r="B410" s="1"/>
-    </row>
-    <row r="411" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A411" s="4" t="s">
+      <c r="B411" s="14"/>
+    </row>
+    <row r="412" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A412" s="16" t="s">
         <v>435</v>
       </c>
-      <c r="B411" s="1"/>
-    </row>
-    <row r="412" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A412" s="4" t="s">
+      <c r="B412" s="14"/>
+    </row>
+    <row r="413" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A413" s="16" t="s">
         <v>436</v>
       </c>
-      <c r="B412" s="1"/>
-    </row>
-    <row r="413" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A413" s="4" t="s">
+      <c r="B413" s="14"/>
+    </row>
+    <row r="414" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A414" s="16" t="s">
         <v>437</v>
       </c>
-      <c r="B413" s="1"/>
-    </row>
-    <row r="414" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A414" s="4" t="s">
+      <c r="B414" s="14"/>
+    </row>
+    <row r="415" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A415" s="16" t="s">
         <v>438</v>
       </c>
-      <c r="B414" s="1"/>
-    </row>
-    <row r="415" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A415" s="4" t="s">
+      <c r="B415" s="14"/>
+    </row>
+    <row r="416" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A416" s="16" t="s">
         <v>439</v>
       </c>
-      <c r="B415" s="1"/>
-    </row>
-    <row r="416" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A416" s="4" t="s">
+      <c r="B416" s="14"/>
+    </row>
+    <row r="417" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A417" s="16" t="s">
         <v>440</v>
       </c>
-      <c r="B416" s="1"/>
-    </row>
-    <row r="417" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A417" s="4" t="s">
+      <c r="B417" s="14"/>
+    </row>
+    <row r="418" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A418" s="16" t="s">
         <v>441</v>
       </c>
-      <c r="B417" s="1"/>
-    </row>
-    <row r="418" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A418" s="4" t="s">
+      <c r="B418" s="14"/>
+    </row>
+    <row r="419" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A419" s="16" t="s">
         <v>442</v>
       </c>
-      <c r="B418" s="1"/>
-    </row>
-    <row r="419" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A419" s="4" t="s">
+      <c r="B419" s="14"/>
+    </row>
+    <row r="420" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A420" s="16" t="s">
         <v>443</v>
       </c>
-      <c r="B419" s="1"/>
-    </row>
-    <row r="420" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A420" s="4" t="s">
+      <c r="B420" s="14"/>
+    </row>
+    <row r="421" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A421" s="16" t="s">
         <v>444</v>
       </c>
-      <c r="B420" s="1"/>
-    </row>
-    <row r="421" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A421" s="4" t="s">
+      <c r="B421" s="14"/>
+    </row>
+    <row r="422" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A422" s="16" t="s">
         <v>445</v>
       </c>
-      <c r="B421" s="1"/>
-    </row>
-    <row r="422" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A422" s="4" t="s">
+      <c r="B422" s="14"/>
+    </row>
+    <row r="423" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A423" s="16" t="s">
         <v>446</v>
       </c>
-      <c r="B422" s="1"/>
-    </row>
-    <row r="423" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A423" s="4" t="s">
+      <c r="B423" s="14"/>
+    </row>
+    <row r="424" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A424" s="16" t="s">
         <v>447</v>
       </c>
-      <c r="B423" s="1"/>
-    </row>
-    <row r="424" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A424" s="4" t="s">
+      <c r="B424" s="14"/>
+    </row>
+    <row r="425" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A425" s="16" t="s">
         <v>448</v>
       </c>
-      <c r="B424" s="1"/>
-    </row>
-    <row r="425" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A425" s="4" t="s">
+      <c r="B425" s="14"/>
+    </row>
+    <row r="426" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A426" s="16" t="s">
         <v>449</v>
       </c>
-      <c r="B425" s="1"/>
-    </row>
-    <row r="426" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A426" s="4" t="s">
+      <c r="B426" s="14"/>
+    </row>
+    <row r="427" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A427" s="16" t="s">
         <v>450</v>
       </c>
-      <c r="B426" s="1"/>
-    </row>
-    <row r="427" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A427" s="4" t="s">
+      <c r="B427" s="18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A428" s="16" t="s">
         <v>451</v>
       </c>
-      <c r="B427" s="1"/>
-    </row>
-    <row r="428" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A428" s="4" t="s">
+      <c r="B428" s="14"/>
+    </row>
+    <row r="429" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A429" s="16" t="s">
         <v>452</v>
       </c>
-      <c r="B428" s="1"/>
-    </row>
-    <row r="429" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A429" s="4" t="s">
+      <c r="B429" s="14"/>
+    </row>
+    <row r="430" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A430" s="16" t="s">
         <v>453</v>
       </c>
-      <c r="B429" s="1"/>
-    </row>
-    <row r="430" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A430" s="4" t="s">
+      <c r="B430" s="14"/>
+    </row>
+    <row r="431" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A431" s="16" t="s">
         <v>454</v>
       </c>
-      <c r="B430" s="1"/>
-    </row>
-    <row r="431" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A431" s="4" t="s">
+      <c r="B431" s="14"/>
+    </row>
+    <row r="432" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A432" s="16" t="s">
         <v>455</v>
       </c>
-      <c r="B431" s="1"/>
-    </row>
-    <row r="432" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A432" s="4" t="s">
+      <c r="B432" s="18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A433" s="16" t="s">
         <v>456</v>
       </c>
-      <c r="B432" s="1"/>
-    </row>
-    <row r="433" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A433" s="4" t="s">
+      <c r="B433" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A434" s="16" t="s">
         <v>457</v>
       </c>
-      <c r="B433" s="1"/>
-    </row>
-    <row r="434" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A434" s="4" t="s">
+      <c r="B434" s="14"/>
+    </row>
+    <row r="435" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A435" s="16" t="s">
         <v>458</v>
       </c>
-      <c r="B434" s="1"/>
-    </row>
-    <row r="435" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A435" s="4" t="s">
+      <c r="B435" s="14"/>
+    </row>
+    <row r="436" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A436" s="16" t="s">
         <v>459</v>
       </c>
-      <c r="B435" s="1"/>
-    </row>
-    <row r="436" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A436" s="4" t="s">
+      <c r="B436" s="14"/>
+    </row>
+    <row r="437" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A437" s="16" t="s">
         <v>460</v>
       </c>
-      <c r="B436" s="1"/>
-    </row>
-    <row r="437" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A437" s="4" t="s">
+      <c r="B437" s="18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A438" s="16" t="s">
         <v>461</v>
       </c>
-      <c r="B437" s="1"/>
-    </row>
-    <row r="438" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A438" s="4" t="s">
+      <c r="B438" s="14"/>
+    </row>
+    <row r="439" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A439" s="16" t="s">
         <v>462</v>
       </c>
-      <c r="B438" s="1"/>
-    </row>
-    <row r="439" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A439" s="4" t="s">
+      <c r="B439" s="14"/>
+    </row>
+    <row r="440" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A440" s="16" t="s">
         <v>463</v>
       </c>
-      <c r="B439" s="1"/>
-    </row>
-    <row r="440" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A440" s="4" t="s">
+      <c r="B440" s="14"/>
+    </row>
+    <row r="441" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A441" s="16" t="s">
         <v>464</v>
       </c>
-      <c r="B440" s="1"/>
-    </row>
-    <row r="441" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A441" s="4" t="s">
+      <c r="B441" s="14"/>
+    </row>
+    <row r="442" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A442" s="16" t="s">
         <v>465</v>
       </c>
-      <c r="B441" s="1"/>
-    </row>
-    <row r="442" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A442" s="4" t="s">
+      <c r="B442" s="14"/>
+    </row>
+    <row r="443" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A443" s="16" t="s">
         <v>466</v>
       </c>
-      <c r="B442" s="1"/>
-    </row>
-    <row r="443" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A443" s="4" t="s">
+      <c r="B443" s="14"/>
+    </row>
+    <row r="444" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A444" s="16" t="s">
         <v>467</v>
       </c>
-      <c r="B443" s="1"/>
-    </row>
-    <row r="444" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A444" s="4" t="s">
+      <c r="B444" s="14"/>
+    </row>
+    <row r="445" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A445" s="16" t="s">
         <v>468</v>
       </c>
-      <c r="B444" s="1"/>
-    </row>
-    <row r="445" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A445" s="4" t="s">
+      <c r="B445" s="14"/>
+    </row>
+    <row r="446" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A446" s="16" t="s">
         <v>469</v>
       </c>
-      <c r="B445" s="1"/>
-    </row>
-    <row r="446" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A446" s="4" t="s">
+      <c r="B446" s="14"/>
+    </row>
+    <row r="447" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A447" s="16" t="s">
         <v>470</v>
       </c>
-      <c r="B446" s="1"/>
-    </row>
-    <row r="447" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A447" s="4" t="s">
+      <c r="B447" s="14"/>
+    </row>
+    <row r="448" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A448" s="16" t="s">
         <v>471</v>
       </c>
-      <c r="B447" s="1"/>
-    </row>
-    <row r="448" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A448" s="4" t="s">
+      <c r="B448" s="14"/>
+    </row>
+    <row r="449" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A449" s="16" t="s">
         <v>472</v>
       </c>
-      <c r="B448" s="1"/>
-    </row>
-    <row r="449" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A449" s="4" t="s">
+      <c r="B449" s="14"/>
+    </row>
+    <row r="450" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A450" s="16" t="s">
         <v>473</v>
       </c>
-      <c r="B449" s="1"/>
-    </row>
-    <row r="450" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A450" s="4" t="s">
+      <c r="B450" s="14"/>
+    </row>
+    <row r="451" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A451" s="16" t="s">
         <v>474</v>
       </c>
-      <c r="B450" s="1"/>
-    </row>
-    <row r="451" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A451" s="4" t="s">
+      <c r="B451" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A452" s="16" t="s">
         <v>475</v>
       </c>
-      <c r="B451" s="1"/>
-    </row>
-    <row r="452" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A452" s="4" t="s">
+      <c r="B452" s="14"/>
+    </row>
+    <row r="453" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A453" s="16" t="s">
         <v>476</v>
       </c>
-      <c r="B452" s="1"/>
-    </row>
-    <row r="453" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A453" s="4" t="s">
+      <c r="B453" s="14"/>
+    </row>
+    <row r="454" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A454" s="16" t="s">
         <v>477</v>
       </c>
-      <c r="B453" s="1"/>
-    </row>
-    <row r="454" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A454" s="4" t="s">
+      <c r="B454" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A455" s="16" t="s">
         <v>478</v>
       </c>
-      <c r="B454" s="1"/>
-    </row>
-    <row r="455" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A455" s="4" t="s">
+      <c r="B455" s="14"/>
+    </row>
+    <row r="456" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A456" s="16" t="s">
         <v>479</v>
       </c>
-      <c r="B455" s="1"/>
-    </row>
-    <row r="456" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A456" s="4" t="s">
+      <c r="B456" s="14"/>
+    </row>
+    <row r="457" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A457" s="16" t="s">
         <v>480</v>
       </c>
-      <c r="B456" s="1"/>
-    </row>
-    <row r="457" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A457" s="4" t="s">
+      <c r="B457" s="14"/>
+    </row>
+    <row r="458" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A458" s="16" t="s">
         <v>481</v>
       </c>
-      <c r="B457" s="1"/>
-    </row>
-    <row r="458" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A458" s="4" t="s">
+      <c r="B458" s="14"/>
+    </row>
+    <row r="459" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A459" s="16" t="s">
         <v>482</v>
       </c>
-      <c r="B458" s="1"/>
-    </row>
-    <row r="459" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A459" s="4" t="s">
+      <c r="B459" s="14"/>
+    </row>
+    <row r="460" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A460" s="16" t="s">
         <v>483</v>
       </c>
-      <c r="B459" s="1"/>
-    </row>
-    <row r="460" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A460" s="4" t="s">
+      <c r="B460" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="461" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A461" s="16" t="s">
         <v>484</v>
       </c>
-      <c r="B460" s="1"/>
-    </row>
-    <row r="461" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A461" s="4" t="s">
+      <c r="B461" s="14"/>
+    </row>
+    <row r="462" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A462" s="16" t="s">
         <v>485</v>
       </c>
-      <c r="B461" s="1"/>
-    </row>
-    <row r="462" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A462" s="4" t="s">
+      <c r="B462" s="14"/>
+    </row>
+    <row r="463" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A463" s="16" t="s">
         <v>486</v>
       </c>
-      <c r="B462" s="1"/>
-    </row>
-    <row r="463" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A463" s="4" t="s">
+      <c r="B463" s="14"/>
+    </row>
+    <row r="464" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A464" s="16" t="s">
         <v>487</v>
       </c>
-      <c r="B463" s="1"/>
-    </row>
-    <row r="464" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A464" s="4" t="s">
+      <c r="B464" s="14"/>
+    </row>
+    <row r="465" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A465" s="16" t="s">
         <v>488</v>
       </c>
-      <c r="B464" s="1"/>
-    </row>
-    <row r="465" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A465" s="4" t="s">
+      <c r="B465" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A466" s="16" t="s">
         <v>489</v>
       </c>
-      <c r="B465" s="1"/>
-    </row>
-    <row r="466" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A466" s="4" t="s">
+      <c r="B466" s="14"/>
+    </row>
+    <row r="467" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A467" s="16" t="s">
         <v>490</v>
       </c>
-      <c r="B466" s="1"/>
-    </row>
-    <row r="467" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A467" s="4" t="s">
+      <c r="B467" s="14"/>
+    </row>
+    <row r="468" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A468" s="16" t="s">
         <v>491</v>
       </c>
-      <c r="B467" s="1"/>
-    </row>
-    <row r="468" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A468" s="4" t="s">
+      <c r="B468" s="14"/>
+    </row>
+    <row r="469" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A469" s="16" t="s">
         <v>492</v>
       </c>
-      <c r="B468" s="1"/>
-    </row>
-    <row r="469" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A469" s="4" t="s">
+      <c r="B469" s="14"/>
+    </row>
+    <row r="470" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A470" s="16" t="s">
         <v>493</v>
       </c>
-      <c r="B469" s="1"/>
-    </row>
-    <row r="470" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A470" s="4" t="s">
+      <c r="B470" s="14"/>
+    </row>
+    <row r="471" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A471" s="16" t="s">
         <v>494</v>
       </c>
-      <c r="B470" s="1"/>
-    </row>
-    <row r="471" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A471" s="4" t="s">
+      <c r="B471" s="14"/>
+    </row>
+    <row r="472" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A472" s="16" t="s">
         <v>495</v>
       </c>
-      <c r="B471" s="1"/>
-    </row>
-    <row r="472" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A472" s="4" t="s">
+      <c r="B472" s="14"/>
+    </row>
+    <row r="473" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A473" s="16" t="s">
         <v>496</v>
       </c>
-      <c r="B472" s="1"/>
-    </row>
-    <row r="473" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A473" s="4" t="s">
+      <c r="B473" s="14"/>
+    </row>
+    <row r="474" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A474" s="16" t="s">
         <v>497</v>
       </c>
-      <c r="B473" s="1"/>
-    </row>
-    <row r="474" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A474" s="4" t="s">
+      <c r="B474" s="14"/>
+    </row>
+    <row r="475" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A475" s="16" t="s">
         <v>498</v>
       </c>
-      <c r="B474" s="1"/>
-    </row>
-    <row r="475" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A475" s="4" t="s">
+      <c r="B475" s="14"/>
+    </row>
+    <row r="476" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A476" s="16" t="s">
         <v>499</v>
       </c>
-      <c r="B475" s="1"/>
-    </row>
-    <row r="476" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A476" s="4" t="s">
+      <c r="B476" s="14"/>
+    </row>
+    <row r="477" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A477" s="16" t="s">
         <v>500</v>
       </c>
-      <c r="B476" s="1"/>
-    </row>
-    <row r="477" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A477" s="4" t="s">
+      <c r="B477" s="14"/>
+    </row>
+    <row r="478" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A478" s="16" t="s">
         <v>501</v>
       </c>
-      <c r="B477" s="1"/>
-    </row>
-    <row r="478" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A478" s="4" t="s">
+      <c r="B478" s="14"/>
+    </row>
+    <row r="479" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A479" s="16" t="s">
         <v>502</v>
       </c>
-      <c r="B478" s="1"/>
-    </row>
-    <row r="479" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A479" s="4" t="s">
+      <c r="B479" s="14"/>
+    </row>
+    <row r="480" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A480" s="16" t="s">
         <v>503</v>
       </c>
-      <c r="B479" s="1"/>
-    </row>
-    <row r="480" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A480" s="4" t="s">
+      <c r="B480" s="14"/>
+    </row>
+    <row r="481" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A481" s="16" t="s">
         <v>504</v>
       </c>
-      <c r="B480" s="1"/>
-    </row>
-    <row r="481" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A481" s="4" t="s">
-        <v>505</v>
-      </c>
-      <c r="B481" s="1"/>
-    </row>
-    <row r="482" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A482" s="4" t="s">
+      <c r="B481" s="14"/>
+    </row>
+    <row r="482" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A482" s="16" t="s">
+        <v>695</v>
+      </c>
+      <c r="B482" s="14"/>
+    </row>
+    <row r="483" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A483" s="16" t="s">
         <v>506</v>
       </c>
-      <c r="B482" s="1"/>
-    </row>
-    <row r="483" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A483" s="4" t="s">
+      <c r="B483" s="14"/>
+    </row>
+    <row r="484" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A484" s="16" t="s">
         <v>507</v>
       </c>
-      <c r="B483" s="1"/>
-    </row>
-    <row r="484" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A484" s="4" t="s">
+      <c r="B484" s="14"/>
+    </row>
+    <row r="485" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A485" s="16" t="s">
         <v>508</v>
       </c>
-      <c r="B484" s="1"/>
-    </row>
-    <row r="485" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A485" s="4" t="s">
+      <c r="B485" s="14"/>
+    </row>
+    <row r="486" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A486" s="16" t="s">
         <v>509</v>
       </c>
-      <c r="B485" s="1"/>
-    </row>
-    <row r="486" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A486" s="4" t="s">
+      <c r="B486" s="14"/>
+    </row>
+    <row r="487" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A487" s="16" t="s">
         <v>510</v>
       </c>
-      <c r="B486" s="1"/>
-    </row>
-    <row r="487" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A487" s="4" t="s">
+      <c r="B487" s="14"/>
+    </row>
+    <row r="488" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A488" s="16" t="s">
         <v>511</v>
       </c>
-      <c r="B487" s="1"/>
-    </row>
-    <row r="488" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A488" s="4" t="s">
+      <c r="B488" s="14"/>
+    </row>
+    <row r="489" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A489" s="16" t="s">
         <v>512</v>
       </c>
-      <c r="B488" s="1"/>
-    </row>
-    <row r="489" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A489" s="4" t="s">
+      <c r="B489" s="14"/>
+    </row>
+    <row r="490" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A490" s="16" t="s">
         <v>513</v>
       </c>
-      <c r="B489" s="1"/>
-    </row>
-    <row r="490" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A490" s="4" t="s">
+      <c r="B490" s="14"/>
+    </row>
+    <row r="491" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A491" s="16" t="s">
         <v>514</v>
       </c>
-      <c r="B490" s="1"/>
-    </row>
-    <row r="491" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A491" s="4" t="s">
+      <c r="B491" s="14"/>
+    </row>
+    <row r="492" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A492" s="16" t="s">
         <v>515</v>
       </c>
-      <c r="B491" s="1"/>
-    </row>
-    <row r="492" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A492" s="4" t="s">
+      <c r="B492" s="14"/>
+    </row>
+    <row r="493" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A493" s="16" t="s">
         <v>516</v>
       </c>
-      <c r="B492" s="1"/>
-    </row>
-    <row r="493" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A493" s="4" t="s">
+      <c r="B493" s="14"/>
+    </row>
+    <row r="494" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A494" s="16" t="s">
         <v>517</v>
       </c>
-      <c r="B493" s="1"/>
-    </row>
-    <row r="494" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A494" s="4" t="s">
+      <c r="B494" s="14"/>
+    </row>
+    <row r="495" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A495" s="16" t="s">
         <v>518</v>
       </c>
-      <c r="B494" s="1"/>
-    </row>
-    <row r="495" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A495" s="4" t="s">
+      <c r="B495" s="14"/>
+    </row>
+    <row r="496" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A496" s="16" t="s">
         <v>519</v>
       </c>
-      <c r="B495" s="1"/>
-    </row>
-    <row r="496" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A496" s="4" t="s">
+      <c r="B496" s="14"/>
+    </row>
+    <row r="497" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A497" s="16" t="s">
         <v>520</v>
       </c>
-      <c r="B496" s="1"/>
-    </row>
-    <row r="497" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A497" s="4" t="s">
-        <v>521</v>
-      </c>
-      <c r="B497" s="1"/>
-    </row>
-    <row r="498" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A498" s="4" t="s">
+      <c r="B497" s="14"/>
+    </row>
+    <row r="498" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A498" s="16" t="s">
+        <v>696</v>
+      </c>
+      <c r="B498" s="14"/>
+    </row>
+    <row r="499" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A499" s="16" t="s">
         <v>522</v>
       </c>
-      <c r="B498" s="1"/>
-    </row>
-    <row r="499" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A499" s="4" t="s">
+      <c r="B499" s="14"/>
+    </row>
+    <row r="500" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A500" s="16" t="s">
         <v>523</v>
       </c>
-      <c r="B499" s="1"/>
-    </row>
-    <row r="500" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A500" s="4" t="s">
+      <c r="B500" s="14"/>
+    </row>
+    <row r="501" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A501" s="16" t="s">
         <v>524</v>
       </c>
-      <c r="B500" s="1"/>
-    </row>
-    <row r="501" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A501" s="4" t="s">
+      <c r="B501" s="14"/>
+    </row>
+    <row r="502" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A502" s="16" t="s">
         <v>525</v>
       </c>
-      <c r="B501" s="1"/>
-    </row>
-    <row r="502" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A502" s="4" t="s">
+      <c r="B502" s="14"/>
+    </row>
+    <row r="503" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A503" s="16" t="s">
         <v>526</v>
       </c>
-      <c r="B502" s="1"/>
-    </row>
-    <row r="503" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A503" s="4" t="s">
+      <c r="B503" s="14"/>
+    </row>
+    <row r="504" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A504" s="16" t="s">
         <v>527</v>
       </c>
-      <c r="B503" s="1"/>
-    </row>
-    <row r="504" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A504" s="4" t="s">
+      <c r="B504" s="14"/>
+    </row>
+    <row r="505" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A505" s="16" t="s">
         <v>528</v>
       </c>
-      <c r="B504" s="1"/>
-    </row>
-    <row r="505" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A505" s="4" t="s">
+      <c r="B505" s="14"/>
+    </row>
+    <row r="506" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A506" s="16" t="s">
         <v>529</v>
       </c>
-      <c r="B505" s="1"/>
-    </row>
-    <row r="506" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A506" s="4" t="s">
+      <c r="B506" s="14"/>
+    </row>
+    <row r="507" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A507" s="16" t="s">
         <v>530</v>
       </c>
-      <c r="B506" s="1"/>
-    </row>
-    <row r="507" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A507" s="4" t="s">
+      <c r="B507" s="14"/>
+    </row>
+    <row r="508" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A508" s="16" t="s">
         <v>531</v>
       </c>
-      <c r="B507" s="1"/>
-    </row>
-    <row r="508" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A508" s="4" t="s">
+      <c r="B508" s="14"/>
+    </row>
+    <row r="509" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A509" s="16" t="s">
         <v>532</v>
       </c>
-      <c r="B508" s="1"/>
-    </row>
-    <row r="509" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A509" s="4" t="s">
+      <c r="B509" s="14"/>
+    </row>
+    <row r="510" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A510" s="16" t="s">
         <v>533</v>
       </c>
-      <c r="B509" s="1"/>
-    </row>
-    <row r="510" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A510" s="4" t="s">
+      <c r="B510" s="14"/>
+    </row>
+    <row r="511" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A511" s="16" t="s">
         <v>534</v>
       </c>
-      <c r="B510" s="1"/>
-    </row>
-    <row r="511" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A511" s="4" t="s">
+      <c r="B511" s="14"/>
+    </row>
+    <row r="512" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A512" s="16" t="s">
         <v>535</v>
       </c>
-      <c r="B511" s="1"/>
-    </row>
-    <row r="512" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A512" s="4" t="s">
+      <c r="B512" s="14"/>
+    </row>
+    <row r="513" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A513" s="16" t="s">
         <v>536</v>
       </c>
-      <c r="B512" s="1"/>
-    </row>
-    <row r="513" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A513" s="4" t="s">
+      <c r="B513" s="14"/>
+    </row>
+    <row r="514" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A514" s="16" t="s">
         <v>537</v>
       </c>
-      <c r="B513" s="1"/>
-    </row>
-    <row r="514" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A514" s="4" t="s">
+      <c r="B514" s="14"/>
+    </row>
+    <row r="515" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A515" s="16" t="s">
         <v>538</v>
       </c>
-      <c r="B514" s="1"/>
-    </row>
-    <row r="515" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A515" s="4" t="s">
+      <c r="B515" s="14"/>
+    </row>
+    <row r="516" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A516" s="16" t="s">
         <v>539</v>
       </c>
-      <c r="B515" s="1"/>
-    </row>
-    <row r="516" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A516" s="4" t="s">
+      <c r="B516" s="14"/>
+    </row>
+    <row r="517" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A517" s="16" t="s">
         <v>540</v>
       </c>
-      <c r="B516" s="1"/>
-    </row>
-    <row r="517" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A517" s="4" t="s">
+      <c r="B517" s="14"/>
+    </row>
+    <row r="518" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A518" s="16" t="s">
         <v>541</v>
       </c>
-      <c r="B517" s="1"/>
-    </row>
-    <row r="518" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A518" s="4" t="s">
+      <c r="B518" s="14"/>
+    </row>
+    <row r="519" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A519" s="16" t="s">
         <v>542</v>
       </c>
-      <c r="B518" s="1"/>
-    </row>
-    <row r="519" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A519" s="4" t="s">
+      <c r="B519" s="14"/>
+    </row>
+    <row r="520" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A520" s="16" t="s">
         <v>543</v>
       </c>
-      <c r="B519" s="1"/>
-    </row>
-    <row r="520" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A520" s="4" t="s">
+      <c r="B520" s="14"/>
+    </row>
+    <row r="521" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A521" s="16" t="s">
         <v>544</v>
       </c>
-      <c r="B520" s="1"/>
-    </row>
-    <row r="521" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A521" s="4" t="s">
+      <c r="B521" s="14"/>
+    </row>
+    <row r="522" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A522" s="16" t="s">
         <v>545</v>
       </c>
-      <c r="B521" s="1"/>
-    </row>
-    <row r="522" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A522" s="4" t="s">
+      <c r="B522" s="14"/>
+    </row>
+    <row r="523" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A523" s="16" t="s">
         <v>546</v>
       </c>
-      <c r="B522" s="1"/>
-    </row>
-    <row r="523" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A523" s="4" t="s">
+      <c r="B523" s="14"/>
+    </row>
+    <row r="524" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A524" s="16" t="s">
         <v>547</v>
       </c>
-      <c r="B523" s="1"/>
-    </row>
-    <row r="524" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A524" s="4" t="s">
+      <c r="B524" s="14"/>
+    </row>
+    <row r="525" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A525" s="16" t="s">
         <v>548</v>
       </c>
-      <c r="B524" s="1"/>
-    </row>
-    <row r="525" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A525" s="4" t="s">
+      <c r="B525" s="14"/>
+    </row>
+    <row r="526" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A526" s="16" t="s">
         <v>549</v>
       </c>
-      <c r="B525" s="1"/>
-    </row>
-    <row r="526" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A526" s="4" t="s">
+      <c r="B526" s="14"/>
+    </row>
+    <row r="527" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A527" s="16" t="s">
         <v>550</v>
       </c>
-      <c r="B526" s="1"/>
-    </row>
-    <row r="527" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A527" s="1"/>
-      <c r="B527" s="1"/>
-    </row>
-    <row r="528" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B527" s="14"/>
+    </row>
+    <row r="528" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A528" s="1"/>
       <c r="B528" s="1"/>
     </row>
-    <row r="529" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A529" s="1"/>
       <c r="B529" s="1"/>
     </row>
-    <row r="530" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A530" s="1"/>
       <c r="B530" s="1"/>
     </row>
-    <row r="531" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A531" s="1"/>
       <c r="B531" s="1"/>
     </row>
-    <row r="532" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A532" s="1"/>
       <c r="B532" s="1"/>
     </row>
-    <row r="533" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A533" s="1"/>
       <c r="B533" s="1"/>
     </row>
-    <row r="534" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A534" s="1"/>
       <c r="B534" s="1"/>
     </row>
-    <row r="535" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A535" s="1"/>
       <c r="B535" s="1"/>
     </row>
-    <row r="536" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A536" s="1"/>
       <c r="B536" s="1"/>
     </row>
-    <row r="537" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A537" s="1"/>
       <c r="B537" s="1"/>
     </row>
-    <row r="538" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A538" s="1"/>
       <c r="B538" s="1"/>
     </row>
-    <row r="539" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A539" s="1"/>
       <c r="B539" s="1"/>
     </row>
-    <row r="540" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A540" s="1"/>
       <c r="B540" s="1"/>
     </row>
-    <row r="541" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A541" s="1"/>
       <c r="B541" s="1"/>
     </row>
-    <row r="542" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A542" s="1"/>
       <c r="B542" s="1"/>
     </row>
-    <row r="543" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A543" s="1"/>
       <c r="B543" s="1"/>
     </row>
-    <row r="544" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A544" s="1"/>
       <c r="B544" s="1"/>
     </row>
-    <row r="545" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A545" s="1"/>
       <c r="B545" s="1"/>
     </row>
-    <row r="546" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A546" s="1"/>
       <c r="B546" s="1"/>
     </row>
-    <row r="547" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A547" s="1"/>
       <c r="B547" s="1"/>
     </row>
-    <row r="548" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A548" s="1"/>
       <c r="B548" s="1"/>
     </row>
-    <row r="549" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A549" s="1"/>
       <c r="B549" s="1"/>
     </row>
-    <row r="550" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A550" s="1"/>
       <c r="B550" s="1"/>
     </row>
-    <row r="551" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A551" s="1"/>
       <c r="B551" s="1"/>
     </row>
-    <row r="552" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A552" s="1"/>
       <c r="B552" s="1"/>
     </row>
-    <row r="553" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A553" s="1"/>
       <c r="B553" s="1"/>
     </row>
-    <row r="554" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A554" s="1"/>
       <c r="B554" s="1"/>
     </row>
-    <row r="555" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A555" s="1"/>
       <c r="B555" s="1"/>
     </row>
-    <row r="556" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A556" s="1"/>
       <c r="B556" s="1"/>
     </row>
-    <row r="557" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A557" s="1"/>
       <c r="B557" s="1"/>
     </row>
-    <row r="558" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A558" s="1"/>
       <c r="B558" s="1"/>
     </row>
-    <row r="559" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A559" s="1"/>
       <c r="B559" s="1"/>
     </row>
-    <row r="560" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A560" s="1"/>
       <c r="B560" s="1"/>
     </row>
-    <row r="561" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A561" s="1"/>
       <c r="B561" s="1"/>
     </row>
-    <row r="562" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A562" s="1"/>
       <c r="B562" s="1"/>
     </row>
-    <row r="563" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A563" s="1"/>
       <c r="B563" s="1"/>
     </row>
-    <row r="564" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A564" s="1"/>
       <c r="B564" s="1"/>
     </row>
-    <row r="565" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A565" s="1"/>
       <c r="B565" s="1"/>
     </row>
-    <row r="566" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A566" s="1"/>
       <c r="B566" s="1"/>
     </row>
-    <row r="567" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A567" s="1"/>
       <c r="B567" s="1"/>
     </row>
-    <row r="568" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A568" s="1"/>
       <c r="B568" s="1"/>
     </row>
-    <row r="569" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A569" s="1"/>
       <c r="B569" s="1"/>
     </row>
-    <row r="570" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A570" s="1"/>
       <c r="B570" s="1"/>
     </row>
-    <row r="571" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A571" s="1"/>
       <c r="B571" s="1"/>
     </row>
-    <row r="572" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A572" s="1"/>
       <c r="B572" s="1"/>
     </row>
-    <row r="573" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A573" s="1"/>
       <c r="B573" s="1"/>
     </row>
-    <row r="574" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A574" s="1"/>
       <c r="B574" s="1"/>
     </row>
-    <row r="575" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A575" s="1"/>
       <c r="B575" s="1"/>
     </row>
-    <row r="576" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A576" s="1"/>
       <c r="B576" s="1"/>
     </row>
-    <row r="577" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A577" s="1"/>
       <c r="B577" s="1"/>
     </row>
-    <row r="578" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A578" s="1"/>
       <c r="B578" s="1"/>
     </row>
-    <row r="579" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A579" s="1"/>
       <c r="B579" s="1"/>
     </row>
-    <row r="580" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
     </row>
-    <row r="581" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A581" s="1"/>
       <c r="B581" s="1"/>
     </row>
-    <row r="582" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A582" s="1"/>
       <c r="B582" s="1"/>
     </row>
-    <row r="583" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A583" s="1"/>
       <c r="B583" s="1"/>
     </row>
-    <row r="584" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A584" s="1"/>
       <c r="B584" s="1"/>
     </row>
-    <row r="585" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A585" s="1"/>
       <c r="B585" s="1"/>
     </row>
-    <row r="586" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A586" s="1"/>
       <c r="B586" s="1"/>
     </row>
-    <row r="587" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A587" s="1"/>
       <c r="B587" s="1"/>
     </row>
-    <row r="588" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A588" s="1"/>
       <c r="B588" s="1"/>
     </row>
-    <row r="589" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A589" s="1"/>
       <c r="B589" s="1"/>
     </row>
-    <row r="590" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A590" s="1"/>
       <c r="B590" s="1"/>
     </row>
-    <row r="591" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A591" s="1"/>
       <c r="B591" s="1"/>
     </row>
-    <row r="592" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A592" s="1"/>
       <c r="B592" s="1"/>
     </row>
-    <row r="593" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A593" s="1"/>
       <c r="B593" s="1"/>
     </row>
-    <row r="594" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A594" s="1"/>
       <c r="B594" s="1"/>
     </row>
-    <row r="595" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A595" s="1"/>
       <c r="B595" s="1"/>
     </row>
-    <row r="596" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A596" s="1"/>
       <c r="B596" s="1"/>
     </row>
-    <row r="597" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A597" s="1"/>
       <c r="B597" s="1"/>
     </row>
-    <row r="598" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A598" s="1"/>
       <c r="B598" s="1"/>
     </row>
-    <row r="599" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A599" s="1"/>
       <c r="B599" s="1"/>
     </row>
-    <row r="600" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A600" s="1"/>
       <c r="B600" s="1"/>
     </row>
-    <row r="601" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A601" s="1"/>
       <c r="B601" s="1"/>
     </row>
-    <row r="602" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A602" s="1"/>
       <c r="B602" s="1"/>
     </row>
-    <row r="603" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A603" s="1"/>
       <c r="B603" s="1"/>
     </row>
-    <row r="604" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A604" s="1"/>
       <c r="B604" s="1"/>
     </row>
-    <row r="605" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A605" s="1"/>
       <c r="B605" s="1"/>
     </row>
-    <row r="606" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A606" s="1"/>
       <c r="B606" s="1"/>
     </row>
-    <row r="607" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A607" s="1"/>
       <c r="B607" s="1"/>
     </row>
-    <row r="608" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A608" s="1"/>
       <c r="B608" s="1"/>
     </row>
-    <row r="609" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A609" s="1"/>
       <c r="B609" s="1"/>
     </row>
-    <row r="610" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A610" s="1"/>
       <c r="B610" s="1"/>
     </row>
-    <row r="611" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A611" s="1"/>
       <c r="B611" s="1"/>
     </row>
-    <row r="612" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A612" s="1"/>
       <c r="B612" s="1"/>
     </row>
-    <row r="613" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A613" s="1"/>
       <c r="B613" s="1"/>
     </row>
-    <row r="614" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A614" s="1"/>
       <c r="B614" s="1"/>
     </row>
-    <row r="615" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A615" s="1"/>
       <c r="B615" s="1"/>
     </row>
-    <row r="616" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A616" s="1"/>
       <c r="B616" s="1"/>
     </row>
-    <row r="617" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A617" s="1"/>
       <c r="B617" s="1"/>
     </row>
-    <row r="618" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A618" s="1"/>
       <c r="B618" s="1"/>
     </row>
-    <row r="619" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A619" s="1"/>
       <c r="B619" s="1"/>
     </row>
-    <row r="620" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A620" s="1"/>
       <c r="B620" s="1"/>
     </row>
-    <row r="621" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A621" s="1"/>
       <c r="B621" s="1"/>
     </row>
-    <row r="622" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A622" s="1"/>
       <c r="B622" s="1"/>
     </row>
-    <row r="623" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A623" s="1"/>
       <c r="B623" s="1"/>
     </row>
-    <row r="624" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A624" s="1"/>
       <c r="B624" s="1"/>
     </row>
-    <row r="625" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A625" s="1"/>
       <c r="B625" s="1"/>
     </row>
-    <row r="626" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A626" s="1"/>
       <c r="B626" s="1"/>
     </row>
-    <row r="627" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A627" s="1"/>
       <c r="B627" s="1"/>
     </row>
-    <row r="628" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A628" s="1"/>
       <c r="B628" s="1"/>
     </row>
-    <row r="629" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A629" s="1"/>
       <c r="B629" s="1"/>
     </row>
-    <row r="630" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A630" s="1"/>
       <c r="B630" s="1"/>
     </row>
-    <row r="631" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A631" s="1"/>
       <c r="B631" s="1"/>
     </row>
-    <row r="632" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A632" s="1"/>
       <c r="B632" s="1"/>
     </row>
-    <row r="633" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A633" s="1"/>
       <c r="B633" s="1"/>
     </row>
-    <row r="634" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A634" s="1"/>
       <c r="B634" s="1"/>
     </row>
-    <row r="635" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A635" s="1"/>
       <c r="B635" s="1"/>
     </row>
-    <row r="636" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A636" s="1"/>
       <c r="B636" s="1"/>
     </row>
-    <row r="637" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A637" s="1"/>
       <c r="B637" s="1"/>
     </row>
-    <row r="638" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A638" s="1"/>
       <c r="B638" s="1"/>
     </row>
-    <row r="639" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A639" s="1"/>
       <c r="B639" s="1"/>
     </row>
-    <row r="640" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A640" s="1"/>
       <c r="B640" s="1"/>
     </row>
-    <row r="641" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A641" s="1"/>
       <c r="B641" s="1"/>
     </row>
-    <row r="642" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A642" s="1"/>
       <c r="B642" s="1"/>
     </row>
-    <row r="643" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A643" s="1"/>
       <c r="B643" s="1"/>
     </row>
-    <row r="644" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A644" s="1"/>
       <c r="B644" s="1"/>
     </row>
-    <row r="645" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A645" s="1"/>
       <c r="B645" s="1"/>
     </row>
-    <row r="646" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A646" s="1"/>
       <c r="B646" s="1"/>
     </row>
-    <row r="647" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A647" s="1"/>
       <c r="B647" s="1"/>
     </row>
-    <row r="648" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A648" s="1"/>
       <c r="B648" s="1"/>
     </row>
-    <row r="649" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A649" s="1"/>
       <c r="B649" s="1"/>
     </row>
-    <row r="650" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A650" s="1"/>
       <c r="B650" s="1"/>
     </row>
-    <row r="651" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A651" s="1"/>
       <c r="B651" s="1"/>
     </row>
-    <row r="652" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A652" s="1"/>
       <c r="B652" s="1"/>
     </row>
-    <row r="653" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A653" s="1"/>
       <c r="B653" s="1"/>
     </row>
-    <row r="654" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A654" s="1"/>
       <c r="B654" s="1"/>
     </row>
-    <row r="655" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A655" s="1"/>
       <c r="B655" s="1"/>
     </row>
-    <row r="656" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A656" s="1"/>
       <c r="B656" s="1"/>
     </row>
-    <row r="657" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A657" s="1"/>
       <c r="B657" s="1"/>
     </row>
-    <row r="658" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A658" s="1"/>
       <c r="B658" s="1"/>
     </row>
-    <row r="659" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A659" s="1"/>
       <c r="B659" s="1"/>
     </row>
-    <row r="660" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A660" s="1"/>
       <c r="B660" s="1"/>
     </row>
-    <row r="661" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A661" s="1"/>
       <c r="B661" s="1"/>
     </row>
-    <row r="662" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A662" s="1"/>
       <c r="B662" s="1"/>
     </row>
-    <row r="663" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A663" s="1"/>
       <c r="B663" s="1"/>
     </row>
-    <row r="664" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A664" s="1"/>
       <c r="B664" s="1"/>
     </row>
-    <row r="665" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A665" s="1"/>
       <c r="B665" s="1"/>
     </row>
-    <row r="666" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A666" s="1"/>
       <c r="B666" s="1"/>
     </row>
-    <row r="667" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A667" s="1"/>
       <c r="B667" s="1"/>
     </row>
-    <row r="668" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A668" s="1"/>
       <c r="B668" s="1"/>
     </row>
-    <row r="669" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A669" s="1"/>
       <c r="B669" s="1"/>
     </row>
-    <row r="670" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A670" s="1"/>
       <c r="B670" s="1"/>
     </row>
-    <row r="671" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A671" s="1"/>
       <c r="B671" s="1"/>
     </row>
-    <row r="672" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A672" s="1"/>
       <c r="B672" s="1"/>
     </row>
-    <row r="673" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A673" s="1"/>
       <c r="B673" s="1"/>
     </row>
-    <row r="674" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A674" s="1"/>
       <c r="B674" s="1"/>
     </row>
-    <row r="675" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A675" s="1"/>
       <c r="B675" s="1"/>
     </row>
-    <row r="676" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A676" s="1"/>
       <c r="B676" s="1"/>
     </row>
-    <row r="677" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A677" s="1"/>
       <c r="B677" s="1"/>
     </row>
-    <row r="678" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A678" s="1"/>
       <c r="B678" s="1"/>
     </row>
-    <row r="679" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A679" s="1"/>
       <c r="B679" s="1"/>
     </row>
-    <row r="680" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A680" s="1"/>
       <c r="B680" s="1"/>
     </row>
-    <row r="681" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A681" s="1"/>
       <c r="B681" s="1"/>
     </row>
-    <row r="682" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A682" s="1"/>
       <c r="B682" s="1"/>
     </row>
-    <row r="683" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A683" s="1"/>
       <c r="B683" s="1"/>
     </row>
-    <row r="684" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A684" s="1"/>
       <c r="B684" s="1"/>
     </row>
-    <row r="685" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A685" s="1"/>
       <c r="B685" s="1"/>
     </row>
-    <row r="686" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A686" s="1"/>
       <c r="B686" s="1"/>
     </row>
-    <row r="687" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A687" s="1"/>
       <c r="B687" s="1"/>
     </row>
-    <row r="688" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A688" s="1"/>
       <c r="B688" s="1"/>
     </row>
-    <row r="689" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A689" s="1"/>
       <c r="B689" s="1"/>
     </row>
-    <row r="690" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A690" s="1"/>
       <c r="B690" s="1"/>
     </row>
-    <row r="691" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A691" s="1"/>
       <c r="B691" s="1"/>
     </row>
-    <row r="692" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A692" s="1"/>
       <c r="B692" s="1"/>
     </row>
-    <row r="693" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A693" s="1"/>
       <c r="B693" s="1"/>
     </row>
-    <row r="694" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A694" s="1"/>
       <c r="B694" s="1"/>
     </row>
-    <row r="695" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A695" s="1"/>
       <c r="B695" s="1"/>
     </row>
-    <row r="696" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A696" s="1"/>
       <c r="B696" s="1"/>
     </row>
-    <row r="697" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A697" s="1"/>
       <c r="B697" s="1"/>
     </row>
-    <row r="698" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A698" s="1"/>
       <c r="B698" s="1"/>
     </row>
-    <row r="699" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A699" s="1"/>
       <c r="B699" s="1"/>
     </row>
-    <row r="700" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A700" s="1"/>
       <c r="B700" s="1"/>
     </row>
-    <row r="701" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A701" s="1"/>
       <c r="B701" s="1"/>
     </row>
-    <row r="702" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A702" s="1"/>
       <c r="B702" s="1"/>
     </row>
-    <row r="703" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A703" s="1"/>
       <c r="B703" s="1"/>
     </row>
-    <row r="704" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A704" s="1"/>
       <c r="B704" s="1"/>
     </row>
-    <row r="705" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A705" s="1"/>
       <c r="B705" s="1"/>
     </row>
-    <row r="706" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A706" s="1"/>
       <c r="B706" s="1"/>
     </row>
-    <row r="707" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A707" s="1"/>
       <c r="B707" s="1"/>
     </row>
-    <row r="708" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A708" s="1"/>
       <c r="B708" s="1"/>
     </row>
-    <row r="709" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A709" s="1"/>
       <c r="B709" s="1"/>
     </row>
-    <row r="710" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A710" s="1"/>
       <c r="B710" s="1"/>
     </row>
-    <row r="711" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A711" s="1"/>
       <c r="B711" s="1"/>
     </row>
-    <row r="712" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A712" s="1"/>
       <c r="B712" s="1"/>
     </row>
-    <row r="713" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A713" s="1"/>
       <c r="B713" s="1"/>
     </row>
-    <row r="714" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A714" s="1"/>
       <c r="B714" s="1"/>
     </row>
-    <row r="715" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A715" s="1"/>
       <c r="B715" s="1"/>
     </row>
-    <row r="716" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A716" s="1"/>
       <c r="B716" s="1"/>
     </row>
-    <row r="717" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A717" s="1"/>
       <c r="B717" s="1"/>
     </row>
-    <row r="718" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A718" s="1"/>
       <c r="B718" s="1"/>
     </row>
-    <row r="719" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A719" s="1"/>
       <c r="B719" s="1"/>
     </row>
-    <row r="720" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A720" s="1"/>
       <c r="B720" s="1"/>
     </row>
-    <row r="721" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A721" s="1"/>
       <c r="B721" s="1"/>
     </row>
-    <row r="722" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A722" s="1"/>
       <c r="B722" s="1"/>
     </row>
-    <row r="723" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A723" s="1"/>
       <c r="B723" s="1"/>
     </row>
-    <row r="724" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A724" s="1"/>
       <c r="B724" s="1"/>
     </row>
-    <row r="725" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A725" s="1"/>
       <c r="B725" s="1"/>
     </row>
-    <row r="726" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A726" s="1"/>
       <c r="B726" s="1"/>
     </row>
-    <row r="727" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A727" s="1"/>
       <c r="B727" s="1"/>
     </row>
-    <row r="728" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A728" s="1"/>
       <c r="B728" s="1"/>
     </row>
-    <row r="729" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A729" s="1"/>
       <c r="B729" s="1"/>
     </row>
-    <row r="730" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A730" s="1"/>
       <c r="B730" s="1"/>
     </row>
-    <row r="731" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A731" s="1"/>
       <c r="B731" s="1"/>
     </row>
-    <row r="732" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A732" s="1"/>
       <c r="B732" s="1"/>
     </row>
-    <row r="733" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A733" s="1"/>
       <c r="B733" s="1"/>
     </row>
-    <row r="734" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A734" s="1"/>
       <c r="B734" s="1"/>
     </row>
-    <row r="735" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A735" s="1"/>
       <c r="B735" s="1"/>
     </row>
-    <row r="736" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A736" s="1"/>
       <c r="B736" s="1"/>
     </row>
-    <row r="737" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A737" s="1"/>
       <c r="B737" s="1"/>
     </row>
-    <row r="738" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A738" s="1"/>
       <c r="B738" s="1"/>
     </row>
-    <row r="739" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A739" s="1"/>
       <c r="B739" s="1"/>
     </row>
-    <row r="740" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A740" s="1"/>
       <c r="B740" s="1"/>
     </row>
-    <row r="741" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A741" s="1"/>
       <c r="B741" s="1"/>
     </row>
-    <row r="742" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A742" s="1"/>
       <c r="B742" s="1"/>
     </row>
-    <row r="743" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A743" s="1"/>
       <c r="B743" s="1"/>
     </row>
-    <row r="744" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A744" s="1"/>
       <c r="B744" s="1"/>
     </row>
-    <row r="745" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A745" s="1"/>
       <c r="B745" s="1"/>
     </row>
-    <row r="746" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A746" s="1"/>
       <c r="B746" s="1"/>
     </row>
-    <row r="747" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A747" s="1"/>
       <c r="B747" s="1"/>
     </row>
-    <row r="748" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A748" s="1"/>
       <c r="B748" s="1"/>
     </row>
-    <row r="749" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A749" s="1"/>
       <c r="B749" s="1"/>
     </row>
-    <row r="750" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A750" s="1"/>
       <c r="B750" s="1"/>
     </row>
-    <row r="751" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A751" s="1"/>
       <c r="B751" s="1"/>
     </row>
-    <row r="752" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A752" s="1"/>
       <c r="B752" s="1"/>
     </row>
-    <row r="753" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A753" s="1"/>
       <c r="B753" s="1"/>
     </row>
-    <row r="754" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A754" s="1"/>
       <c r="B754" s="1"/>
     </row>
-    <row r="755" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A755" s="1"/>
       <c r="B755" s="1"/>
     </row>
-    <row r="756" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A756" s="1"/>
       <c r="B756" s="1"/>
     </row>
-    <row r="757" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A757" s="1"/>
       <c r="B757" s="1"/>
     </row>
-    <row r="758" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A758" s="1"/>
       <c r="B758" s="1"/>
     </row>
-    <row r="759" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A759" s="1"/>
       <c r="B759" s="1"/>
     </row>
-    <row r="760" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A760" s="1"/>
       <c r="B760" s="1"/>
     </row>
-    <row r="761" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A761" s="1"/>
       <c r="B761" s="1"/>
     </row>
-    <row r="762" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A762" s="1"/>
       <c r="B762" s="1"/>
     </row>
-    <row r="763" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A763" s="1"/>
       <c r="B763" s="1"/>
     </row>
-    <row r="764" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A764" s="1"/>
       <c r="B764" s="1"/>
     </row>
-    <row r="765" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A765" s="1"/>
       <c r="B765" s="1"/>
     </row>
-    <row r="766" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A766" s="1"/>
       <c r="B766" s="1"/>
     </row>
-    <row r="767" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A767" s="1"/>
       <c r="B767" s="1"/>
     </row>
-    <row r="768" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A768" s="1"/>
       <c r="B768" s="1"/>
     </row>
-    <row r="769" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A769" s="1"/>
       <c r="B769" s="1"/>
     </row>
-    <row r="770" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A770" s="1"/>
       <c r="B770" s="1"/>
     </row>
-    <row r="771" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A771" s="1"/>
       <c r="B771" s="1"/>
     </row>
-    <row r="772" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A772" s="1"/>
       <c r="B772" s="1"/>
     </row>
-    <row r="773" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A773" s="1"/>
       <c r="B773" s="1"/>
     </row>
-    <row r="774" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A774" s="1"/>
       <c r="B774" s="1"/>
     </row>
-    <row r="775" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="775" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A775" s="1"/>
       <c r="B775" s="1"/>
     </row>
-    <row r="776" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="776" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A776" s="1"/>
       <c r="B776" s="1"/>
     </row>
-    <row r="777" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="777" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A777" s="1"/>
       <c r="B777" s="1"/>
     </row>
-    <row r="778" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A778" s="1"/>
       <c r="B778" s="1"/>
     </row>
-    <row r="779" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="779" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A779" s="1"/>
       <c r="B779" s="1"/>
     </row>
-    <row r="780" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A780" s="1"/>
       <c r="B780" s="1"/>
     </row>
-    <row r="781" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="781" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A781" s="1"/>
       <c r="B781" s="1"/>
     </row>
-    <row r="782" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="782" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A782" s="1"/>
       <c r="B782" s="1"/>
     </row>
-    <row r="783" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A783" s="1"/>
       <c r="B783" s="1"/>
     </row>
-    <row r="784" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="784" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A784" s="1"/>
       <c r="B784" s="1"/>
     </row>
-    <row r="785" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="785" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A785" s="1"/>
       <c r="B785" s="1"/>
     </row>
-    <row r="786" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="786" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A786" s="1"/>
       <c r="B786" s="1"/>
     </row>
-    <row r="787" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="787" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A787" s="1"/>
       <c r="B787" s="1"/>
     </row>
-    <row r="788" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="788" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A788" s="1"/>
       <c r="B788" s="1"/>
     </row>
-    <row r="789" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A789" s="1"/>
       <c r="B789" s="1"/>
     </row>
-    <row r="790" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="790" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A790" s="1"/>
       <c r="B790" s="1"/>
     </row>
-    <row r="791" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="791" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A791" s="1"/>
       <c r="B791" s="1"/>
     </row>
-    <row r="792" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="792" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A792" s="1"/>
       <c r="B792" s="1"/>
     </row>
-    <row r="793" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="793" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A793" s="1"/>
       <c r="B793" s="1"/>
     </row>
-    <row r="794" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="794" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A794" s="1"/>
       <c r="B794" s="1"/>
     </row>
-    <row r="795" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="795" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A795" s="1"/>
       <c r="B795" s="1"/>
     </row>
-    <row r="796" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="796" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A796" s="1"/>
       <c r="B796" s="1"/>
     </row>
-    <row r="797" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="797" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A797" s="1"/>
       <c r="B797" s="1"/>
     </row>
-    <row r="798" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="798" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A798" s="1"/>
       <c r="B798" s="1"/>
     </row>
-    <row r="799" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="799" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A799" s="1"/>
       <c r="B799" s="1"/>
     </row>
-    <row r="800" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="800" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A800" s="1"/>
       <c r="B800" s="1"/>
     </row>
-    <row r="801" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="801" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A801" s="1"/>
       <c r="B801" s="1"/>
     </row>
-    <row r="802" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="802" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A802" s="1"/>
       <c r="B802" s="1"/>
     </row>
-    <row r="803" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="803" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A803" s="1"/>
       <c r="B803" s="1"/>
     </row>
-    <row r="804" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="804" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A804" s="1"/>
       <c r="B804" s="1"/>
     </row>
-    <row r="805" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="805" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A805" s="1"/>
       <c r="B805" s="1"/>
     </row>
-    <row r="806" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="806" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A806" s="1"/>
       <c r="B806" s="1"/>
     </row>
-    <row r="807" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="807" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A807" s="1"/>
       <c r="B807" s="1"/>
     </row>
-    <row r="808" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="808" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A808" s="1"/>
       <c r="B808" s="1"/>
     </row>
-    <row r="809" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="809" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A809" s="1"/>
       <c r="B809" s="1"/>
     </row>
-    <row r="810" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="810" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A810" s="1"/>
       <c r="B810" s="1"/>
     </row>
-    <row r="811" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="811" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A811" s="1"/>
       <c r="B811" s="1"/>
     </row>
-    <row r="812" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="812" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A812" s="1"/>
       <c r="B812" s="1"/>
     </row>
-    <row r="813" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="813" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A813" s="1"/>
       <c r="B813" s="1"/>
     </row>
-    <row r="814" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="814" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A814" s="1"/>
       <c r="B814" s="1"/>
     </row>
-    <row r="815" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="815" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A815" s="1"/>
       <c r="B815" s="1"/>
     </row>
-    <row r="816" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="816" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A816" s="1"/>
       <c r="B816" s="1"/>
     </row>
-    <row r="817" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="817" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A817" s="1"/>
       <c r="B817" s="1"/>
     </row>
-    <row r="818" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="818" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A818" s="1"/>
       <c r="B818" s="1"/>
     </row>
-    <row r="819" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="819" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A819" s="1"/>
       <c r="B819" s="1"/>
     </row>
-    <row r="820" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="820" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A820" s="1"/>
       <c r="B820" s="1"/>
     </row>
-    <row r="821" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="821" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A821" s="1"/>
       <c r="B821" s="1"/>
     </row>
-    <row r="822" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="822" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A822" s="1"/>
       <c r="B822" s="1"/>
     </row>
-    <row r="823" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="823" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A823" s="1"/>
       <c r="B823" s="1"/>
     </row>
-    <row r="824" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="824" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A824" s="1"/>
       <c r="B824" s="1"/>
     </row>
-    <row r="825" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="825" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A825" s="1"/>
       <c r="B825" s="1"/>
     </row>
-    <row r="826" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="826" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A826" s="1"/>
       <c r="B826" s="1"/>
     </row>
-    <row r="827" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="827" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A827" s="1"/>
       <c r="B827" s="1"/>
     </row>
-    <row r="828" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="828" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A828" s="1"/>
       <c r="B828" s="1"/>
     </row>
-    <row r="829" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="829" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A829" s="1"/>
       <c r="B829" s="1"/>
     </row>
-    <row r="830" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="830" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A830" s="1"/>
       <c r="B830" s="1"/>
     </row>
-    <row r="831" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="831" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A831" s="1"/>
       <c r="B831" s="1"/>
     </row>
-    <row r="832" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="832" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A832" s="1"/>
       <c r="B832" s="1"/>
     </row>
-    <row r="833" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="833" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A833" s="1"/>
       <c r="B833" s="1"/>
     </row>
-    <row r="834" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="834" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A834" s="1"/>
       <c r="B834" s="1"/>
     </row>
-    <row r="835" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="835" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A835" s="1"/>
       <c r="B835" s="1"/>
     </row>
-    <row r="836" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="836" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A836" s="1"/>
       <c r="B836" s="1"/>
     </row>
-    <row r="837" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="837" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A837" s="1"/>
       <c r="B837" s="1"/>
     </row>
-    <row r="838" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="838" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A838" s="1"/>
       <c r="B838" s="1"/>
     </row>
-    <row r="839" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="839" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A839" s="1"/>
       <c r="B839" s="1"/>
     </row>
-    <row r="840" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="840" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A840" s="1"/>
       <c r="B840" s="1"/>
     </row>
-    <row r="841" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="841" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A841" s="1"/>
       <c r="B841" s="1"/>
     </row>
-    <row r="842" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="842" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A842" s="1"/>
       <c r="B842" s="1"/>
     </row>
-    <row r="843" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="843" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A843" s="1"/>
       <c r="B843" s="1"/>
     </row>
-    <row r="844" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="844" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A844" s="1"/>
       <c r="B844" s="1"/>
     </row>
-    <row r="845" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="845" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A845" s="1"/>
       <c r="B845" s="1"/>
     </row>
-    <row r="846" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="846" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A846" s="1"/>
       <c r="B846" s="1"/>
     </row>
-    <row r="847" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="847" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A847" s="1"/>
       <c r="B847" s="1"/>
     </row>
-    <row r="848" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="848" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A848" s="1"/>
       <c r="B848" s="1"/>
     </row>
-    <row r="849" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="849" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A849" s="1"/>
       <c r="B849" s="1"/>
     </row>
-    <row r="850" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="850" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A850" s="1"/>
       <c r="B850" s="1"/>
     </row>
-    <row r="851" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="851" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A851" s="1"/>
       <c r="B851" s="1"/>
     </row>
-    <row r="852" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="852" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A852" s="1"/>
       <c r="B852" s="1"/>
     </row>
-    <row r="853" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="853" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A853" s="1"/>
       <c r="B853" s="1"/>
     </row>
-    <row r="854" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="854" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A854" s="1"/>
       <c r="B854" s="1"/>
     </row>
-    <row r="855" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="855" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A855" s="1"/>
       <c r="B855" s="1"/>
     </row>
-    <row r="856" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="856" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A856" s="1"/>
       <c r="B856" s="1"/>
     </row>
-    <row r="857" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="857" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A857" s="1"/>
       <c r="B857" s="1"/>
     </row>
-    <row r="858" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="858" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A858" s="1"/>
       <c r="B858" s="1"/>
     </row>
-    <row r="859" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="859" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A859" s="1"/>
       <c r="B859" s="1"/>
     </row>
-    <row r="860" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="860" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A860" s="1"/>
       <c r="B860" s="1"/>
     </row>
-    <row r="861" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="861" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A861" s="1"/>
       <c r="B861" s="1"/>
     </row>
-    <row r="862" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="862" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A862" s="1"/>
       <c r="B862" s="1"/>
     </row>
-    <row r="863" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="863" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A863" s="1"/>
       <c r="B863" s="1"/>
     </row>
-    <row r="864" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="864" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A864" s="1"/>
       <c r="B864" s="1"/>
     </row>
-    <row r="865" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="865" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A865" s="1"/>
       <c r="B865" s="1"/>
     </row>
-    <row r="866" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="866" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A866" s="1"/>
       <c r="B866" s="1"/>
     </row>
-    <row r="867" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="867" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A867" s="1"/>
       <c r="B867" s="1"/>
     </row>
-    <row r="868" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="868" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A868" s="1"/>
       <c r="B868" s="1"/>
     </row>
-    <row r="869" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="869" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A869" s="1"/>
       <c r="B869" s="1"/>
     </row>
-    <row r="870" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="870" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A870" s="1"/>
       <c r="B870" s="1"/>
     </row>
-    <row r="871" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="871" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A871" s="1"/>
       <c r="B871" s="1"/>
     </row>
-    <row r="872" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="872" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A872" s="1"/>
       <c r="B872" s="1"/>
     </row>
-    <row r="873" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="873" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A873" s="1"/>
       <c r="B873" s="1"/>
     </row>
-    <row r="874" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="874" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A874" s="1"/>
       <c r="B874" s="1"/>
     </row>
-    <row r="875" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="875" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A875" s="1"/>
       <c r="B875" s="1"/>
     </row>
-    <row r="876" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="876" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A876" s="1"/>
       <c r="B876" s="1"/>
     </row>
-    <row r="877" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="877" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A877" s="1"/>
       <c r="B877" s="1"/>
     </row>
-    <row r="878" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="878" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A878" s="1"/>
       <c r="B878" s="1"/>
     </row>
-    <row r="879" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="879" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A879" s="1"/>
       <c r="B879" s="1"/>
     </row>
-    <row r="880" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="880" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A880" s="1"/>
       <c r="B880" s="1"/>
     </row>
-    <row r="881" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="881" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A881" s="1"/>
       <c r="B881" s="1"/>
     </row>
-    <row r="882" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="882" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A882" s="1"/>
       <c r="B882" s="1"/>
     </row>
-    <row r="883" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="883" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A883" s="1"/>
       <c r="B883" s="1"/>
     </row>
-    <row r="884" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="884" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A884" s="1"/>
       <c r="B884" s="1"/>
     </row>
-    <row r="885" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="885" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A885" s="1"/>
       <c r="B885" s="1"/>
     </row>
-    <row r="886" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="886" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A886" s="1"/>
       <c r="B886" s="1"/>
     </row>
-    <row r="887" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="887" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A887" s="1"/>
       <c r="B887" s="1"/>
     </row>
-    <row r="888" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="888" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A888" s="1"/>
       <c r="B888" s="1"/>
     </row>
-    <row r="889" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="889" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A889" s="1"/>
       <c r="B889" s="1"/>
     </row>
-    <row r="890" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="890" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A890" s="1"/>
       <c r="B890" s="1"/>
     </row>
-    <row r="891" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="891" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A891" s="1"/>
       <c r="B891" s="1"/>
     </row>
-    <row r="892" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="892" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A892" s="1"/>
       <c r="B892" s="1"/>
     </row>
-    <row r="893" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="893" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A893" s="1"/>
       <c r="B893" s="1"/>
     </row>
-    <row r="894" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="894" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A894" s="1"/>
       <c r="B894" s="1"/>
     </row>
-    <row r="895" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="895" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A895" s="1"/>
       <c r="B895" s="1"/>
     </row>
-    <row r="896" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="896" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A896" s="1"/>
       <c r="B896" s="1"/>
     </row>
-    <row r="897" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="897" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A897" s="1"/>
       <c r="B897" s="1"/>
     </row>
-    <row r="898" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="898" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A898" s="1"/>
       <c r="B898" s="1"/>
     </row>
-    <row r="899" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="899" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A899" s="1"/>
       <c r="B899" s="1"/>
     </row>
-    <row r="900" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="900" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A900" s="1"/>
       <c r="B900" s="1"/>
     </row>
-    <row r="901" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="901" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A901" s="1"/>
       <c r="B901" s="1"/>
     </row>
-    <row r="902" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="902" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A902" s="1"/>
       <c r="B902" s="1"/>
     </row>
-    <row r="903" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="903" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A903" s="1"/>
       <c r="B903" s="1"/>
     </row>
-    <row r="904" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="904" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A904" s="1"/>
       <c r="B904" s="1"/>
     </row>
-    <row r="905" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="905" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A905" s="1"/>
       <c r="B905" s="1"/>
     </row>
-    <row r="906" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="906" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A906" s="1"/>
       <c r="B906" s="1"/>
     </row>
-    <row r="907" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="907" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A907" s="1"/>
       <c r="B907" s="1"/>
     </row>
-    <row r="908" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="908" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A908" s="1"/>
       <c r="B908" s="1"/>
     </row>
-    <row r="909" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="909" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A909" s="1"/>
       <c r="B909" s="1"/>
     </row>
-    <row r="910" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="910" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A910" s="1"/>
       <c r="B910" s="1"/>
     </row>
-    <row r="911" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="911" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A911" s="1"/>
       <c r="B911" s="1"/>
     </row>
-    <row r="912" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="912" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A912" s="1"/>
       <c r="B912" s="1"/>
     </row>
-    <row r="913" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="913" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A913" s="1"/>
       <c r="B913" s="1"/>
     </row>
-    <row r="914" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="914" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A914" s="1"/>
       <c r="B914" s="1"/>
     </row>
-    <row r="915" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="915" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A915" s="1"/>
       <c r="B915" s="1"/>
     </row>
-    <row r="916" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="916" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A916" s="1"/>
       <c r="B916" s="1"/>
     </row>
-    <row r="917" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="917" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A917" s="1"/>
       <c r="B917" s="1"/>
     </row>
-    <row r="918" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="918" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A918" s="1"/>
       <c r="B918" s="1"/>
     </row>
-    <row r="919" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="919" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A919" s="1"/>
       <c r="B919" s="1"/>
     </row>
-    <row r="920" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="920" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A920" s="1"/>
       <c r="B920" s="1"/>
     </row>
-    <row r="921" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="921" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A921" s="1"/>
       <c r="B921" s="1"/>
     </row>
-    <row r="922" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="922" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A922" s="1"/>
       <c r="B922" s="1"/>
     </row>
-    <row r="923" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="923" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A923" s="1"/>
       <c r="B923" s="1"/>
     </row>
-    <row r="924" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="924" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A924" s="1"/>
       <c r="B924" s="1"/>
     </row>
-    <row r="925" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="925" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A925" s="1"/>
       <c r="B925" s="1"/>
     </row>
-    <row r="926" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="926" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A926" s="1"/>
       <c r="B926" s="1"/>
     </row>
-    <row r="927" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="927" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A927" s="1"/>
       <c r="B927" s="1"/>
     </row>
-    <row r="928" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="928" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A928" s="1"/>
       <c r="B928" s="1"/>
     </row>
-    <row r="929" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="929" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A929" s="1"/>
       <c r="B929" s="1"/>
     </row>
-    <row r="930" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="930" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A930" s="1"/>
       <c r="B930" s="1"/>
     </row>
-    <row r="931" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="931" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A931" s="1"/>
       <c r="B931" s="1"/>
     </row>
-    <row r="932" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="932" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A932" s="1"/>
       <c r="B932" s="1"/>
     </row>
-    <row r="933" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="933" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A933" s="1"/>
       <c r="B933" s="1"/>
     </row>
-    <row r="934" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="934" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A934" s="1"/>
       <c r="B934" s="1"/>
     </row>
-    <row r="935" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="935" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A935" s="1"/>
       <c r="B935" s="1"/>
     </row>
-    <row r="936" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="936" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A936" s="1"/>
       <c r="B936" s="1"/>
     </row>
-    <row r="937" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="937" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A937" s="1"/>
       <c r="B937" s="1"/>
     </row>
-    <row r="938" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="938" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A938" s="1"/>
       <c r="B938" s="1"/>
     </row>
-    <row r="939" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="939" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A939" s="1"/>
       <c r="B939" s="1"/>
     </row>
-    <row r="940" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="940" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A940" s="1"/>
       <c r="B940" s="1"/>
     </row>
-    <row r="941" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="941" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A941" s="1"/>
       <c r="B941" s="1"/>
     </row>
-    <row r="942" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="942" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A942" s="1"/>
       <c r="B942" s="1"/>
     </row>
-    <row r="943" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="943" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A943" s="1"/>
       <c r="B943" s="1"/>
     </row>
-    <row r="944" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="944" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A944" s="1"/>
       <c r="B944" s="1"/>
     </row>
-    <row r="945" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="945" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A945" s="1"/>
       <c r="B945" s="1"/>
     </row>
-    <row r="946" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="946" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A946" s="1"/>
       <c r="B946" s="1"/>
     </row>
-    <row r="947" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="947" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A947" s="1"/>
       <c r="B947" s="1"/>
     </row>
-    <row r="948" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="948" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A948" s="1"/>
       <c r="B948" s="1"/>
     </row>
-    <row r="949" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="949" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A949" s="1"/>
       <c r="B949" s="1"/>
     </row>
-    <row r="950" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="950" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A950" s="1"/>
       <c r="B950" s="1"/>
     </row>
-    <row r="951" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="951" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A951" s="1"/>
       <c r="B951" s="1"/>
     </row>
-    <row r="952" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="952" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A952" s="1"/>
       <c r="B952" s="1"/>
     </row>
-    <row r="953" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="953" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A953" s="1"/>
       <c r="B953" s="1"/>
     </row>
-    <row r="954" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="954" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A954" s="1"/>
       <c r="B954" s="1"/>
     </row>
-    <row r="955" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="955" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A955" s="1"/>
       <c r="B955" s="1"/>
     </row>
-    <row r="956" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="956" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A956" s="1"/>
       <c r="B956" s="1"/>
     </row>
-    <row r="957" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="957" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A957" s="1"/>
       <c r="B957" s="1"/>
     </row>
-    <row r="958" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="958" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A958" s="1"/>
       <c r="B958" s="1"/>
     </row>
-    <row r="959" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="959" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A959" s="1"/>
       <c r="B959" s="1"/>
     </row>
-    <row r="960" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="960" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A960" s="1"/>
       <c r="B960" s="1"/>
     </row>
-    <row r="961" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="961" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A961" s="1"/>
       <c r="B961" s="1"/>
     </row>
-    <row r="962" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="962" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A962" s="1"/>
       <c r="B962" s="1"/>
     </row>
-    <row r="963" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="963" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A963" s="1"/>
       <c r="B963" s="1"/>
     </row>
-    <row r="964" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="964" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A964" s="1"/>
       <c r="B964" s="1"/>
     </row>
-    <row r="965" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="965" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A965" s="1"/>
       <c r="B965" s="1"/>
     </row>
-    <row r="966" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="966" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A966" s="1"/>
       <c r="B966" s="1"/>
     </row>
-    <row r="967" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="967" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A967" s="1"/>
       <c r="B967" s="1"/>
     </row>
-    <row r="968" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="968" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A968" s="1"/>
       <c r="B968" s="1"/>
     </row>
-    <row r="969" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="969" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A969" s="1"/>
       <c r="B969" s="1"/>
     </row>
-    <row r="970" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="970" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A970" s="1"/>
       <c r="B970" s="1"/>
     </row>
-    <row r="971" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="971" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A971" s="1"/>
       <c r="B971" s="1"/>
     </row>
-    <row r="972" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="972" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A972" s="1"/>
       <c r="B972" s="1"/>
     </row>
-    <row r="973" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="973" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A973" s="1"/>
       <c r="B973" s="1"/>
     </row>
-    <row r="974" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="974" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A974" s="1"/>
       <c r="B974" s="1"/>
     </row>
-    <row r="975" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="975" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A975" s="1"/>
       <c r="B975" s="1"/>
     </row>
-    <row r="976" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="976" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A976" s="1"/>
       <c r="B976" s="1"/>
     </row>
-    <row r="977" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="977" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A977" s="1"/>
       <c r="B977" s="1"/>
     </row>
-    <row r="978" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="978" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A978" s="1"/>
       <c r="B978" s="1"/>
     </row>
-    <row r="979" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="979" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A979" s="1"/>
       <c r="B979" s="1"/>
     </row>
-    <row r="980" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="980" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A980" s="1"/>
       <c r="B980" s="1"/>
     </row>
-    <row r="981" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="981" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A981" s="1"/>
       <c r="B981" s="1"/>
     </row>
-    <row r="982" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="982" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A982" s="1"/>
       <c r="B982" s="1"/>
     </row>
-    <row r="983" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="983" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A983" s="1"/>
       <c r="B983" s="1"/>
     </row>
-    <row r="984" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="984" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A984" s="1"/>
       <c r="B984" s="1"/>
     </row>
-    <row r="985" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="985" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A985" s="1"/>
       <c r="B985" s="1"/>
     </row>
-    <row r="986" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="986" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A986" s="1"/>
       <c r="B986" s="1"/>
     </row>
-    <row r="987" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="987" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A987" s="1"/>
       <c r="B987" s="1"/>
     </row>
-    <row r="988" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="988" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A988" s="1"/>
       <c r="B988" s="1"/>
     </row>
-    <row r="989" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="989" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A989" s="1"/>
       <c r="B989" s="1"/>
     </row>
-    <row r="990" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="990" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A990" s="1"/>
       <c r="B990" s="1"/>
     </row>
-    <row r="991" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="991" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A991" s="1"/>
       <c r="B991" s="1"/>
     </row>
-    <row r="992" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="992" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A992" s="1"/>
       <c r="B992" s="1"/>
     </row>
-    <row r="993" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="993" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A993" s="1"/>
       <c r="B993" s="1"/>
     </row>
-    <row r="994" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="994" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A994" s="1"/>
       <c r="B994" s="1"/>
     </row>
-    <row r="995" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="995" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A995" s="1"/>
       <c r="B995" s="1"/>
     </row>
-    <row r="996" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="996" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A996" s="1"/>
       <c r="B996" s="1"/>
     </row>
-    <row r="997" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="997" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A997" s="1"/>
       <c r="B997" s="1"/>
     </row>
-    <row r="998" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="998" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A998" s="1"/>
       <c r="B998" s="1"/>
     </row>
-    <row r="999" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="999" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A999" s="1"/>
       <c r="B999" s="1"/>
     </row>
-    <row r="1000" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1000" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1000" s="1"/>
       <c r="B1000" s="1"/>
     </row>
-    <row r="1001" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1001" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1001" s="1"/>
       <c r="B1001" s="1"/>
     </row>
-    <row r="1002" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1002" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1002" s="1"/>
       <c r="B1002" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -35988,10 +36191,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -36007,7 +36210,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -36015,7 +36218,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -36039,7 +36242,7 @@
         <v>10</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -36047,7 +36250,7 @@
         <v>12</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -36119,7 +36322,7 @@
         <v>25</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
@@ -36127,7 +36330,7 @@
         <v>27</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -36143,7 +36346,7 @@
         <v>30</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
@@ -36191,7 +36394,7 @@
         <v>41</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
@@ -36231,7 +36434,7 @@
         <v>51</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
@@ -36239,7 +36442,7 @@
         <v>54</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
@@ -41158,28 +41361,28 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="B1" s="12" t="s">
+        <v>578</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>579</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>580</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>581</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>582</v>
+      </c>
+      <c r="G1" s="12" t="s">
         <v>583</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="H1" s="12" t="s">
         <v>584</v>
-      </c>
-      <c r="D1" s="12" t="s">
-        <v>585</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>586</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>587</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>588</v>
-      </c>
-      <c r="H1" s="12" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -41213,25 +41416,25 @@
         <v>4</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>643</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>644</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>645</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>646</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>647</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>648</v>
+      </c>
+      <c r="H3" s="6" t="s">
         <v>649</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>650</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>651</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>652</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>653</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>654</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -41239,25 +41442,25 @@
         <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
@@ -41369,25 +41572,25 @@
         <v>14</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -41577,25 +41780,25 @@
         <v>25</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
@@ -41603,25 +41806,25 @@
         <v>27</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
@@ -41658,10 +41861,10 @@
         <v>32</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>31</v>
@@ -41811,25 +42014,25 @@
         <v>41</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
@@ -41889,25 +42092,25 @@
         <v>47</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
@@ -41941,13 +42144,13 @@
         <v>51</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
@@ -41959,25 +42162,25 @@
         <v>54</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
@@ -52822,16 +53025,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -52853,13 +53056,13 @@
         <v>4</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -52867,13 +53070,13 @@
         <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -52881,13 +53084,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -52909,13 +53112,13 @@
         <v>10</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -52923,13 +53126,13 @@
         <v>12</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -52937,13 +53140,13 @@
         <v>14</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -53035,13 +53238,13 @@
         <v>24</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
@@ -53049,13 +53252,13 @@
         <v>25</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
@@ -53063,13 +53266,13 @@
         <v>27</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -53094,7 +53297,7 @@
         <v>31</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>32</v>
@@ -53175,13 +53378,13 @@
         <v>41</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
@@ -53245,13 +53448,13 @@
         <v>51</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
@@ -53259,13 +53462,13 @@
         <v>54</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
@@ -60183,13 +60386,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -60208,10 +60411,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -60219,10 +60422,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -60230,10 +60433,10 @@
         <v>7</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -60274,10 +60477,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -60307,10 +60510,10 @@
         <v>18</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -60362,10 +60565,10 @@
         <v>25</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -60373,10 +60576,10 @@
         <v>27</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -60398,7 +60601,7 @@
         <v>31</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>579</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -60517,7 +60720,7 @@
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="4" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -60525,10 +60728,10 @@
         <v>54</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -66555,13 +66758,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -66580,10 +66783,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -66591,10 +66794,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -66602,10 +66805,10 @@
         <v>7</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -66635,10 +66838,10 @@
         <v>12</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -66701,10 +66904,10 @@
         <v>21</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -66833,10 +67036,10 @@
         <v>41</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -66889,7 +67092,7 @@
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="4" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -66897,7 +67100,7 @@
         <v>54</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="C32" s="1"/>
     </row>

--- a/hspa-test.xlsx
+++ b/hspa-test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jonas.grabbe\tafi_test-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39A2F53B-73A2-4ACC-95BD-71679B47F1C6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20FA06A3-F869-465F-87ED-55B29F23F5D4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28770" windowHeight="12030" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2839,13 +2839,6 @@
       <c r="A33" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="8">
-        <v>1</v>
-      </c>
-      <c r="C33" s="8">
-        <v>1</v>
-      </c>
-      <c r="D33" s="1"/>
     </row>
     <row r="34" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
@@ -2859,8 +2852,12 @@
       <c r="A35" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
+      <c r="B35" s="8">
+        <v>1</v>
+      </c>
+      <c r="C35" s="8">
+        <v>1</v>
+      </c>
       <c r="D35" s="1"/>
     </row>
     <row r="36" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -9943,7 +9940,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -16905,9 +16902,6 @@
       <c r="A33" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="8">
-        <v>1</v>
-      </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="11" t="s">
@@ -16919,7 +16913,9 @@
       <c r="A35" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="1"/>
+      <c r="B35" s="8">
+        <v>1</v>
+      </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="11" t="s">
@@ -22344,18 +22340,6 @@
       <c r="A33" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="8">
-        <v>1</v>
-      </c>
-      <c r="C33" s="8">
-        <v>1</v>
-      </c>
-      <c r="D33" s="8">
-        <v>1</v>
-      </c>
-      <c r="E33" s="8">
-        <v>1</v>
-      </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="11" t="s">
@@ -22370,10 +22354,18 @@
       <c r="A35" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
+      <c r="B35" s="8">
+        <v>1</v>
+      </c>
+      <c r="C35" s="8">
+        <v>1</v>
+      </c>
+      <c r="D35" s="8">
+        <v>1</v>
+      </c>
+      <c r="E35" s="8">
+        <v>1</v>
+      </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="11" t="s">
@@ -36230,7 +36222,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -36502,9 +36494,6 @@
       <c r="A33" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="8">
-        <v>2</v>
-      </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="11" t="s">
@@ -36516,7 +36505,9 @@
       <c r="A35" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="1"/>
+      <c r="B35" s="8">
+        <v>2</v>
+      </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="11" t="s">
@@ -42240,9 +42231,6 @@
       <c r="A33" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="8">
-        <v>1</v>
-      </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
@@ -42266,7 +42254,9 @@
       <c r="A35" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="1"/>
+      <c r="B35" s="8">
+        <v>1</v>
+      </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
@@ -53528,15 +53518,6 @@
       <c r="A33" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="8">
-        <v>13</v>
-      </c>
-      <c r="C33" s="8">
-        <v>2</v>
-      </c>
-      <c r="D33" s="8">
-        <v>2</v>
-      </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="11" t="s">
@@ -53550,9 +53531,15 @@
       <c r="A35" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
+      <c r="B35" s="8">
+        <v>13</v>
+      </c>
+      <c r="C35" s="8">
+        <v>2</v>
+      </c>
+      <c r="D35" s="8">
+        <v>2</v>
+      </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="11" t="s">
@@ -60437,7 +60424,7 @@
   <dimension ref="A1:C1003"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>595</v>
       </c>
@@ -60448,7 +60435,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="11" t="s">
         <v>3</v>
       </c>
@@ -60459,7 +60446,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
         <v>4</v>
       </c>
@@ -60470,7 +60457,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
@@ -60481,7 +60468,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="11" t="s">
         <v>7</v>
       </c>
@@ -60492,7 +60479,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
         <v>9</v>
       </c>
@@ -60503,7 +60490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
         <v>622</v>
       </c>
@@ -60514,7 +60501,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
         <v>623</v>
       </c>
@@ -60525,7 +60512,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
         <v>624</v>
       </c>
@@ -60536,7 +60523,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
         <v>625</v>
       </c>
@@ -60547,7 +60534,7 @@
         <v>70000</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
         <v>626</v>
       </c>
@@ -60558,7 +60545,7 @@
         <v>35000</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
         <v>627</v>
       </c>
@@ -60569,7 +60556,7 @@
         <v>46145</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
         <v>628</v>
       </c>
@@ -60580,7 +60567,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
         <v>629</v>
       </c>
@@ -60591,7 +60578,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
         <v>630</v>
       </c>
@@ -60602,7 +60589,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
         <v>631</v>
       </c>
@@ -60613,7 +60600,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="11" t="s">
         <v>15</v>
       </c>
@@ -60624,7 +60611,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="11" t="s">
         <v>17</v>
       </c>
@@ -60635,7 +60622,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="11" t="s">
         <v>19</v>
       </c>
@@ -60646,7 +60633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="11" t="s">
         <v>20</v>
       </c>
@@ -60657,7 +60644,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
         <v>632</v>
       </c>
@@ -60668,7 +60655,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="11" t="s">
         <v>633</v>
       </c>
@@ -60679,7 +60666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="11" t="s">
         <v>23</v>
       </c>
@@ -60690,7 +60677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="11" t="s">
         <v>24</v>
       </c>
@@ -60701,7 +60688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="11" t="s">
         <v>25</v>
       </c>
@@ -60712,7 +60699,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="11" t="s">
         <v>634</v>
       </c>
@@ -60723,7 +60710,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="11" t="s">
         <v>635</v>
       </c>
@@ -60734,7 +60721,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="11" t="s">
         <v>636</v>
       </c>
@@ -60745,7 +60732,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="11" t="s">
         <v>637</v>
       </c>
@@ -60756,7 +60743,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="11" t="s">
         <v>33</v>
       </c>
@@ -60767,7 +60754,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="11" t="s">
         <v>35</v>
       </c>
@@ -60776,7 +60763,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="11" t="s">
         <v>37</v>
       </c>
@@ -60787,1246 +60774,1246 @@
         <v>578</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="11" t="s">
         <v>39</v>
       </c>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="11" t="s">
         <v>40</v>
       </c>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="11" t="s">
         <v>41</v>
       </c>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="11" t="s">
         <v>42</v>
       </c>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="11" t="s">
         <v>43</v>
       </c>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="11" t="s">
         <v>44</v>
       </c>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A39" s="11" t="s">
         <v>45</v>
       </c>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="11" t="s">
         <v>46</v>
       </c>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="11" t="s">
         <v>47</v>
       </c>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A42" s="11" t="s">
         <v>48</v>
       </c>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A43" s="11" t="s">
         <v>49</v>
       </c>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A44" s="11" t="s">
         <v>50</v>
       </c>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A45" s="11" t="s">
         <v>51</v>
       </c>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A46" s="11" t="s">
         <v>52</v>
       </c>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A47" s="11" t="s">
         <v>53</v>
       </c>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A48" s="11" t="s">
         <v>54</v>
       </c>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A49" s="11" t="s">
         <v>55</v>
       </c>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A50" s="11" t="s">
         <v>56</v>
       </c>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A51" s="11" t="s">
         <v>57</v>
       </c>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A52" s="11" t="s">
         <v>58</v>
       </c>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A53" s="11" t="s">
         <v>59</v>
       </c>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A54" s="11" t="s">
         <v>60</v>
       </c>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A55" s="11" t="s">
         <v>61</v>
       </c>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A56" s="11" t="s">
         <v>62</v>
       </c>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A57" s="11" t="s">
         <v>63</v>
       </c>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A58" s="11" t="s">
         <v>64</v>
       </c>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A59" s="11" t="s">
         <v>65</v>
       </c>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A60" s="11" t="s">
         <v>66</v>
       </c>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A61" s="11" t="s">
         <v>67</v>
       </c>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A62" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A63" s="11" t="s">
         <v>69</v>
       </c>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A64" s="11" t="s">
         <v>70</v>
       </c>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A65" s="11" t="s">
         <v>71</v>
       </c>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A66" s="11" t="s">
         <v>72</v>
       </c>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A67" s="11" t="s">
         <v>73</v>
       </c>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="11" t="s">
         <v>74</v>
       </c>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A69" s="11" t="s">
         <v>75</v>
       </c>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="11" t="s">
         <v>76</v>
       </c>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="11" t="s">
         <v>77</v>
       </c>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="11" t="s">
         <v>78</v>
       </c>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="11" t="s">
         <v>79</v>
       </c>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A74" s="11" t="s">
         <v>80</v>
       </c>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="11" t="s">
         <v>81</v>
       </c>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="11" t="s">
         <v>652</v>
       </c>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="11" t="s">
         <v>82</v>
       </c>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="11" t="s">
         <v>83</v>
       </c>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="11" t="s">
         <v>84</v>
       </c>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="11" t="s">
         <v>85</v>
       </c>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="11" t="s">
         <v>86</v>
       </c>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A82" s="11" t="s">
         <v>87</v>
       </c>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A83" s="11" t="s">
         <v>88</v>
       </c>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A84" s="11" t="s">
         <v>89</v>
       </c>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="11" t="s">
         <v>90</v>
       </c>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A86" s="11" t="s">
         <v>91</v>
       </c>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="11" t="s">
         <v>92</v>
       </c>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="11" t="s">
         <v>93</v>
       </c>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="11" t="s">
         <v>94</v>
       </c>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A90" s="11" t="s">
         <v>95</v>
       </c>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A91" s="11" t="s">
         <v>96</v>
       </c>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A92" s="11" t="s">
         <v>97</v>
       </c>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A93" s="11" t="s">
         <v>98</v>
       </c>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A94" s="11" t="s">
         <v>99</v>
       </c>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A95" s="11" t="s">
         <v>100</v>
       </c>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A96" s="11" t="s">
         <v>101</v>
       </c>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A97" s="11" t="s">
         <v>102</v>
       </c>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="11" t="s">
         <v>103</v>
       </c>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A99" s="11" t="s">
         <v>104</v>
       </c>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="11" t="s">
         <v>105</v>
       </c>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="11" t="s">
         <v>106</v>
       </c>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="11" t="s">
         <v>107</v>
       </c>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A103" s="11" t="s">
         <v>108</v>
       </c>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A104" s="11" t="s">
         <v>109</v>
       </c>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A105" s="11" t="s">
         <v>110</v>
       </c>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A106" s="11" t="s">
         <v>111</v>
       </c>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A107" s="11" t="s">
         <v>112</v>
       </c>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A108" s="11" t="s">
         <v>113</v>
       </c>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A109" s="11" t="s">
         <v>114</v>
       </c>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A110" s="11" t="s">
         <v>115</v>
       </c>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A111" s="11" t="s">
         <v>116</v>
       </c>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A112" s="11" t="s">
         <v>117</v>
       </c>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A113" s="11" t="s">
         <v>118</v>
       </c>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A114" s="11" t="s">
         <v>119</v>
       </c>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A115" s="11" t="s">
         <v>120</v>
       </c>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A116" s="11" t="s">
         <v>121</v>
       </c>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A117" s="11" t="s">
         <v>122</v>
       </c>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A118" s="11" t="s">
         <v>123</v>
       </c>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A119" s="11" t="s">
         <v>124</v>
       </c>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A120" s="11" t="s">
         <v>125</v>
       </c>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A121" s="11" t="s">
         <v>126</v>
       </c>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A122" s="11" t="s">
         <v>127</v>
       </c>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A123" s="11" t="s">
         <v>128</v>
       </c>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A124" s="11" t="s">
         <v>129</v>
       </c>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A125" s="11" t="s">
         <v>130</v>
       </c>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A126" s="11" t="s">
         <v>131</v>
       </c>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A127" s="11" t="s">
         <v>132</v>
       </c>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A128" s="11" t="s">
         <v>133</v>
       </c>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A129" s="11" t="s">
         <v>134</v>
       </c>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A130" s="11" t="s">
         <v>135</v>
       </c>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A131" s="11" t="s">
         <v>136</v>
       </c>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A132" s="11" t="s">
         <v>137</v>
       </c>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A133" s="11" t="s">
         <v>138</v>
       </c>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A134" s="11" t="s">
         <v>139</v>
       </c>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A135" s="11" t="s">
         <v>140</v>
       </c>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A136" s="11" t="s">
         <v>141</v>
       </c>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A137" s="11" t="s">
         <v>142</v>
       </c>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A138" s="11" t="s">
         <v>143</v>
       </c>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A139" s="11" t="s">
         <v>144</v>
       </c>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A140" s="11" t="s">
         <v>145</v>
       </c>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A141" s="11" t="s">
         <v>146</v>
       </c>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A142" s="11" t="s">
         <v>147</v>
       </c>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A143" s="11" t="s">
         <v>148</v>
       </c>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A144" s="11" t="s">
         <v>149</v>
       </c>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A145" s="11" t="s">
         <v>150</v>
       </c>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A146" s="11" t="s">
         <v>151</v>
       </c>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A147" s="11" t="s">
         <v>152</v>
       </c>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A148" s="11" t="s">
         <v>153</v>
       </c>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A149" s="11" t="s">
         <v>154</v>
       </c>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A150" s="11" t="s">
         <v>155</v>
       </c>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A151" s="11" t="s">
         <v>156</v>
       </c>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A152" s="11" t="s">
         <v>157</v>
       </c>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A153" s="11" t="s">
         <v>158</v>
       </c>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A154" s="11" t="s">
         <v>159</v>
       </c>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A155" s="11" t="s">
         <v>160</v>
       </c>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A156" s="11" t="s">
         <v>161</v>
       </c>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A157" s="11" t="s">
         <v>162</v>
       </c>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A158" s="11" t="s">
         <v>163</v>
       </c>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A159" s="11" t="s">
         <v>164</v>
       </c>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A160" s="11" t="s">
         <v>165</v>
       </c>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A161" s="11" t="s">
         <v>166</v>
       </c>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A162" s="11" t="s">
         <v>167</v>
       </c>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A163" s="11" t="s">
         <v>168</v>
       </c>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A164" s="11" t="s">
         <v>169</v>
       </c>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A165" s="11" t="s">
         <v>170</v>
       </c>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A166" s="11" t="s">
         <v>171</v>
       </c>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A167" s="11" t="s">
         <v>172</v>
       </c>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A168" s="11" t="s">
         <v>173</v>
       </c>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A169" s="11" t="s">
         <v>174</v>
       </c>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A170" s="11" t="s">
         <v>175</v>
       </c>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A171" s="11" t="s">
         <v>176</v>
       </c>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A172" s="11" t="s">
         <v>177</v>
       </c>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A173" s="11" t="s">
         <v>178</v>
       </c>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A174" s="11" t="s">
         <v>179</v>
       </c>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A175" s="11" t="s">
         <v>180</v>
       </c>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A176" s="11" t="s">
         <v>181</v>
       </c>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A177" s="11" t="s">
         <v>182</v>
       </c>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A178" s="11" t="s">
         <v>183</v>
       </c>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A179" s="11" t="s">
         <v>184</v>
       </c>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A180" s="11" t="s">
         <v>185</v>
       </c>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A181" s="11" t="s">
         <v>186</v>
       </c>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A182" s="11" t="s">
         <v>187</v>
       </c>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A183" s="11" t="s">
         <v>188</v>
       </c>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A184" s="11" t="s">
         <v>189</v>
       </c>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A185" s="11" t="s">
         <v>190</v>
       </c>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A186" s="11" t="s">
         <v>191</v>
       </c>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A187" s="11" t="s">
         <v>192</v>
       </c>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A188" s="11" t="s">
         <v>193</v>
       </c>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A189" s="11" t="s">
         <v>194</v>
       </c>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A190" s="11" t="s">
         <v>195</v>
       </c>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A191" s="11" t="s">
         <v>196</v>
       </c>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A192" s="11" t="s">
         <v>197</v>
       </c>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A193" s="11" t="s">
         <v>198</v>
       </c>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A194" s="11" t="s">
         <v>199</v>
       </c>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A195" s="11" t="s">
         <v>200</v>
       </c>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A196" s="11" t="s">
         <v>201</v>
       </c>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A197" s="11" t="s">
         <v>202</v>
       </c>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A198" s="11" t="s">
         <v>203</v>
       </c>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A199" s="11" t="s">
         <v>204</v>
       </c>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A200" s="11" t="s">
         <v>205</v>
       </c>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A201" s="11" t="s">
         <v>206</v>
       </c>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A202" s="11" t="s">
         <v>207</v>
       </c>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A203" s="11" t="s">
         <v>208</v>
       </c>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A204" s="11" t="s">
         <v>209</v>
       </c>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A205" s="11" t="s">
         <v>210</v>
       </c>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A206" s="11" t="s">
         <v>211</v>
       </c>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A207" s="11" t="s">
         <v>212</v>
       </c>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A208" s="11" t="s">
         <v>213</v>
       </c>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A209" s="11" t="s">
         <v>214</v>
       </c>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A210" s="11" t="s">
         <v>215</v>
       </c>
@@ -62035,245 +62022,245 @@
         <v>22</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A211" s="11" t="s">
         <v>216</v>
       </c>
       <c r="B211" s="1"/>
       <c r="C211" s="8"/>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A212" s="11" t="s">
         <v>217</v>
       </c>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A213" s="11" t="s">
         <v>218</v>
       </c>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A214" s="11" t="s">
         <v>219</v>
       </c>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A215" s="11" t="s">
         <v>220</v>
       </c>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A216" s="11" t="s">
         <v>221</v>
       </c>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A217" s="11" t="s">
         <v>222</v>
       </c>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A218" s="11" t="s">
         <v>223</v>
       </c>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A219" s="11" t="s">
         <v>224</v>
       </c>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A220" s="11" t="s">
         <v>225</v>
       </c>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A221" s="11" t="s">
         <v>226</v>
       </c>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A222" s="11" t="s">
         <v>227</v>
       </c>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A223" s="11" t="s">
         <v>228</v>
       </c>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A224" s="11" t="s">
         <v>229</v>
       </c>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A225" s="11" t="s">
         <v>230</v>
       </c>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A226" s="11" t="s">
         <v>231</v>
       </c>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A227" s="11" t="s">
         <v>232</v>
       </c>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A228" s="11" t="s">
         <v>233</v>
       </c>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A229" s="11" t="s">
         <v>234</v>
       </c>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A230" s="11" t="s">
         <v>235</v>
       </c>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A231" s="11" t="s">
         <v>236</v>
       </c>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A232" s="11" t="s">
         <v>237</v>
       </c>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A233" s="11" t="s">
         <v>238</v>
       </c>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A234" s="11" t="s">
         <v>239</v>
       </c>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A235" s="11" t="s">
         <v>240</v>
       </c>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A236" s="11" t="s">
         <v>241</v>
       </c>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A237" s="11" t="s">
         <v>242</v>
       </c>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A238" s="11" t="s">
         <v>243</v>
       </c>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A239" s="11" t="s">
         <v>244</v>
       </c>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A240" s="11" t="s">
         <v>245</v>
       </c>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A241" s="11" t="s">
         <v>246</v>
       </c>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A242" s="11" t="s">
         <v>247</v>
       </c>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A243" s="11" t="s">
         <v>248</v>
       </c>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A244" s="11" t="s">
         <v>523</v>
       </c>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A245" s="11" t="s">
         <v>250</v>
       </c>
@@ -62282,307 +62269,307 @@
         <v>11</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A246" s="11" t="s">
         <v>249</v>
       </c>
       <c r="B246" s="1"/>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A247" s="11" t="s">
         <v>638</v>
       </c>
       <c r="B247" s="1"/>
       <c r="C247" s="8"/>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A248" s="11" t="s">
         <v>639</v>
       </c>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A249" s="11" t="s">
         <v>653</v>
       </c>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A250" s="11" t="s">
         <v>251</v>
       </c>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A251" s="11" t="s">
         <v>252</v>
       </c>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A252" s="11" t="s">
         <v>654</v>
       </c>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A253" s="11" t="s">
         <v>253</v>
       </c>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A254" s="11" t="s">
         <v>254</v>
       </c>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A255" s="11" t="s">
         <v>655</v>
       </c>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A256" s="11" t="s">
         <v>255</v>
       </c>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A257" s="11" t="s">
         <v>256</v>
       </c>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A258" s="11" t="s">
         <v>656</v>
       </c>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A259" s="11" t="s">
         <v>257</v>
       </c>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A260" s="11" t="s">
         <v>258</v>
       </c>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A261" s="11" t="s">
         <v>657</v>
       </c>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A262" s="11" t="s">
         <v>259</v>
       </c>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A263" s="11" t="s">
         <v>260</v>
       </c>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A264" s="11" t="s">
         <v>658</v>
       </c>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A265" s="11" t="s">
         <v>261</v>
       </c>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A266" s="11" t="s">
         <v>262</v>
       </c>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A267" s="11" t="s">
         <v>659</v>
       </c>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A268" s="11" t="s">
         <v>263</v>
       </c>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A269" s="11" t="s">
         <v>264</v>
       </c>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A270" s="11" t="s">
         <v>660</v>
       </c>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A271" s="11" t="s">
         <v>265</v>
       </c>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A272" s="11" t="s">
         <v>266</v>
       </c>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A273" s="11" t="s">
         <v>661</v>
       </c>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A274" s="11" t="s">
         <v>267</v>
       </c>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A275" s="11" t="s">
         <v>268</v>
       </c>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A276" s="11" t="s">
         <v>662</v>
       </c>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A277" s="11" t="s">
         <v>269</v>
       </c>
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A278" s="11" t="s">
         <v>270</v>
       </c>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A279" s="11" t="s">
         <v>663</v>
       </c>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A280" s="11" t="s">
         <v>271</v>
       </c>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A281" s="11" t="s">
         <v>272</v>
       </c>
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A282" s="11" t="s">
         <v>664</v>
       </c>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A283" s="11" t="s">
         <v>273</v>
       </c>
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A284" s="11" t="s">
         <v>274</v>
       </c>
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A285" s="11" t="s">
         <v>275</v>
       </c>
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A286" s="11" t="s">
         <v>276</v>
       </c>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A287" s="11" t="s">
         <v>277</v>
       </c>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A288" s="11" t="s">
         <v>278</v>
       </c>
       <c r="B288" s="1"/>
       <c r="C288" s="8"/>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A289" s="11" t="s">
         <v>279</v>
       </c>
@@ -62591,7 +62578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A290" s="11" t="s">
         <v>280</v>
       </c>
@@ -62600,21 +62587,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A291" s="11" t="s">
         <v>281</v>
       </c>
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A292" s="11" t="s">
         <v>282</v>
       </c>
       <c r="B292" s="1"/>
       <c r="C292" s="8"/>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A293" s="11" t="s">
         <v>283</v>
       </c>
@@ -62623,42 +62610,42 @@
         <v>1</v>
       </c>
     </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A294" s="11" t="s">
         <v>284</v>
       </c>
       <c r="B294" s="1"/>
       <c r="C294" s="1"/>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A295" s="11" t="s">
         <v>285</v>
       </c>
       <c r="B295" s="1"/>
       <c r="C295" s="1"/>
     </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A296" s="11" t="s">
         <v>286</v>
       </c>
       <c r="B296" s="1"/>
       <c r="C296" s="1"/>
     </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A297" s="11" t="s">
         <v>287</v>
       </c>
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
     </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A298" s="11" t="s">
         <v>288</v>
       </c>
       <c r="B298" s="1"/>
       <c r="C298" s="8"/>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A299" s="11" t="s">
         <v>289</v>
       </c>
@@ -62667,28 +62654,28 @@
         <v>1</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A300" s="11" t="s">
         <v>290</v>
       </c>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A301" s="11" t="s">
         <v>291</v>
       </c>
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A302" s="11" t="s">
         <v>292</v>
       </c>
       <c r="B302" s="1"/>
       <c r="C302" s="8"/>
     </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A303" s="11" t="s">
         <v>293</v>
       </c>
@@ -62697,7 +62684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A304" s="11" t="s">
         <v>294</v>
       </c>
@@ -62706,21 +62693,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A305" s="11" t="s">
         <v>295</v>
       </c>
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
     </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A306" s="11" t="s">
         <v>296</v>
       </c>
       <c r="B306" s="1"/>
       <c r="C306" s="8"/>
     </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A307" s="11" t="s">
         <v>297</v>
       </c>
@@ -62729,7 +62716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A308" s="11" t="s">
         <v>298</v>
       </c>
@@ -62738,49 +62725,49 @@
         <v>1</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A309" s="11" t="s">
         <v>299</v>
       </c>
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
     </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A310" s="11" t="s">
         <v>300</v>
       </c>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
     </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A311" s="11" t="s">
         <v>301</v>
       </c>
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
     </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A312" s="11" t="s">
         <v>302</v>
       </c>
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
     </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A313" s="11" t="s">
         <v>303</v>
       </c>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
     </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A314" s="11" t="s">
         <v>304</v>
       </c>
       <c r="B314" s="8"/>
       <c r="C314" s="1"/>
     </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A315" s="11" t="s">
         <v>305</v>
       </c>
@@ -62789,154 +62776,154 @@
       </c>
       <c r="C315" s="1"/>
     </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A316" s="11" t="s">
         <v>306</v>
       </c>
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
     </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A317" s="11" t="s">
         <v>307</v>
       </c>
       <c r="B317" s="1"/>
       <c r="C317" s="1"/>
     </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A318" s="11" t="s">
         <v>308</v>
       </c>
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
     </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A319" s="11" t="s">
         <v>309</v>
       </c>
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
     </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A320" s="11" t="s">
         <v>310</v>
       </c>
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
     </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A321" s="11" t="s">
         <v>311</v>
       </c>
       <c r="B321" s="1"/>
       <c r="C321" s="1"/>
     </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A322" s="11" t="s">
         <v>312</v>
       </c>
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
     </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A323" s="11" t="s">
         <v>313</v>
       </c>
       <c r="B323" s="1"/>
       <c r="C323" s="1"/>
     </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A324" s="11" t="s">
         <v>314</v>
       </c>
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
     </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A325" s="11" t="s">
         <v>315</v>
       </c>
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
     </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A326" s="11" t="s">
         <v>316</v>
       </c>
       <c r="B326" s="1"/>
       <c r="C326" s="1"/>
     </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A327" s="11" t="s">
         <v>317</v>
       </c>
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
     </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A328" s="11" t="s">
         <v>318</v>
       </c>
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
     </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A329" s="11" t="s">
         <v>319</v>
       </c>
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
     </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A330" s="11" t="s">
         <v>320</v>
       </c>
       <c r="B330" s="1"/>
       <c r="C330" s="1"/>
     </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A331" s="11" t="s">
         <v>321</v>
       </c>
       <c r="B331" s="1"/>
       <c r="C331" s="1"/>
     </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A332" s="11" t="s">
         <v>322</v>
       </c>
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
     </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A333" s="11" t="s">
         <v>323</v>
       </c>
       <c r="B333" s="1"/>
       <c r="C333" s="1"/>
     </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A334" s="11" t="s">
         <v>324</v>
       </c>
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
     </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A335" s="11" t="s">
         <v>325</v>
       </c>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
     </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A336" s="11" t="s">
         <v>326</v>
       </c>
       <c r="B336" s="8"/>
       <c r="C336" s="8"/>
     </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A337" s="11" t="s">
         <v>327</v>
       </c>
@@ -62947,7 +62934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A338" s="11" t="s">
         <v>328</v>
       </c>
@@ -62956,7 +62943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A339" s="11" t="s">
         <v>329</v>
       </c>
@@ -62967,7 +62954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A340" s="11" t="s">
         <v>330</v>
       </c>
@@ -62976,28 +62963,28 @@
         <v>1</v>
       </c>
     </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A341" s="11" t="s">
         <v>331</v>
       </c>
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
     </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A342" s="11" t="s">
         <v>332</v>
       </c>
       <c r="B342" s="1"/>
       <c r="C342" s="1"/>
     </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A343" s="11" t="s">
         <v>333</v>
       </c>
       <c r="B343" s="1"/>
       <c r="C343" s="8"/>
     </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A344" s="11" t="s">
         <v>334</v>
       </c>
@@ -63006,42 +62993,42 @@
         <v>1</v>
       </c>
     </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A345" s="11" t="s">
         <v>335</v>
       </c>
       <c r="B345" s="1"/>
       <c r="C345" s="1"/>
     </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A346" s="11" t="s">
         <v>336</v>
       </c>
       <c r="B346" s="1"/>
       <c r="C346" s="1"/>
     </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A347" s="11" t="s">
         <v>337</v>
       </c>
       <c r="B347" s="1"/>
       <c r="C347" s="1"/>
     </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A348" s="11" t="s">
         <v>338</v>
       </c>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
     </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A349" s="11" t="s">
         <v>339</v>
       </c>
       <c r="B349" s="8"/>
       <c r="C349" s="1"/>
     </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A350" s="11" t="s">
         <v>340</v>
       </c>
@@ -63050,35 +63037,35 @@
       </c>
       <c r="C350" s="1"/>
     </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A351" s="11" t="s">
         <v>640</v>
       </c>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
     </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A352" s="11" t="s">
         <v>341</v>
       </c>
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
     </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A353" s="11" t="s">
         <v>342</v>
       </c>
       <c r="B353" s="1"/>
       <c r="C353" s="1"/>
     </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A354" s="11" t="s">
         <v>343</v>
       </c>
       <c r="B354" s="1"/>
       <c r="C354" s="8"/>
     </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A355" s="11" t="s">
         <v>344</v>
       </c>
@@ -63087,49 +63074,49 @@
         <v>1</v>
       </c>
     </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A356" s="11" t="s">
         <v>345</v>
       </c>
       <c r="B356" s="1"/>
       <c r="C356" s="1"/>
     </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A357" s="11" t="s">
         <v>346</v>
       </c>
       <c r="B357" s="1"/>
       <c r="C357" s="1"/>
     </row>
-    <row r="358" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A358" s="11" t="s">
         <v>347</v>
       </c>
       <c r="B358" s="1"/>
       <c r="C358" s="1"/>
     </row>
-    <row r="359" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A359" s="11" t="s">
         <v>348</v>
       </c>
       <c r="B359" s="1"/>
       <c r="C359" s="1"/>
     </row>
-    <row r="360" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A360" s="11" t="s">
         <v>349</v>
       </c>
       <c r="B360" s="1"/>
       <c r="C360" s="1"/>
     </row>
-    <row r="361" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A361" s="11" t="s">
         <v>350</v>
       </c>
       <c r="B361" s="1"/>
       <c r="C361" s="8"/>
     </row>
-    <row r="362" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A362" s="11" t="s">
         <v>351</v>
       </c>
@@ -63138,42 +63125,42 @@
         <v>1</v>
       </c>
     </row>
-    <row r="363" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A363" s="11" t="s">
         <v>352</v>
       </c>
       <c r="B363" s="1"/>
       <c r="C363" s="1"/>
     </row>
-    <row r="364" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A364" s="11" t="s">
         <v>353</v>
       </c>
       <c r="B364" s="1"/>
       <c r="C364" s="1"/>
     </row>
-    <row r="365" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A365" s="11" t="s">
         <v>354</v>
       </c>
       <c r="B365" s="1"/>
       <c r="C365" s="1"/>
     </row>
-    <row r="366" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A366" s="11" t="s">
         <v>355</v>
       </c>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
     </row>
-    <row r="367" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A367" s="11" t="s">
         <v>641</v>
       </c>
       <c r="B367" s="8"/>
       <c r="C367" s="1"/>
     </row>
-    <row r="368" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A368" s="11" t="s">
         <v>356</v>
       </c>
@@ -63182,98 +63169,98 @@
       </c>
       <c r="C368" s="1"/>
     </row>
-    <row r="369" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A369" s="11" t="s">
         <v>357</v>
       </c>
       <c r="B369" s="1"/>
       <c r="C369" s="1"/>
     </row>
-    <row r="370" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A370" s="11" t="s">
         <v>358</v>
       </c>
       <c r="B370" s="1"/>
       <c r="C370" s="1"/>
     </row>
-    <row r="371" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A371" s="11" t="s">
         <v>359</v>
       </c>
       <c r="B371" s="1"/>
       <c r="C371" s="1"/>
     </row>
-    <row r="372" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A372" s="11" t="s">
         <v>360</v>
       </c>
       <c r="B372" s="1"/>
       <c r="C372" s="1"/>
     </row>
-    <row r="373" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A373" s="11" t="s">
         <v>361</v>
       </c>
       <c r="B373" s="1"/>
       <c r="C373" s="1"/>
     </row>
-    <row r="374" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A374" s="11" t="s">
         <v>362</v>
       </c>
       <c r="B374" s="1"/>
       <c r="C374" s="1"/>
     </row>
-    <row r="375" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A375" s="11" t="s">
         <v>363</v>
       </c>
       <c r="B375" s="1"/>
       <c r="C375" s="1"/>
     </row>
-    <row r="376" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A376" s="11" t="s">
         <v>364</v>
       </c>
       <c r="B376" s="1"/>
       <c r="C376" s="1"/>
     </row>
-    <row r="377" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A377" s="11" t="s">
         <v>365</v>
       </c>
       <c r="B377" s="1"/>
       <c r="C377" s="1"/>
     </row>
-    <row r="378" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A378" s="11" t="s">
         <v>366</v>
       </c>
       <c r="B378" s="1"/>
       <c r="C378" s="1"/>
     </row>
-    <row r="379" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A379" s="11" t="s">
         <v>367</v>
       </c>
       <c r="B379" s="1"/>
       <c r="C379" s="1"/>
     </row>
-    <row r="380" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A380" s="11" t="s">
         <v>368</v>
       </c>
       <c r="B380" s="1"/>
       <c r="C380" s="1"/>
     </row>
-    <row r="381" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A381" s="11" t="s">
         <v>369</v>
       </c>
       <c r="B381" s="8"/>
       <c r="C381" s="1"/>
     </row>
-    <row r="382" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A382" s="11" t="s">
         <v>370</v>
       </c>
@@ -63282,21 +63269,21 @@
       </c>
       <c r="C382" s="1"/>
     </row>
-    <row r="383" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A383" s="11" t="s">
         <v>371</v>
       </c>
       <c r="B383" s="1"/>
       <c r="C383" s="1"/>
     </row>
-    <row r="384" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A384" s="11" t="s">
         <v>372</v>
       </c>
       <c r="B384" s="8"/>
       <c r="C384" s="1"/>
     </row>
-    <row r="385" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A385" s="11" t="s">
         <v>373</v>
       </c>
@@ -63305,49 +63292,49 @@
       </c>
       <c r="C385" s="1"/>
     </row>
-    <row r="386" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A386" s="11" t="s">
         <v>374</v>
       </c>
       <c r="B386" s="1"/>
       <c r="C386" s="1"/>
     </row>
-    <row r="387" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A387" s="11" t="s">
         <v>375</v>
       </c>
       <c r="B387" s="1"/>
       <c r="C387" s="1"/>
     </row>
-    <row r="388" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A388" s="11" t="s">
         <v>376</v>
       </c>
       <c r="B388" s="1"/>
       <c r="C388" s="1"/>
     </row>
-    <row r="389" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A389" s="11" t="s">
         <v>377</v>
       </c>
       <c r="B389" s="1"/>
       <c r="C389" s="1"/>
     </row>
-    <row r="390" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A390" s="11" t="s">
         <v>378</v>
       </c>
       <c r="B390" s="1"/>
       <c r="C390" s="1"/>
     </row>
-    <row r="391" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A391" s="11" t="s">
         <v>379</v>
       </c>
       <c r="B391" s="8"/>
       <c r="C391" s="1"/>
     </row>
-    <row r="392" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A392" s="11" t="s">
         <v>380</v>
       </c>
@@ -63356,189 +63343,189 @@
       </c>
       <c r="C392" s="1"/>
     </row>
-    <row r="393" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A393" s="11" t="s">
         <v>381</v>
       </c>
       <c r="B393" s="1"/>
       <c r="C393" s="1"/>
     </row>
-    <row r="394" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A394" s="11" t="s">
         <v>382</v>
       </c>
       <c r="B394" s="1"/>
       <c r="C394" s="1"/>
     </row>
-    <row r="395" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A395" s="11" t="s">
         <v>383</v>
       </c>
       <c r="B395" s="1"/>
       <c r="C395" s="1"/>
     </row>
-    <row r="396" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A396" s="11" t="s">
         <v>384</v>
       </c>
       <c r="B396" s="1"/>
       <c r="C396" s="1"/>
     </row>
-    <row r="397" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A397" s="11" t="s">
         <v>385</v>
       </c>
       <c r="B397" s="1"/>
       <c r="C397" s="1"/>
     </row>
-    <row r="398" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A398" s="11" t="s">
         <v>386</v>
       </c>
       <c r="B398" s="1"/>
       <c r="C398" s="1"/>
     </row>
-    <row r="399" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A399" s="11" t="s">
         <v>387</v>
       </c>
       <c r="B399" s="1"/>
       <c r="C399" s="1"/>
     </row>
-    <row r="400" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A400" s="11" t="s">
         <v>388</v>
       </c>
       <c r="B400" s="1"/>
       <c r="C400" s="1"/>
     </row>
-    <row r="401" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A401" s="11" t="s">
         <v>389</v>
       </c>
       <c r="B401" s="1"/>
       <c r="C401" s="1"/>
     </row>
-    <row r="402" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A402" s="11" t="s">
         <v>390</v>
       </c>
       <c r="B402" s="1"/>
       <c r="C402" s="1"/>
     </row>
-    <row r="403" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A403" s="11" t="s">
         <v>391</v>
       </c>
       <c r="B403" s="1"/>
       <c r="C403" s="1"/>
     </row>
-    <row r="404" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A404" s="11" t="s">
         <v>392</v>
       </c>
       <c r="B404" s="1"/>
       <c r="C404" s="1"/>
     </row>
-    <row r="405" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A405" s="11" t="s">
         <v>393</v>
       </c>
       <c r="B405" s="1"/>
       <c r="C405" s="1"/>
     </row>
-    <row r="406" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A406" s="11" t="s">
         <v>394</v>
       </c>
       <c r="B406" s="1"/>
       <c r="C406" s="1"/>
     </row>
-    <row r="407" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A407" s="11" t="s">
         <v>395</v>
       </c>
       <c r="B407" s="1"/>
       <c r="C407" s="1"/>
     </row>
-    <row r="408" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A408" s="11" t="s">
         <v>396</v>
       </c>
       <c r="B408" s="1"/>
       <c r="C408" s="1"/>
     </row>
-    <row r="409" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A409" s="11" t="s">
         <v>397</v>
       </c>
       <c r="B409" s="1"/>
       <c r="C409" s="1"/>
     </row>
-    <row r="410" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A410" s="11" t="s">
         <v>398</v>
       </c>
       <c r="B410" s="1"/>
       <c r="C410" s="1"/>
     </row>
-    <row r="411" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A411" s="11" t="s">
         <v>399</v>
       </c>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
     </row>
-    <row r="412" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A412" s="11" t="s">
         <v>400</v>
       </c>
       <c r="B412" s="1"/>
       <c r="C412" s="1"/>
     </row>
-    <row r="413" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A413" s="11" t="s">
         <v>401</v>
       </c>
       <c r="B413" s="1"/>
       <c r="C413" s="1"/>
     </row>
-    <row r="414" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A414" s="11" t="s">
         <v>402</v>
       </c>
       <c r="B414" s="1"/>
       <c r="C414" s="1"/>
     </row>
-    <row r="415" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A415" s="11" t="s">
         <v>403</v>
       </c>
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
     </row>
-    <row r="416" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A416" s="11" t="s">
         <v>404</v>
       </c>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
     </row>
-    <row r="417" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A417" s="11" t="s">
         <v>405</v>
       </c>
       <c r="B417" s="1"/>
       <c r="C417" s="1"/>
     </row>
-    <row r="418" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A418" s="11" t="s">
         <v>406</v>
       </c>
       <c r="B418" s="1"/>
       <c r="C418" s="8"/>
     </row>
-    <row r="419" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A419" s="11" t="s">
         <v>407</v>
       </c>
@@ -63547,70 +63534,70 @@
         <v>1</v>
       </c>
     </row>
-    <row r="420" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A420" s="11" t="s">
         <v>408</v>
       </c>
       <c r="B420" s="1"/>
       <c r="C420" s="1"/>
     </row>
-    <row r="421" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A421" s="11" t="s">
         <v>409</v>
       </c>
       <c r="B421" s="1"/>
       <c r="C421" s="1"/>
     </row>
-    <row r="422" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A422" s="11" t="s">
         <v>410</v>
       </c>
       <c r="B422" s="1"/>
       <c r="C422" s="1"/>
     </row>
-    <row r="423" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A423" s="11" t="s">
         <v>411</v>
       </c>
       <c r="B423" s="1"/>
       <c r="C423" s="1"/>
     </row>
-    <row r="424" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A424" s="11" t="s">
         <v>412</v>
       </c>
       <c r="B424" s="1"/>
       <c r="C424" s="1"/>
     </row>
-    <row r="425" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A425" s="11" t="s">
         <v>413</v>
       </c>
       <c r="B425" s="1"/>
       <c r="C425" s="1"/>
     </row>
-    <row r="426" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A426" s="11" t="s">
         <v>414</v>
       </c>
       <c r="B426" s="1"/>
       <c r="C426" s="1"/>
     </row>
-    <row r="427" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A427" s="11" t="s">
         <v>415</v>
       </c>
       <c r="B427" s="1"/>
       <c r="C427" s="1"/>
     </row>
-    <row r="428" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A428" s="11" t="s">
         <v>416</v>
       </c>
       <c r="B428" s="1"/>
       <c r="C428" s="8"/>
     </row>
-    <row r="429" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A429" s="11" t="s">
         <v>417</v>
       </c>
@@ -63619,7 +63606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="430" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A430" s="11" t="s">
         <v>418</v>
       </c>
@@ -63628,14 +63615,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="431" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A431" s="11" t="s">
         <v>419</v>
       </c>
       <c r="B431" s="8"/>
       <c r="C431" s="8"/>
     </row>
-    <row r="432" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A432" s="11" t="s">
         <v>420</v>
       </c>
@@ -63646,7 +63633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="433" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A433" s="11" t="s">
         <v>421</v>
       </c>
@@ -63655,21 +63642,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="434" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A434" s="11" t="s">
         <v>422</v>
       </c>
       <c r="B434" s="1"/>
       <c r="C434" s="1"/>
     </row>
-    <row r="435" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A435" s="11" t="s">
         <v>423</v>
       </c>
       <c r="B435" s="8"/>
       <c r="C435" s="8"/>
     </row>
-    <row r="436" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A436" s="11" t="s">
         <v>424</v>
       </c>
@@ -63680,28 +63667,28 @@
         <v>1</v>
       </c>
     </row>
-    <row r="437" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A437" s="11" t="s">
         <v>425</v>
       </c>
       <c r="B437" s="1"/>
       <c r="C437" s="1"/>
     </row>
-    <row r="438" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A438" s="11" t="s">
         <v>426</v>
       </c>
       <c r="B438" s="1"/>
       <c r="C438" s="1"/>
     </row>
-    <row r="439" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A439" s="11" t="s">
         <v>427</v>
       </c>
       <c r="B439" s="8"/>
       <c r="C439" s="1"/>
     </row>
-    <row r="440" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A440" s="11" t="s">
         <v>428</v>
       </c>
@@ -63710,56 +63697,56 @@
       </c>
       <c r="C440" s="1"/>
     </row>
-    <row r="441" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A441" s="11" t="s">
         <v>429</v>
       </c>
       <c r="B441" s="1"/>
       <c r="C441" s="1"/>
     </row>
-    <row r="442" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A442" s="11" t="s">
         <v>430</v>
       </c>
       <c r="B442" s="1"/>
       <c r="C442" s="1"/>
     </row>
-    <row r="443" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A443" s="11" t="s">
         <v>431</v>
       </c>
       <c r="B443" s="1"/>
       <c r="C443" s="1"/>
     </row>
-    <row r="444" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A444" s="11" t="s">
         <v>432</v>
       </c>
       <c r="B444" s="1"/>
       <c r="C444" s="1"/>
     </row>
-    <row r="445" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A445" s="11" t="s">
         <v>433</v>
       </c>
       <c r="B445" s="1"/>
       <c r="C445" s="1"/>
     </row>
-    <row r="446" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A446" s="11" t="s">
         <v>434</v>
       </c>
       <c r="B446" s="1"/>
       <c r="C446" s="1"/>
     </row>
-    <row r="447" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A447" s="11" t="s">
         <v>435</v>
       </c>
       <c r="B447" s="8"/>
       <c r="C447" s="1"/>
     </row>
-    <row r="448" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A448" s="11" t="s">
         <v>436</v>
       </c>
@@ -63768,7 +63755,7 @@
       </c>
       <c r="C448" s="1"/>
     </row>
-    <row r="449" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A449" s="11" t="s">
         <v>437</v>
       </c>
@@ -63777,7 +63764,7 @@
       </c>
       <c r="C449" s="1"/>
     </row>
-    <row r="450" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A450" s="11" t="s">
         <v>438</v>
       </c>
@@ -63786,7 +63773,7 @@
       </c>
       <c r="C450" s="1"/>
     </row>
-    <row r="451" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A451" s="11" t="s">
         <v>439</v>
       </c>
@@ -63795,7 +63782,7 @@
       </c>
       <c r="C451" s="1"/>
     </row>
-    <row r="452" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A452" s="11" t="s">
         <v>440</v>
       </c>
@@ -63804,7 +63791,7 @@
       </c>
       <c r="C452" s="1"/>
     </row>
-    <row r="453" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A453" s="11" t="s">
         <v>441</v>
       </c>
@@ -63813,7 +63800,7 @@
       </c>
       <c r="C453" s="1"/>
     </row>
-    <row r="454" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A454" s="11" t="s">
         <v>442</v>
       </c>
@@ -63822,21 +63809,21 @@
       </c>
       <c r="C454" s="1"/>
     </row>
-    <row r="455" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A455" s="11" t="s">
         <v>443</v>
       </c>
       <c r="B455" s="1"/>
       <c r="C455" s="1"/>
     </row>
-    <row r="456" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A456" s="11" t="s">
         <v>444</v>
       </c>
       <c r="B456" s="8"/>
       <c r="C456" s="1"/>
     </row>
-    <row r="457" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A457" s="11" t="s">
         <v>445</v>
       </c>
@@ -63845,7 +63832,7 @@
       </c>
       <c r="C457" s="1"/>
     </row>
-    <row r="458" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A458" s="11" t="s">
         <v>446</v>
       </c>
@@ -63854,7 +63841,7 @@
       </c>
       <c r="C458" s="1"/>
     </row>
-    <row r="459" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A459" s="11" t="s">
         <v>447</v>
       </c>
@@ -63863,7 +63850,7 @@
       </c>
       <c r="C459" s="1"/>
     </row>
-    <row r="460" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A460" s="11" t="s">
         <v>448</v>
       </c>
@@ -63872,7 +63859,7 @@
       </c>
       <c r="C460" s="1"/>
     </row>
-    <row r="461" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A461" s="11" t="s">
         <v>449</v>
       </c>
@@ -63881,7 +63868,7 @@
       </c>
       <c r="C461" s="1"/>
     </row>
-    <row r="462" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A462" s="11" t="s">
         <v>450</v>
       </c>
@@ -63890,7 +63877,7 @@
       </c>
       <c r="C462" s="1"/>
     </row>
-    <row r="463" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A463" s="11" t="s">
         <v>451</v>
       </c>
@@ -63899,35 +63886,35 @@
       </c>
       <c r="C463" s="1"/>
     </row>
-    <row r="464" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A464" s="11" t="s">
         <v>452</v>
       </c>
       <c r="B464" s="1"/>
       <c r="C464" s="1"/>
     </row>
-    <row r="465" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A465" s="11" t="s">
         <v>453</v>
       </c>
       <c r="B465" s="1"/>
       <c r="C465" s="1"/>
     </row>
-    <row r="466" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A466" s="11" t="s">
         <v>454</v>
       </c>
       <c r="B466" s="1"/>
       <c r="C466" s="1"/>
     </row>
-    <row r="467" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A467" s="11" t="s">
         <v>455</v>
       </c>
       <c r="B467" s="8"/>
       <c r="C467" s="1"/>
     </row>
-    <row r="468" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A468" s="11" t="s">
         <v>456</v>
       </c>
@@ -63936,7 +63923,7 @@
       </c>
       <c r="C468" s="1"/>
     </row>
-    <row r="469" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A469" s="11" t="s">
         <v>457</v>
       </c>
@@ -63945,7 +63932,7 @@
       </c>
       <c r="C469" s="1"/>
     </row>
-    <row r="470" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A470" s="11" t="s">
         <v>458</v>
       </c>
@@ -63954,7 +63941,7 @@
       </c>
       <c r="C470" s="1"/>
     </row>
-    <row r="471" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A471" s="11" t="s">
         <v>459</v>
       </c>
@@ -63963,7 +63950,7 @@
       </c>
       <c r="C471" s="1"/>
     </row>
-    <row r="472" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A472" s="11" t="s">
         <v>460</v>
       </c>
@@ -63972,21 +63959,21 @@
       </c>
       <c r="C472" s="1"/>
     </row>
-    <row r="473" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A473" s="11" t="s">
         <v>461</v>
       </c>
       <c r="B473" s="1"/>
       <c r="C473" s="1"/>
     </row>
-    <row r="474" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A474" s="11" t="s">
         <v>462</v>
       </c>
       <c r="B474" s="8"/>
       <c r="C474" s="1"/>
     </row>
-    <row r="475" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A475" s="11" t="s">
         <v>463</v>
       </c>
@@ -63995,7 +63982,7 @@
       </c>
       <c r="C475" s="1"/>
     </row>
-    <row r="476" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A476" s="11" t="s">
         <v>464</v>
       </c>
@@ -64004,7 +63991,7 @@
       </c>
       <c r="C476" s="1"/>
     </row>
-    <row r="477" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A477" s="11" t="s">
         <v>465</v>
       </c>
@@ -64013,7 +64000,7 @@
       </c>
       <c r="C477" s="1"/>
     </row>
-    <row r="478" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A478" s="11" t="s">
         <v>466</v>
       </c>
@@ -64022,7 +64009,7 @@
       </c>
       <c r="C478" s="1"/>
     </row>
-    <row r="479" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A479" s="11" t="s">
         <v>467</v>
       </c>
@@ -64031,49 +64018,49 @@
       </c>
       <c r="C479" s="1"/>
     </row>
-    <row r="480" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A480" s="11" t="s">
         <v>468</v>
       </c>
       <c r="B480" s="1"/>
       <c r="C480" s="1"/>
     </row>
-    <row r="481" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A481" s="11" t="s">
         <v>469</v>
       </c>
       <c r="B481" s="1"/>
       <c r="C481" s="1"/>
     </row>
-    <row r="482" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A482" s="11" t="s">
         <v>642</v>
       </c>
       <c r="B482" s="1"/>
       <c r="C482" s="1"/>
     </row>
-    <row r="483" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A483" s="11" t="s">
         <v>470</v>
       </c>
       <c r="B483" s="1"/>
       <c r="C483" s="1"/>
     </row>
-    <row r="484" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A484" s="11" t="s">
         <v>471</v>
       </c>
       <c r="B484" s="1"/>
       <c r="C484" s="1"/>
     </row>
-    <row r="485" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A485" s="11" t="s">
         <v>472</v>
       </c>
       <c r="B485" s="8"/>
       <c r="C485" s="1"/>
     </row>
-    <row r="486" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A486" s="11" t="s">
         <v>473</v>
       </c>
@@ -64082,7 +64069,7 @@
       </c>
       <c r="C486" s="1"/>
     </row>
-    <row r="487" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A487" s="11" t="s">
         <v>474</v>
       </c>
@@ -64091,7 +64078,7 @@
       </c>
       <c r="C487" s="1"/>
     </row>
-    <row r="488" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A488" s="11" t="s">
         <v>475</v>
       </c>
@@ -64100,7 +64087,7 @@
       </c>
       <c r="C488" s="1"/>
     </row>
-    <row r="489" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A489" s="11" t="s">
         <v>476</v>
       </c>
@@ -64109,7 +64096,7 @@
       </c>
       <c r="C489" s="1"/>
     </row>
-    <row r="490" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A490" s="11" t="s">
         <v>477</v>
       </c>
@@ -64118,21 +64105,21 @@
       </c>
       <c r="C490" s="1"/>
     </row>
-    <row r="491" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A491" s="11" t="s">
         <v>478</v>
       </c>
       <c r="B491" s="1"/>
       <c r="C491" s="1"/>
     </row>
-    <row r="492" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A492" s="11" t="s">
         <v>479</v>
       </c>
       <c r="B492" s="8"/>
       <c r="C492" s="1"/>
     </row>
-    <row r="493" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A493" s="11" t="s">
         <v>480</v>
       </c>
@@ -64141,7 +64128,7 @@
       </c>
       <c r="C493" s="1"/>
     </row>
-    <row r="494" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A494" s="11" t="s">
         <v>481</v>
       </c>
@@ -64150,7 +64137,7 @@
       </c>
       <c r="C494" s="1"/>
     </row>
-    <row r="495" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A495" s="11" t="s">
         <v>482</v>
       </c>
@@ -64159,7 +64146,7 @@
       </c>
       <c r="C495" s="1"/>
     </row>
-    <row r="496" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A496" s="11" t="s">
         <v>483</v>
       </c>
@@ -64168,7 +64155,7 @@
       </c>
       <c r="C496" s="1"/>
     </row>
-    <row r="497" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A497" s="11" t="s">
         <v>484</v>
       </c>
@@ -64177,35 +64164,35 @@
       </c>
       <c r="C497" s="1"/>
     </row>
-    <row r="498" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A498" s="11" t="s">
         <v>643</v>
       </c>
       <c r="B498" s="1"/>
       <c r="C498" s="1"/>
     </row>
-    <row r="499" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A499" s="11" t="s">
         <v>485</v>
       </c>
       <c r="B499" s="1"/>
       <c r="C499" s="1"/>
     </row>
-    <row r="500" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A500" s="11" t="s">
         <v>486</v>
       </c>
       <c r="B500" s="1"/>
       <c r="C500" s="1"/>
     </row>
-    <row r="501" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A501" s="11" t="s">
         <v>487</v>
       </c>
       <c r="B501" s="8"/>
       <c r="C501" s="1"/>
     </row>
-    <row r="502" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A502" s="11" t="s">
         <v>488</v>
       </c>
@@ -64214,7 +64201,7 @@
       </c>
       <c r="C502" s="1"/>
     </row>
-    <row r="503" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A503" s="11" t="s">
         <v>489</v>
       </c>
@@ -64223,7 +64210,7 @@
       </c>
       <c r="C503" s="1"/>
     </row>
-    <row r="504" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A504" s="11" t="s">
         <v>490</v>
       </c>
@@ -64232,7 +64219,7 @@
       </c>
       <c r="C504" s="1"/>
     </row>
-    <row r="505" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A505" s="11" t="s">
         <v>491</v>
       </c>
@@ -64241,21 +64228,21 @@
       </c>
       <c r="C505" s="1"/>
     </row>
-    <row r="506" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A506" s="11" t="s">
         <v>492</v>
       </c>
       <c r="B506" s="1"/>
       <c r="C506" s="1"/>
     </row>
-    <row r="507" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A507" s="11" t="s">
         <v>493</v>
       </c>
       <c r="B507" s="8"/>
       <c r="C507" s="1"/>
     </row>
-    <row r="508" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A508" s="11" t="s">
         <v>494</v>
       </c>
@@ -64264,7 +64251,7 @@
       </c>
       <c r="C508" s="1"/>
     </row>
-    <row r="509" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A509" s="11" t="s">
         <v>495</v>
       </c>
@@ -64273,7 +64260,7 @@
       </c>
       <c r="C509" s="1"/>
     </row>
-    <row r="510" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A510" s="11" t="s">
         <v>496</v>
       </c>
@@ -64282,7 +64269,7 @@
       </c>
       <c r="C510" s="1"/>
     </row>
-    <row r="511" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A511" s="11" t="s">
         <v>497</v>
       </c>
@@ -64291,35 +64278,35 @@
       </c>
       <c r="C511" s="1"/>
     </row>
-    <row r="512" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A512" s="11" t="s">
         <v>498</v>
       </c>
       <c r="B512" s="1"/>
       <c r="C512" s="1"/>
     </row>
-    <row r="513" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A513" s="11" t="s">
         <v>499</v>
       </c>
       <c r="B513" s="1"/>
       <c r="C513" s="1"/>
     </row>
-    <row r="514" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A514" s="11" t="s">
         <v>500</v>
       </c>
       <c r="B514" s="1"/>
       <c r="C514" s="1"/>
     </row>
-    <row r="515" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A515" s="11" t="s">
         <v>501</v>
       </c>
       <c r="B515" s="8"/>
       <c r="C515" s="1"/>
     </row>
-    <row r="516" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A516" s="11" t="s">
         <v>502</v>
       </c>
@@ -64328,7 +64315,7 @@
       </c>
       <c r="C516" s="1"/>
     </row>
-    <row r="517" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A517" s="11" t="s">
         <v>503</v>
       </c>
@@ -64337,7 +64324,7 @@
       </c>
       <c r="C517" s="1"/>
     </row>
-    <row r="518" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A518" s="11" t="s">
         <v>504</v>
       </c>
@@ -64346,7 +64333,7 @@
       </c>
       <c r="C518" s="1"/>
     </row>
-    <row r="519" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A519" s="11" t="s">
         <v>505</v>
       </c>
@@ -64355,7 +64342,7 @@
       </c>
       <c r="C519" s="1"/>
     </row>
-    <row r="520" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A520" s="11" t="s">
         <v>506</v>
       </c>
@@ -64364,21 +64351,21 @@
       </c>
       <c r="C520" s="1"/>
     </row>
-    <row r="521" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A521" s="11" t="s">
         <v>507</v>
       </c>
       <c r="B521" s="1"/>
       <c r="C521" s="1"/>
     </row>
-    <row r="522" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A522" s="11" t="s">
         <v>508</v>
       </c>
       <c r="B522" s="8"/>
       <c r="C522" s="1"/>
     </row>
-    <row r="523" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A523" s="11" t="s">
         <v>509</v>
       </c>
@@ -64387,7 +64374,7 @@
       </c>
       <c r="C523" s="1"/>
     </row>
-    <row r="524" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A524" s="11" t="s">
         <v>510</v>
       </c>
@@ -64396,7 +64383,7 @@
       </c>
       <c r="C524" s="1"/>
     </row>
-    <row r="525" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A525" s="11" t="s">
         <v>511</v>
       </c>
@@ -64405,7 +64392,7 @@
       </c>
       <c r="C525" s="1"/>
     </row>
-    <row r="526" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A526" s="11" t="s">
         <v>512</v>
       </c>
@@ -64414,7 +64401,7 @@
       </c>
       <c r="C526" s="1"/>
     </row>
-    <row r="527" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A527" s="11" t="s">
         <v>513</v>
       </c>
@@ -64423,2377 +64410,2377 @@
       </c>
       <c r="C527" s="1"/>
     </row>
-    <row r="528" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A528" s="5"/>
       <c r="B528" s="1"/>
       <c r="C528" s="1"/>
     </row>
-    <row r="529" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A529" s="5"/>
       <c r="B529" s="1"/>
       <c r="C529" s="1"/>
     </row>
-    <row r="530" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A530" s="5"/>
       <c r="B530" s="1"/>
       <c r="C530" s="1"/>
     </row>
-    <row r="531" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A531" s="5"/>
       <c r="B531" s="1"/>
       <c r="C531" s="1"/>
     </row>
-    <row r="532" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A532" s="5"/>
       <c r="B532" s="1"/>
       <c r="C532" s="1"/>
     </row>
-    <row r="533" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A533" s="5"/>
       <c r="B533" s="1"/>
       <c r="C533" s="1"/>
     </row>
-    <row r="534" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A534" s="5"/>
       <c r="B534" s="1"/>
       <c r="C534" s="1"/>
     </row>
-    <row r="535" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A535" s="5"/>
       <c r="B535" s="1"/>
       <c r="C535" s="1"/>
     </row>
-    <row r="536" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A536" s="5"/>
       <c r="B536" s="1"/>
       <c r="C536" s="1"/>
     </row>
-    <row r="537" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A537" s="5"/>
       <c r="B537" s="1"/>
       <c r="C537" s="1"/>
     </row>
-    <row r="538" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A538" s="5"/>
       <c r="B538" s="1"/>
       <c r="C538" s="1"/>
     </row>
-    <row r="539" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A539" s="5"/>
       <c r="B539" s="1"/>
       <c r="C539" s="1"/>
     </row>
-    <row r="540" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A540" s="5"/>
       <c r="B540" s="1"/>
       <c r="C540" s="1"/>
     </row>
-    <row r="541" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A541" s="5"/>
       <c r="B541" s="1"/>
       <c r="C541" s="1"/>
     </row>
-    <row r="542" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A542" s="5"/>
       <c r="B542" s="1"/>
       <c r="C542" s="1"/>
     </row>
-    <row r="543" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A543" s="5"/>
       <c r="B543" s="1"/>
       <c r="C543" s="1"/>
     </row>
-    <row r="544" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A544" s="5"/>
       <c r="B544" s="1"/>
       <c r="C544" s="1"/>
     </row>
-    <row r="545" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A545" s="5"/>
       <c r="B545" s="1"/>
       <c r="C545" s="1"/>
     </row>
-    <row r="546" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A546" s="5"/>
       <c r="B546" s="1"/>
       <c r="C546" s="1"/>
     </row>
-    <row r="547" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A547" s="5"/>
       <c r="B547" s="1"/>
       <c r="C547" s="1"/>
     </row>
-    <row r="548" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A548" s="5"/>
       <c r="B548" s="1"/>
       <c r="C548" s="1"/>
     </row>
-    <row r="549" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A549" s="5"/>
       <c r="B549" s="1"/>
       <c r="C549" s="1"/>
     </row>
-    <row r="550" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A550" s="5"/>
       <c r="B550" s="1"/>
       <c r="C550" s="1"/>
     </row>
-    <row r="551" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A551" s="5"/>
       <c r="B551" s="1"/>
       <c r="C551" s="1"/>
     </row>
-    <row r="552" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A552" s="5"/>
       <c r="B552" s="1"/>
       <c r="C552" s="1"/>
     </row>
-    <row r="553" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A553" s="5"/>
       <c r="B553" s="1"/>
       <c r="C553" s="1"/>
     </row>
-    <row r="554" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A554" s="5"/>
       <c r="B554" s="1"/>
       <c r="C554" s="1"/>
     </row>
-    <row r="555" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A555" s="5"/>
       <c r="B555" s="1"/>
       <c r="C555" s="1"/>
     </row>
-    <row r="556" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A556" s="5"/>
       <c r="B556" s="1"/>
       <c r="C556" s="1"/>
     </row>
-    <row r="557" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A557" s="5"/>
       <c r="B557" s="1"/>
       <c r="C557" s="1"/>
     </row>
-    <row r="558" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A558" s="5"/>
       <c r="B558" s="1"/>
       <c r="C558" s="1"/>
     </row>
-    <row r="559" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A559" s="5"/>
       <c r="B559" s="1"/>
       <c r="C559" s="1"/>
     </row>
-    <row r="560" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A560" s="5"/>
       <c r="B560" s="1"/>
       <c r="C560" s="1"/>
     </row>
-    <row r="561" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A561" s="5"/>
       <c r="B561" s="1"/>
       <c r="C561" s="1"/>
     </row>
-    <row r="562" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A562" s="5"/>
       <c r="B562" s="1"/>
       <c r="C562" s="1"/>
     </row>
-    <row r="563" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A563" s="5"/>
       <c r="B563" s="1"/>
       <c r="C563" s="1"/>
     </row>
-    <row r="564" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A564" s="5"/>
       <c r="B564" s="1"/>
       <c r="C564" s="1"/>
     </row>
-    <row r="565" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A565" s="5"/>
       <c r="B565" s="1"/>
       <c r="C565" s="1"/>
     </row>
-    <row r="566" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A566" s="5"/>
       <c r="B566" s="1"/>
       <c r="C566" s="1"/>
     </row>
-    <row r="567" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A567" s="5"/>
       <c r="B567" s="1"/>
       <c r="C567" s="1"/>
     </row>
-    <row r="568" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A568" s="5"/>
       <c r="B568" s="1"/>
       <c r="C568" s="1"/>
     </row>
-    <row r="569" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A569" s="5"/>
       <c r="B569" s="1"/>
       <c r="C569" s="1"/>
     </row>
-    <row r="570" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A570" s="5"/>
       <c r="B570" s="1"/>
       <c r="C570" s="1"/>
     </row>
-    <row r="571" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A571" s="5"/>
       <c r="B571" s="1"/>
       <c r="C571" s="1"/>
     </row>
-    <row r="572" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A572" s="5"/>
       <c r="B572" s="1"/>
       <c r="C572" s="1"/>
     </row>
-    <row r="573" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A573" s="5"/>
       <c r="B573" s="1"/>
       <c r="C573" s="1"/>
     </row>
-    <row r="574" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A574" s="5"/>
       <c r="B574" s="1"/>
       <c r="C574" s="1"/>
     </row>
-    <row r="575" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A575" s="5"/>
       <c r="B575" s="1"/>
       <c r="C575" s="1"/>
     </row>
-    <row r="576" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A576" s="5"/>
       <c r="B576" s="1"/>
       <c r="C576" s="1"/>
     </row>
-    <row r="577" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A577" s="5"/>
       <c r="B577" s="1"/>
       <c r="C577" s="1"/>
     </row>
-    <row r="578" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A578" s="5"/>
       <c r="B578" s="1"/>
       <c r="C578" s="1"/>
     </row>
-    <row r="579" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A579" s="5"/>
       <c r="B579" s="1"/>
       <c r="C579" s="1"/>
     </row>
-    <row r="580" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A580" s="5"/>
       <c r="B580" s="1"/>
       <c r="C580" s="1"/>
     </row>
-    <row r="581" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A581" s="5"/>
       <c r="B581" s="1"/>
       <c r="C581" s="1"/>
     </row>
-    <row r="582" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A582" s="5"/>
       <c r="B582" s="1"/>
       <c r="C582" s="1"/>
     </row>
-    <row r="583" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A583" s="5"/>
       <c r="B583" s="1"/>
       <c r="C583" s="1"/>
     </row>
-    <row r="584" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A584" s="5"/>
       <c r="B584" s="1"/>
       <c r="C584" s="1"/>
     </row>
-    <row r="585" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A585" s="5"/>
       <c r="B585" s="1"/>
       <c r="C585" s="1"/>
     </row>
-    <row r="586" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A586" s="5"/>
       <c r="B586" s="1"/>
       <c r="C586" s="1"/>
     </row>
-    <row r="587" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A587" s="5"/>
       <c r="B587" s="1"/>
       <c r="C587" s="1"/>
     </row>
-    <row r="588" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A588" s="5"/>
       <c r="B588" s="1"/>
       <c r="C588" s="1"/>
     </row>
-    <row r="589" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A589" s="5"/>
       <c r="B589" s="1"/>
       <c r="C589" s="1"/>
     </row>
-    <row r="590" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A590" s="5"/>
       <c r="B590" s="1"/>
       <c r="C590" s="1"/>
     </row>
-    <row r="591" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A591" s="5"/>
       <c r="B591" s="1"/>
       <c r="C591" s="1"/>
     </row>
-    <row r="592" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A592" s="5"/>
       <c r="B592" s="1"/>
       <c r="C592" s="1"/>
     </row>
-    <row r="593" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A593" s="5"/>
       <c r="B593" s="1"/>
       <c r="C593" s="1"/>
     </row>
-    <row r="594" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A594" s="5"/>
       <c r="B594" s="1"/>
       <c r="C594" s="1"/>
     </row>
-    <row r="595" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A595" s="5"/>
       <c r="B595" s="1"/>
       <c r="C595" s="1"/>
     </row>
-    <row r="596" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A596" s="5"/>
       <c r="B596" s="1"/>
       <c r="C596" s="1"/>
     </row>
-    <row r="597" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A597" s="5"/>
       <c r="B597" s="1"/>
       <c r="C597" s="1"/>
     </row>
-    <row r="598" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A598" s="5"/>
       <c r="B598" s="1"/>
       <c r="C598" s="1"/>
     </row>
-    <row r="599" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A599" s="5"/>
       <c r="B599" s="1"/>
       <c r="C599" s="1"/>
     </row>
-    <row r="600" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A600" s="5"/>
       <c r="B600" s="1"/>
       <c r="C600" s="1"/>
     </row>
-    <row r="601" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A601" s="5"/>
       <c r="B601" s="1"/>
       <c r="C601" s="1"/>
     </row>
-    <row r="602" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A602" s="5"/>
       <c r="B602" s="1"/>
       <c r="C602" s="1"/>
     </row>
-    <row r="603" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A603" s="5"/>
       <c r="B603" s="1"/>
       <c r="C603" s="1"/>
     </row>
-    <row r="604" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A604" s="5"/>
       <c r="B604" s="1"/>
       <c r="C604" s="1"/>
     </row>
-    <row r="605" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A605" s="5"/>
       <c r="B605" s="1"/>
       <c r="C605" s="1"/>
     </row>
-    <row r="606" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A606" s="5"/>
       <c r="B606" s="1"/>
       <c r="C606" s="1"/>
     </row>
-    <row r="607" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A607" s="5"/>
       <c r="B607" s="1"/>
       <c r="C607" s="1"/>
     </row>
-    <row r="608" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A608" s="5"/>
       <c r="B608" s="1"/>
       <c r="C608" s="1"/>
     </row>
-    <row r="609" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A609" s="5"/>
       <c r="B609" s="1"/>
       <c r="C609" s="1"/>
     </row>
-    <row r="610" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A610" s="5"/>
       <c r="B610" s="1"/>
       <c r="C610" s="1"/>
     </row>
-    <row r="611" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A611" s="5"/>
       <c r="B611" s="1"/>
       <c r="C611" s="1"/>
     </row>
-    <row r="612" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A612" s="5"/>
       <c r="B612" s="1"/>
       <c r="C612" s="1"/>
     </row>
-    <row r="613" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A613" s="5"/>
       <c r="B613" s="1"/>
       <c r="C613" s="1"/>
     </row>
-    <row r="614" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A614" s="5"/>
       <c r="B614" s="1"/>
       <c r="C614" s="1"/>
     </row>
-    <row r="615" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A615" s="5"/>
       <c r="B615" s="1"/>
       <c r="C615" s="1"/>
     </row>
-    <row r="616" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A616" s="5"/>
       <c r="B616" s="1"/>
       <c r="C616" s="1"/>
     </row>
-    <row r="617" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A617" s="5"/>
       <c r="B617" s="1"/>
       <c r="C617" s="1"/>
     </row>
-    <row r="618" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A618" s="5"/>
       <c r="B618" s="1"/>
       <c r="C618" s="1"/>
     </row>
-    <row r="619" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A619" s="5"/>
       <c r="B619" s="1"/>
       <c r="C619" s="1"/>
     </row>
-    <row r="620" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A620" s="5"/>
       <c r="B620" s="1"/>
       <c r="C620" s="1"/>
     </row>
-    <row r="621" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A621" s="5"/>
       <c r="B621" s="1"/>
       <c r="C621" s="1"/>
     </row>
-    <row r="622" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A622" s="5"/>
       <c r="B622" s="1"/>
       <c r="C622" s="1"/>
     </row>
-    <row r="623" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A623" s="5"/>
       <c r="B623" s="1"/>
       <c r="C623" s="1"/>
     </row>
-    <row r="624" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A624" s="5"/>
       <c r="B624" s="1"/>
       <c r="C624" s="1"/>
     </row>
-    <row r="625" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A625" s="5"/>
       <c r="B625" s="1"/>
       <c r="C625" s="1"/>
     </row>
-    <row r="626" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A626" s="5"/>
       <c r="B626" s="1"/>
       <c r="C626" s="1"/>
     </row>
-    <row r="627" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A627" s="5"/>
       <c r="B627" s="1"/>
       <c r="C627" s="1"/>
     </row>
-    <row r="628" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A628" s="5"/>
       <c r="B628" s="1"/>
       <c r="C628" s="1"/>
     </row>
-    <row r="629" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A629" s="5"/>
       <c r="B629" s="1"/>
       <c r="C629" s="1"/>
     </row>
-    <row r="630" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A630" s="5"/>
       <c r="B630" s="1"/>
       <c r="C630" s="1"/>
     </row>
-    <row r="631" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A631" s="5"/>
       <c r="B631" s="1"/>
       <c r="C631" s="1"/>
     </row>
-    <row r="632" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A632" s="5"/>
       <c r="B632" s="1"/>
       <c r="C632" s="1"/>
     </row>
-    <row r="633" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A633" s="5"/>
       <c r="B633" s="1"/>
       <c r="C633" s="1"/>
     </row>
-    <row r="634" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A634" s="5"/>
       <c r="B634" s="1"/>
       <c r="C634" s="1"/>
     </row>
-    <row r="635" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A635" s="5"/>
       <c r="B635" s="1"/>
       <c r="C635" s="1"/>
     </row>
-    <row r="636" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A636" s="5"/>
       <c r="B636" s="1"/>
       <c r="C636" s="1"/>
     </row>
-    <row r="637" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A637" s="5"/>
       <c r="B637" s="1"/>
       <c r="C637" s="1"/>
     </row>
-    <row r="638" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A638" s="5"/>
       <c r="B638" s="1"/>
       <c r="C638" s="1"/>
     </row>
-    <row r="639" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A639" s="5"/>
       <c r="B639" s="1"/>
       <c r="C639" s="1"/>
     </row>
-    <row r="640" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A640" s="5"/>
       <c r="B640" s="1"/>
       <c r="C640" s="1"/>
     </row>
-    <row r="641" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A641" s="5"/>
       <c r="B641" s="1"/>
       <c r="C641" s="1"/>
     </row>
-    <row r="642" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A642" s="5"/>
       <c r="B642" s="1"/>
       <c r="C642" s="1"/>
     </row>
-    <row r="643" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A643" s="5"/>
       <c r="B643" s="1"/>
       <c r="C643" s="1"/>
     </row>
-    <row r="644" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A644" s="5"/>
       <c r="B644" s="1"/>
       <c r="C644" s="1"/>
     </row>
-    <row r="645" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A645" s="5"/>
       <c r="B645" s="1"/>
       <c r="C645" s="1"/>
     </row>
-    <row r="646" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A646" s="5"/>
       <c r="B646" s="1"/>
       <c r="C646" s="1"/>
     </row>
-    <row r="647" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A647" s="5"/>
       <c r="B647" s="1"/>
       <c r="C647" s="1"/>
     </row>
-    <row r="648" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A648" s="5"/>
       <c r="B648" s="1"/>
       <c r="C648" s="1"/>
     </row>
-    <row r="649" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A649" s="5"/>
       <c r="B649" s="1"/>
       <c r="C649" s="1"/>
     </row>
-    <row r="650" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A650" s="5"/>
       <c r="B650" s="1"/>
       <c r="C650" s="1"/>
     </row>
-    <row r="651" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A651" s="5"/>
       <c r="B651" s="1"/>
       <c r="C651" s="1"/>
     </row>
-    <row r="652" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A652" s="5"/>
       <c r="B652" s="1"/>
       <c r="C652" s="1"/>
     </row>
-    <row r="653" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A653" s="5"/>
       <c r="B653" s="1"/>
       <c r="C653" s="1"/>
     </row>
-    <row r="654" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A654" s="5"/>
       <c r="B654" s="1"/>
       <c r="C654" s="1"/>
     </row>
-    <row r="655" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A655" s="5"/>
       <c r="B655" s="1"/>
       <c r="C655" s="1"/>
     </row>
-    <row r="656" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A656" s="5"/>
       <c r="B656" s="1"/>
       <c r="C656" s="1"/>
     </row>
-    <row r="657" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A657" s="5"/>
       <c r="B657" s="1"/>
       <c r="C657" s="1"/>
     </row>
-    <row r="658" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A658" s="5"/>
       <c r="B658" s="1"/>
       <c r="C658" s="1"/>
     </row>
-    <row r="659" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A659" s="5"/>
       <c r="B659" s="1"/>
       <c r="C659" s="1"/>
     </row>
-    <row r="660" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A660" s="5"/>
       <c r="B660" s="1"/>
       <c r="C660" s="1"/>
     </row>
-    <row r="661" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A661" s="5"/>
       <c r="B661" s="1"/>
       <c r="C661" s="1"/>
     </row>
-    <row r="662" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A662" s="5"/>
       <c r="B662" s="1"/>
       <c r="C662" s="1"/>
     </row>
-    <row r="663" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A663" s="5"/>
       <c r="B663" s="1"/>
       <c r="C663" s="1"/>
     </row>
-    <row r="664" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A664" s="5"/>
       <c r="B664" s="1"/>
       <c r="C664" s="1"/>
     </row>
-    <row r="665" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A665" s="5"/>
       <c r="B665" s="1"/>
       <c r="C665" s="1"/>
     </row>
-    <row r="666" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A666" s="5"/>
       <c r="B666" s="1"/>
       <c r="C666" s="1"/>
     </row>
-    <row r="667" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A667" s="5"/>
       <c r="B667" s="1"/>
       <c r="C667" s="1"/>
     </row>
-    <row r="668" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A668" s="5"/>
       <c r="B668" s="1"/>
       <c r="C668" s="1"/>
     </row>
-    <row r="669" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A669" s="5"/>
       <c r="B669" s="1"/>
       <c r="C669" s="1"/>
     </row>
-    <row r="670" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A670" s="5"/>
       <c r="B670" s="1"/>
       <c r="C670" s="1"/>
     </row>
-    <row r="671" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A671" s="5"/>
       <c r="B671" s="1"/>
       <c r="C671" s="1"/>
     </row>
-    <row r="672" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A672" s="5"/>
       <c r="B672" s="1"/>
       <c r="C672" s="1"/>
     </row>
-    <row r="673" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A673" s="5"/>
       <c r="B673" s="1"/>
       <c r="C673" s="1"/>
     </row>
-    <row r="674" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A674" s="5"/>
       <c r="B674" s="1"/>
       <c r="C674" s="1"/>
     </row>
-    <row r="675" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A675" s="5"/>
       <c r="B675" s="1"/>
       <c r="C675" s="1"/>
     </row>
-    <row r="676" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A676" s="5"/>
       <c r="B676" s="1"/>
       <c r="C676" s="1"/>
     </row>
-    <row r="677" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A677" s="5"/>
       <c r="B677" s="1"/>
       <c r="C677" s="1"/>
     </row>
-    <row r="678" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A678" s="5"/>
       <c r="B678" s="1"/>
       <c r="C678" s="1"/>
     </row>
-    <row r="679" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A679" s="5"/>
       <c r="B679" s="1"/>
       <c r="C679" s="1"/>
     </row>
-    <row r="680" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A680" s="5"/>
       <c r="B680" s="1"/>
       <c r="C680" s="1"/>
     </row>
-    <row r="681" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A681" s="5"/>
       <c r="B681" s="1"/>
       <c r="C681" s="1"/>
     </row>
-    <row r="682" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A682" s="5"/>
       <c r="B682" s="1"/>
       <c r="C682" s="1"/>
     </row>
-    <row r="683" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A683" s="5"/>
       <c r="B683" s="1"/>
       <c r="C683" s="1"/>
     </row>
-    <row r="684" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A684" s="5"/>
       <c r="B684" s="1"/>
       <c r="C684" s="1"/>
     </row>
-    <row r="685" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A685" s="5"/>
       <c r="B685" s="1"/>
       <c r="C685" s="1"/>
     </row>
-    <row r="686" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A686" s="5"/>
       <c r="B686" s="1"/>
       <c r="C686" s="1"/>
     </row>
-    <row r="687" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A687" s="5"/>
       <c r="B687" s="1"/>
       <c r="C687" s="1"/>
     </row>
-    <row r="688" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A688" s="5"/>
       <c r="B688" s="1"/>
       <c r="C688" s="1"/>
     </row>
-    <row r="689" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A689" s="5"/>
       <c r="B689" s="1"/>
       <c r="C689" s="1"/>
     </row>
-    <row r="690" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A690" s="5"/>
       <c r="B690" s="1"/>
       <c r="C690" s="1"/>
     </row>
-    <row r="691" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A691" s="5"/>
       <c r="B691" s="1"/>
       <c r="C691" s="1"/>
     </row>
-    <row r="692" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A692" s="5"/>
       <c r="B692" s="1"/>
       <c r="C692" s="1"/>
     </row>
-    <row r="693" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A693" s="5"/>
       <c r="B693" s="1"/>
       <c r="C693" s="1"/>
     </row>
-    <row r="694" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A694" s="5"/>
       <c r="B694" s="1"/>
       <c r="C694" s="1"/>
     </row>
-    <row r="695" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A695" s="5"/>
       <c r="B695" s="1"/>
       <c r="C695" s="1"/>
     </row>
-    <row r="696" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A696" s="5"/>
       <c r="B696" s="1"/>
       <c r="C696" s="1"/>
     </row>
-    <row r="697" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A697" s="5"/>
       <c r="B697" s="1"/>
       <c r="C697" s="1"/>
     </row>
-    <row r="698" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A698" s="5"/>
       <c r="B698" s="1"/>
       <c r="C698" s="1"/>
     </row>
-    <row r="699" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A699" s="5"/>
       <c r="B699" s="1"/>
       <c r="C699" s="1"/>
     </row>
-    <row r="700" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A700" s="5"/>
       <c r="B700" s="1"/>
       <c r="C700" s="1"/>
     </row>
-    <row r="701" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A701" s="5"/>
       <c r="B701" s="1"/>
       <c r="C701" s="1"/>
     </row>
-    <row r="702" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A702" s="5"/>
       <c r="B702" s="1"/>
       <c r="C702" s="1"/>
     </row>
-    <row r="703" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A703" s="5"/>
       <c r="B703" s="1"/>
       <c r="C703" s="1"/>
     </row>
-    <row r="704" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A704" s="5"/>
       <c r="B704" s="1"/>
       <c r="C704" s="1"/>
     </row>
-    <row r="705" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A705" s="5"/>
       <c r="B705" s="1"/>
       <c r="C705" s="1"/>
     </row>
-    <row r="706" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A706" s="5"/>
       <c r="B706" s="1"/>
       <c r="C706" s="1"/>
     </row>
-    <row r="707" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A707" s="5"/>
       <c r="B707" s="1"/>
       <c r="C707" s="1"/>
     </row>
-    <row r="708" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A708" s="5"/>
       <c r="B708" s="1"/>
       <c r="C708" s="1"/>
     </row>
-    <row r="709" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A709" s="5"/>
       <c r="B709" s="1"/>
       <c r="C709" s="1"/>
     </row>
-    <row r="710" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A710" s="5"/>
       <c r="B710" s="1"/>
       <c r="C710" s="1"/>
     </row>
-    <row r="711" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A711" s="5"/>
       <c r="B711" s="1"/>
       <c r="C711" s="1"/>
     </row>
-    <row r="712" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A712" s="5"/>
       <c r="B712" s="1"/>
       <c r="C712" s="1"/>
     </row>
-    <row r="713" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A713" s="5"/>
       <c r="B713" s="1"/>
       <c r="C713" s="1"/>
     </row>
-    <row r="714" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A714" s="5"/>
       <c r="B714" s="1"/>
       <c r="C714" s="1"/>
     </row>
-    <row r="715" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A715" s="5"/>
       <c r="B715" s="1"/>
       <c r="C715" s="1"/>
     </row>
-    <row r="716" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A716" s="5"/>
       <c r="B716" s="1"/>
       <c r="C716" s="1"/>
     </row>
-    <row r="717" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A717" s="5"/>
       <c r="B717" s="1"/>
       <c r="C717" s="1"/>
     </row>
-    <row r="718" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A718" s="5"/>
       <c r="B718" s="1"/>
       <c r="C718" s="1"/>
     </row>
-    <row r="719" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A719" s="5"/>
       <c r="B719" s="1"/>
       <c r="C719" s="1"/>
     </row>
-    <row r="720" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A720" s="5"/>
       <c r="B720" s="1"/>
       <c r="C720" s="1"/>
     </row>
-    <row r="721" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A721" s="5"/>
       <c r="B721" s="1"/>
       <c r="C721" s="1"/>
     </row>
-    <row r="722" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A722" s="5"/>
       <c r="B722" s="1"/>
       <c r="C722" s="1"/>
     </row>
-    <row r="723" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A723" s="5"/>
       <c r="B723" s="1"/>
       <c r="C723" s="1"/>
     </row>
-    <row r="724" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A724" s="5"/>
       <c r="B724" s="1"/>
       <c r="C724" s="1"/>
     </row>
-    <row r="725" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A725" s="5"/>
       <c r="B725" s="1"/>
       <c r="C725" s="1"/>
     </row>
-    <row r="726" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A726" s="5"/>
       <c r="B726" s="1"/>
       <c r="C726" s="1"/>
     </row>
-    <row r="727" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A727" s="5"/>
       <c r="B727" s="1"/>
       <c r="C727" s="1"/>
     </row>
-    <row r="728" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A728" s="5"/>
       <c r="B728" s="1"/>
       <c r="C728" s="1"/>
     </row>
-    <row r="729" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A729" s="5"/>
       <c r="B729" s="1"/>
       <c r="C729" s="1"/>
     </row>
-    <row r="730" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A730" s="5"/>
       <c r="B730" s="1"/>
       <c r="C730" s="1"/>
     </row>
-    <row r="731" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A731" s="5"/>
       <c r="B731" s="1"/>
       <c r="C731" s="1"/>
     </row>
-    <row r="732" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A732" s="5"/>
       <c r="B732" s="1"/>
       <c r="C732" s="1"/>
     </row>
-    <row r="733" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A733" s="5"/>
       <c r="B733" s="1"/>
       <c r="C733" s="1"/>
     </row>
-    <row r="734" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A734" s="5"/>
       <c r="B734" s="1"/>
       <c r="C734" s="1"/>
     </row>
-    <row r="735" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A735" s="5"/>
       <c r="B735" s="1"/>
       <c r="C735" s="1"/>
     </row>
-    <row r="736" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A736" s="5"/>
       <c r="B736" s="1"/>
       <c r="C736" s="1"/>
     </row>
-    <row r="737" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A737" s="5"/>
       <c r="B737" s="1"/>
       <c r="C737" s="1"/>
     </row>
-    <row r="738" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A738" s="5"/>
       <c r="B738" s="1"/>
       <c r="C738" s="1"/>
     </row>
-    <row r="739" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A739" s="5"/>
       <c r="B739" s="1"/>
       <c r="C739" s="1"/>
     </row>
-    <row r="740" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A740" s="5"/>
       <c r="B740" s="1"/>
       <c r="C740" s="1"/>
     </row>
-    <row r="741" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A741" s="5"/>
       <c r="B741" s="1"/>
       <c r="C741" s="1"/>
     </row>
-    <row r="742" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A742" s="5"/>
       <c r="B742" s="1"/>
       <c r="C742" s="1"/>
     </row>
-    <row r="743" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A743" s="5"/>
       <c r="B743" s="1"/>
       <c r="C743" s="1"/>
     </row>
-    <row r="744" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A744" s="5"/>
       <c r="B744" s="1"/>
       <c r="C744" s="1"/>
     </row>
-    <row r="745" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A745" s="5"/>
       <c r="B745" s="1"/>
       <c r="C745" s="1"/>
     </row>
-    <row r="746" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A746" s="5"/>
       <c r="B746" s="1"/>
       <c r="C746" s="1"/>
     </row>
-    <row r="747" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A747" s="5"/>
       <c r="B747" s="1"/>
       <c r="C747" s="1"/>
     </row>
-    <row r="748" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A748" s="5"/>
       <c r="B748" s="1"/>
       <c r="C748" s="1"/>
     </row>
-    <row r="749" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A749" s="5"/>
       <c r="B749" s="1"/>
       <c r="C749" s="1"/>
     </row>
-    <row r="750" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A750" s="5"/>
       <c r="B750" s="1"/>
       <c r="C750" s="1"/>
     </row>
-    <row r="751" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A751" s="5"/>
       <c r="B751" s="1"/>
       <c r="C751" s="1"/>
     </row>
-    <row r="752" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A752" s="5"/>
       <c r="B752" s="1"/>
       <c r="C752" s="1"/>
     </row>
-    <row r="753" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A753" s="5"/>
       <c r="B753" s="1"/>
       <c r="C753" s="1"/>
     </row>
-    <row r="754" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A754" s="5"/>
       <c r="B754" s="1"/>
       <c r="C754" s="1"/>
     </row>
-    <row r="755" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A755" s="5"/>
       <c r="B755" s="1"/>
       <c r="C755" s="1"/>
     </row>
-    <row r="756" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A756" s="5"/>
       <c r="B756" s="1"/>
       <c r="C756" s="1"/>
     </row>
-    <row r="757" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A757" s="5"/>
       <c r="B757" s="1"/>
       <c r="C757" s="1"/>
     </row>
-    <row r="758" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A758" s="5"/>
       <c r="B758" s="1"/>
       <c r="C758" s="1"/>
     </row>
-    <row r="759" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A759" s="5"/>
       <c r="B759" s="1"/>
       <c r="C759" s="1"/>
     </row>
-    <row r="760" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A760" s="5"/>
       <c r="B760" s="1"/>
       <c r="C760" s="1"/>
     </row>
-    <row r="761" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A761" s="5"/>
       <c r="B761" s="1"/>
       <c r="C761" s="1"/>
     </row>
-    <row r="762" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A762" s="5"/>
       <c r="B762" s="1"/>
       <c r="C762" s="1"/>
     </row>
-    <row r="763" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A763" s="5"/>
       <c r="B763" s="1"/>
       <c r="C763" s="1"/>
     </row>
-    <row r="764" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A764" s="5"/>
       <c r="B764" s="1"/>
       <c r="C764" s="1"/>
     </row>
-    <row r="765" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A765" s="5"/>
       <c r="B765" s="1"/>
       <c r="C765" s="1"/>
     </row>
-    <row r="766" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A766" s="5"/>
       <c r="B766" s="1"/>
       <c r="C766" s="1"/>
     </row>
-    <row r="767" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A767" s="5"/>
       <c r="B767" s="1"/>
       <c r="C767" s="1"/>
     </row>
-    <row r="768" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A768" s="5"/>
       <c r="B768" s="1"/>
       <c r="C768" s="1"/>
     </row>
-    <row r="769" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A769" s="5"/>
       <c r="B769" s="1"/>
       <c r="C769" s="1"/>
     </row>
-    <row r="770" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A770" s="5"/>
       <c r="B770" s="1"/>
       <c r="C770" s="1"/>
     </row>
-    <row r="771" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A771" s="5"/>
       <c r="B771" s="1"/>
       <c r="C771" s="1"/>
     </row>
-    <row r="772" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A772" s="5"/>
       <c r="B772" s="1"/>
       <c r="C772" s="1"/>
     </row>
-    <row r="773" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A773" s="5"/>
       <c r="B773" s="1"/>
       <c r="C773" s="1"/>
     </row>
-    <row r="774" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A774" s="5"/>
       <c r="B774" s="1"/>
       <c r="C774" s="1"/>
     </row>
-    <row r="775" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="775" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A775" s="5"/>
       <c r="B775" s="1"/>
       <c r="C775" s="1"/>
     </row>
-    <row r="776" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="776" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A776" s="5"/>
       <c r="B776" s="1"/>
       <c r="C776" s="1"/>
     </row>
-    <row r="777" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="777" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A777" s="5"/>
       <c r="B777" s="1"/>
       <c r="C777" s="1"/>
     </row>
-    <row r="778" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A778" s="5"/>
       <c r="B778" s="1"/>
       <c r="C778" s="1"/>
     </row>
-    <row r="779" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="779" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A779" s="5"/>
       <c r="B779" s="1"/>
       <c r="C779" s="1"/>
     </row>
-    <row r="780" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A780" s="5"/>
       <c r="B780" s="1"/>
       <c r="C780" s="1"/>
     </row>
-    <row r="781" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="781" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A781" s="5"/>
       <c r="B781" s="1"/>
       <c r="C781" s="1"/>
     </row>
-    <row r="782" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="782" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A782" s="5"/>
       <c r="B782" s="1"/>
       <c r="C782" s="1"/>
     </row>
-    <row r="783" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A783" s="5"/>
       <c r="B783" s="1"/>
       <c r="C783" s="1"/>
     </row>
-    <row r="784" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="784" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A784" s="5"/>
       <c r="B784" s="1"/>
       <c r="C784" s="1"/>
     </row>
-    <row r="785" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="785" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A785" s="5"/>
       <c r="B785" s="1"/>
       <c r="C785" s="1"/>
     </row>
-    <row r="786" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="786" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A786" s="5"/>
       <c r="B786" s="1"/>
       <c r="C786" s="1"/>
     </row>
-    <row r="787" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="787" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A787" s="5"/>
       <c r="B787" s="1"/>
       <c r="C787" s="1"/>
     </row>
-    <row r="788" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="788" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A788" s="5"/>
       <c r="B788" s="1"/>
       <c r="C788" s="1"/>
     </row>
-    <row r="789" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A789" s="5"/>
       <c r="B789" s="1"/>
       <c r="C789" s="1"/>
     </row>
-    <row r="790" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="790" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A790" s="5"/>
       <c r="B790" s="1"/>
       <c r="C790" s="1"/>
     </row>
-    <row r="791" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="791" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A791" s="5"/>
       <c r="B791" s="1"/>
       <c r="C791" s="1"/>
     </row>
-    <row r="792" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="792" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A792" s="5"/>
       <c r="B792" s="1"/>
       <c r="C792" s="1"/>
     </row>
-    <row r="793" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="793" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A793" s="5"/>
       <c r="B793" s="1"/>
       <c r="C793" s="1"/>
     </row>
-    <row r="794" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="794" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A794" s="5"/>
       <c r="B794" s="1"/>
       <c r="C794" s="1"/>
     </row>
-    <row r="795" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="795" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A795" s="5"/>
       <c r="B795" s="1"/>
       <c r="C795" s="1"/>
     </row>
-    <row r="796" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="796" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A796" s="5"/>
       <c r="B796" s="1"/>
       <c r="C796" s="1"/>
     </row>
-    <row r="797" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="797" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A797" s="5"/>
       <c r="B797" s="1"/>
       <c r="C797" s="1"/>
     </row>
-    <row r="798" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="798" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A798" s="5"/>
       <c r="B798" s="1"/>
       <c r="C798" s="1"/>
     </row>
-    <row r="799" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="799" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A799" s="5"/>
       <c r="B799" s="1"/>
       <c r="C799" s="1"/>
     </row>
-    <row r="800" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="800" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A800" s="5"/>
       <c r="B800" s="1"/>
       <c r="C800" s="1"/>
     </row>
-    <row r="801" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="801" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A801" s="5"/>
       <c r="B801" s="1"/>
       <c r="C801" s="1"/>
     </row>
-    <row r="802" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="802" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A802" s="5"/>
       <c r="B802" s="1"/>
       <c r="C802" s="1"/>
     </row>
-    <row r="803" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="803" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A803" s="5"/>
       <c r="B803" s="1"/>
       <c r="C803" s="1"/>
     </row>
-    <row r="804" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="804" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A804" s="5"/>
       <c r="B804" s="1"/>
       <c r="C804" s="1"/>
     </row>
-    <row r="805" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="805" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A805" s="5"/>
       <c r="B805" s="1"/>
       <c r="C805" s="1"/>
     </row>
-    <row r="806" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="806" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A806" s="5"/>
       <c r="B806" s="1"/>
       <c r="C806" s="1"/>
     </row>
-    <row r="807" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="807" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A807" s="5"/>
       <c r="B807" s="1"/>
       <c r="C807" s="1"/>
     </row>
-    <row r="808" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="808" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A808" s="5"/>
       <c r="B808" s="1"/>
       <c r="C808" s="1"/>
     </row>
-    <row r="809" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="809" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A809" s="5"/>
       <c r="B809" s="1"/>
       <c r="C809" s="1"/>
     </row>
-    <row r="810" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="810" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A810" s="5"/>
       <c r="B810" s="1"/>
       <c r="C810" s="1"/>
     </row>
-    <row r="811" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="811" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A811" s="5"/>
       <c r="B811" s="1"/>
       <c r="C811" s="1"/>
     </row>
-    <row r="812" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="812" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A812" s="5"/>
       <c r="B812" s="1"/>
       <c r="C812" s="1"/>
     </row>
-    <row r="813" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="813" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A813" s="5"/>
       <c r="B813" s="1"/>
       <c r="C813" s="1"/>
     </row>
-    <row r="814" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="814" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A814" s="5"/>
       <c r="B814" s="1"/>
       <c r="C814" s="1"/>
     </row>
-    <row r="815" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="815" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A815" s="5"/>
       <c r="B815" s="1"/>
       <c r="C815" s="1"/>
     </row>
-    <row r="816" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="816" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A816" s="5"/>
       <c r="B816" s="1"/>
       <c r="C816" s="1"/>
     </row>
-    <row r="817" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="817" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A817" s="5"/>
       <c r="B817" s="1"/>
       <c r="C817" s="1"/>
     </row>
-    <row r="818" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="818" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A818" s="5"/>
       <c r="B818" s="1"/>
       <c r="C818" s="1"/>
     </row>
-    <row r="819" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="819" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A819" s="5"/>
       <c r="B819" s="1"/>
       <c r="C819" s="1"/>
     </row>
-    <row r="820" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="820" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A820" s="5"/>
       <c r="B820" s="1"/>
       <c r="C820" s="1"/>
     </row>
-    <row r="821" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="821" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A821" s="5"/>
       <c r="B821" s="1"/>
       <c r="C821" s="1"/>
     </row>
-    <row r="822" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="822" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A822" s="5"/>
       <c r="B822" s="1"/>
       <c r="C822" s="1"/>
     </row>
-    <row r="823" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="823" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A823" s="5"/>
       <c r="B823" s="1"/>
       <c r="C823" s="1"/>
     </row>
-    <row r="824" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="824" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A824" s="5"/>
       <c r="B824" s="1"/>
       <c r="C824" s="1"/>
     </row>
-    <row r="825" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="825" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A825" s="5"/>
       <c r="B825" s="1"/>
       <c r="C825" s="1"/>
     </row>
-    <row r="826" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="826" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A826" s="5"/>
       <c r="B826" s="1"/>
       <c r="C826" s="1"/>
     </row>
-    <row r="827" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="827" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A827" s="5"/>
       <c r="B827" s="1"/>
       <c r="C827" s="1"/>
     </row>
-    <row r="828" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="828" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A828" s="5"/>
       <c r="B828" s="1"/>
       <c r="C828" s="1"/>
     </row>
-    <row r="829" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="829" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A829" s="5"/>
       <c r="B829" s="1"/>
       <c r="C829" s="1"/>
     </row>
-    <row r="830" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="830" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A830" s="5"/>
       <c r="B830" s="1"/>
       <c r="C830" s="1"/>
     </row>
-    <row r="831" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="831" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A831" s="5"/>
       <c r="B831" s="1"/>
       <c r="C831" s="1"/>
     </row>
-    <row r="832" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="832" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A832" s="5"/>
       <c r="B832" s="1"/>
       <c r="C832" s="1"/>
     </row>
-    <row r="833" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="833" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A833" s="5"/>
       <c r="B833" s="1"/>
       <c r="C833" s="1"/>
     </row>
-    <row r="834" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="834" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A834" s="5"/>
       <c r="B834" s="1"/>
       <c r="C834" s="1"/>
     </row>
-    <row r="835" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="835" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A835" s="5"/>
       <c r="B835" s="1"/>
       <c r="C835" s="1"/>
     </row>
-    <row r="836" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="836" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A836" s="5"/>
       <c r="B836" s="1"/>
       <c r="C836" s="1"/>
     </row>
-    <row r="837" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="837" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A837" s="5"/>
       <c r="B837" s="1"/>
       <c r="C837" s="1"/>
     </row>
-    <row r="838" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="838" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A838" s="5"/>
       <c r="B838" s="1"/>
       <c r="C838" s="1"/>
     </row>
-    <row r="839" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="839" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A839" s="5"/>
       <c r="B839" s="1"/>
       <c r="C839" s="1"/>
     </row>
-    <row r="840" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="840" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A840" s="5"/>
       <c r="B840" s="1"/>
       <c r="C840" s="1"/>
     </row>
-    <row r="841" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="841" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A841" s="5"/>
       <c r="B841" s="1"/>
       <c r="C841" s="1"/>
     </row>
-    <row r="842" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="842" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A842" s="5"/>
       <c r="B842" s="1"/>
       <c r="C842" s="1"/>
     </row>
-    <row r="843" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="843" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A843" s="5"/>
       <c r="B843" s="1"/>
       <c r="C843" s="1"/>
     </row>
-    <row r="844" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="844" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A844" s="5"/>
       <c r="B844" s="1"/>
       <c r="C844" s="1"/>
     </row>
-    <row r="845" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="845" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A845" s="5"/>
       <c r="B845" s="1"/>
       <c r="C845" s="1"/>
     </row>
-    <row r="846" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="846" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A846" s="5"/>
       <c r="B846" s="1"/>
       <c r="C846" s="1"/>
     </row>
-    <row r="847" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="847" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A847" s="5"/>
       <c r="B847" s="1"/>
       <c r="C847" s="1"/>
     </row>
-    <row r="848" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="848" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A848" s="5"/>
       <c r="B848" s="1"/>
       <c r="C848" s="1"/>
     </row>
-    <row r="849" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="849" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A849" s="5"/>
       <c r="B849" s="1"/>
       <c r="C849" s="1"/>
     </row>
-    <row r="850" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="850" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A850" s="5"/>
       <c r="B850" s="1"/>
       <c r="C850" s="1"/>
     </row>
-    <row r="851" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="851" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A851" s="5"/>
       <c r="B851" s="1"/>
       <c r="C851" s="1"/>
     </row>
-    <row r="852" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="852" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A852" s="5"/>
       <c r="B852" s="1"/>
       <c r="C852" s="1"/>
     </row>
-    <row r="853" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="853" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A853" s="5"/>
       <c r="B853" s="1"/>
       <c r="C853" s="1"/>
     </row>
-    <row r="854" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="854" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A854" s="5"/>
       <c r="B854" s="1"/>
       <c r="C854" s="1"/>
     </row>
-    <row r="855" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="855" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A855" s="5"/>
       <c r="B855" s="1"/>
       <c r="C855" s="1"/>
     </row>
-    <row r="856" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="856" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A856" s="5"/>
       <c r="B856" s="1"/>
       <c r="C856" s="1"/>
     </row>
-    <row r="857" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="857" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A857" s="5"/>
       <c r="B857" s="1"/>
       <c r="C857" s="1"/>
     </row>
-    <row r="858" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="858" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A858" s="5"/>
       <c r="B858" s="1"/>
       <c r="C858" s="1"/>
     </row>
-    <row r="859" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="859" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A859" s="5"/>
       <c r="B859" s="1"/>
       <c r="C859" s="1"/>
     </row>
-    <row r="860" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="860" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A860" s="5"/>
       <c r="B860" s="1"/>
       <c r="C860" s="1"/>
     </row>
-    <row r="861" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="861" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A861" s="5"/>
       <c r="B861" s="1"/>
       <c r="C861" s="1"/>
     </row>
-    <row r="862" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="862" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A862" s="5"/>
       <c r="B862" s="1"/>
       <c r="C862" s="1"/>
     </row>
-    <row r="863" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="863" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A863" s="5"/>
       <c r="B863" s="1"/>
       <c r="C863" s="1"/>
     </row>
-    <row r="864" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="864" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A864" s="5"/>
       <c r="B864" s="1"/>
       <c r="C864" s="1"/>
     </row>
-    <row r="865" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="865" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A865" s="5"/>
       <c r="B865" s="1"/>
       <c r="C865" s="1"/>
     </row>
-    <row r="866" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="866" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A866" s="5"/>
       <c r="B866" s="1"/>
       <c r="C866" s="1"/>
     </row>
-    <row r="867" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="867" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A867" s="5"/>
       <c r="B867" s="1"/>
       <c r="C867" s="1"/>
     </row>
-    <row r="868" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="868" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A868" s="5"/>
       <c r="B868" s="1"/>
       <c r="C868" s="1"/>
     </row>
-    <row r="869" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="869" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A869" s="5"/>
       <c r="B869" s="1"/>
       <c r="C869" s="1"/>
     </row>
-    <row r="870" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="870" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A870" s="5"/>
       <c r="B870" s="1"/>
       <c r="C870" s="1"/>
     </row>
-    <row r="871" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="871" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A871" s="5"/>
       <c r="B871" s="1"/>
       <c r="C871" s="1"/>
     </row>
-    <row r="872" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="872" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A872" s="5"/>
       <c r="B872" s="1"/>
       <c r="C872" s="1"/>
     </row>
-    <row r="873" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="873" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A873" s="5"/>
       <c r="B873" s="1"/>
       <c r="C873" s="1"/>
     </row>
-    <row r="874" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="874" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A874" s="5"/>
       <c r="B874" s="1"/>
       <c r="C874" s="1"/>
     </row>
-    <row r="875" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="875" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A875" s="5"/>
       <c r="B875" s="1"/>
       <c r="C875" s="1"/>
     </row>
-    <row r="876" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="876" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A876" s="5"/>
       <c r="B876" s="1"/>
       <c r="C876" s="1"/>
     </row>
-    <row r="877" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="877" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A877" s="5"/>
       <c r="B877" s="1"/>
       <c r="C877" s="1"/>
     </row>
-    <row r="878" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="878" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A878" s="5"/>
       <c r="B878" s="1"/>
       <c r="C878" s="1"/>
     </row>
-    <row r="879" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="879" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A879" s="5"/>
       <c r="B879" s="1"/>
       <c r="C879" s="1"/>
     </row>
-    <row r="880" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="880" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A880" s="5"/>
       <c r="B880" s="1"/>
       <c r="C880" s="1"/>
     </row>
-    <row r="881" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="881" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A881" s="5"/>
       <c r="B881" s="1"/>
       <c r="C881" s="1"/>
     </row>
-    <row r="882" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="882" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A882" s="5"/>
       <c r="B882" s="1"/>
       <c r="C882" s="1"/>
     </row>
-    <row r="883" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="883" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A883" s="5"/>
       <c r="B883" s="1"/>
       <c r="C883" s="1"/>
     </row>
-    <row r="884" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="884" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A884" s="5"/>
       <c r="B884" s="1"/>
       <c r="C884" s="1"/>
     </row>
-    <row r="885" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="885" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A885" s="5"/>
       <c r="B885" s="1"/>
       <c r="C885" s="1"/>
     </row>
-    <row r="886" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="886" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A886" s="5"/>
       <c r="B886" s="1"/>
       <c r="C886" s="1"/>
     </row>
-    <row r="887" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="887" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A887" s="5"/>
       <c r="B887" s="1"/>
       <c r="C887" s="1"/>
     </row>
-    <row r="888" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="888" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A888" s="5"/>
       <c r="B888" s="1"/>
       <c r="C888" s="1"/>
     </row>
-    <row r="889" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="889" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A889" s="5"/>
       <c r="B889" s="1"/>
       <c r="C889" s="1"/>
     </row>
-    <row r="890" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="890" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A890" s="5"/>
       <c r="B890" s="1"/>
       <c r="C890" s="1"/>
     </row>
-    <row r="891" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="891" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A891" s="5"/>
       <c r="B891" s="1"/>
       <c r="C891" s="1"/>
     </row>
-    <row r="892" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="892" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A892" s="5"/>
       <c r="B892" s="1"/>
       <c r="C892" s="1"/>
     </row>
-    <row r="893" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="893" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A893" s="5"/>
       <c r="B893" s="1"/>
       <c r="C893" s="1"/>
     </row>
-    <row r="894" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="894" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A894" s="5"/>
       <c r="B894" s="1"/>
       <c r="C894" s="1"/>
     </row>
-    <row r="895" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="895" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A895" s="5"/>
       <c r="B895" s="1"/>
       <c r="C895" s="1"/>
     </row>
-    <row r="896" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="896" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A896" s="5"/>
       <c r="B896" s="1"/>
       <c r="C896" s="1"/>
     </row>
-    <row r="897" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="897" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A897" s="5"/>
       <c r="B897" s="1"/>
       <c r="C897" s="1"/>
     </row>
-    <row r="898" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="898" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A898" s="5"/>
       <c r="B898" s="1"/>
       <c r="C898" s="1"/>
     </row>
-    <row r="899" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="899" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A899" s="5"/>
       <c r="B899" s="1"/>
       <c r="C899" s="1"/>
     </row>
-    <row r="900" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="900" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A900" s="5"/>
       <c r="B900" s="1"/>
       <c r="C900" s="1"/>
     </row>
-    <row r="901" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="901" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A901" s="5"/>
       <c r="B901" s="1"/>
       <c r="C901" s="1"/>
     </row>
-    <row r="902" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="902" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A902" s="5"/>
       <c r="B902" s="1"/>
       <c r="C902" s="1"/>
     </row>
-    <row r="903" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="903" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A903" s="5"/>
       <c r="B903" s="1"/>
       <c r="C903" s="1"/>
     </row>
-    <row r="904" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="904" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A904" s="5"/>
       <c r="B904" s="1"/>
       <c r="C904" s="1"/>
     </row>
-    <row r="905" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="905" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A905" s="5"/>
       <c r="B905" s="1"/>
       <c r="C905" s="1"/>
     </row>
-    <row r="906" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="906" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A906" s="5"/>
       <c r="B906" s="1"/>
       <c r="C906" s="1"/>
     </row>
-    <row r="907" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="907" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A907" s="5"/>
       <c r="B907" s="1"/>
       <c r="C907" s="1"/>
     </row>
-    <row r="908" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="908" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A908" s="5"/>
       <c r="B908" s="1"/>
       <c r="C908" s="1"/>
     </row>
-    <row r="909" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="909" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A909" s="5"/>
       <c r="B909" s="1"/>
       <c r="C909" s="1"/>
     </row>
-    <row r="910" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="910" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A910" s="5"/>
       <c r="B910" s="1"/>
       <c r="C910" s="1"/>
     </row>
-    <row r="911" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="911" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A911" s="5"/>
       <c r="B911" s="1"/>
       <c r="C911" s="1"/>
     </row>
-    <row r="912" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="912" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A912" s="5"/>
       <c r="B912" s="1"/>
       <c r="C912" s="1"/>
     </row>
-    <row r="913" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="913" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A913" s="5"/>
       <c r="B913" s="1"/>
       <c r="C913" s="1"/>
     </row>
-    <row r="914" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="914" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A914" s="5"/>
       <c r="B914" s="1"/>
       <c r="C914" s="1"/>
     </row>
-    <row r="915" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="915" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A915" s="5"/>
       <c r="B915" s="1"/>
       <c r="C915" s="1"/>
     </row>
-    <row r="916" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="916" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A916" s="5"/>
       <c r="B916" s="1"/>
       <c r="C916" s="1"/>
     </row>
-    <row r="917" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="917" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A917" s="5"/>
       <c r="B917" s="1"/>
       <c r="C917" s="1"/>
     </row>
-    <row r="918" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="918" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A918" s="5"/>
       <c r="B918" s="1"/>
       <c r="C918" s="1"/>
     </row>
-    <row r="919" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="919" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A919" s="5"/>
       <c r="B919" s="1"/>
       <c r="C919" s="1"/>
     </row>
-    <row r="920" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="920" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A920" s="5"/>
       <c r="B920" s="1"/>
       <c r="C920" s="1"/>
     </row>
-    <row r="921" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="921" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A921" s="5"/>
       <c r="B921" s="1"/>
       <c r="C921" s="1"/>
     </row>
-    <row r="922" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="922" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A922" s="5"/>
       <c r="B922" s="1"/>
       <c r="C922" s="1"/>
     </row>
-    <row r="923" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="923" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A923" s="5"/>
       <c r="B923" s="1"/>
       <c r="C923" s="1"/>
     </row>
-    <row r="924" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="924" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A924" s="5"/>
       <c r="B924" s="1"/>
       <c r="C924" s="1"/>
     </row>
-    <row r="925" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="925" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A925" s="5"/>
       <c r="B925" s="1"/>
       <c r="C925" s="1"/>
     </row>
-    <row r="926" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="926" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A926" s="5"/>
       <c r="B926" s="1"/>
       <c r="C926" s="1"/>
     </row>
-    <row r="927" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="927" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A927" s="5"/>
       <c r="B927" s="1"/>
       <c r="C927" s="1"/>
     </row>
-    <row r="928" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="928" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A928" s="5"/>
       <c r="B928" s="1"/>
       <c r="C928" s="1"/>
     </row>
-    <row r="929" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="929" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A929" s="5"/>
       <c r="B929" s="1"/>
       <c r="C929" s="1"/>
     </row>
-    <row r="930" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="930" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A930" s="5"/>
       <c r="B930" s="1"/>
       <c r="C930" s="1"/>
     </row>
-    <row r="931" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="931" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A931" s="5"/>
       <c r="B931" s="1"/>
       <c r="C931" s="1"/>
     </row>
-    <row r="932" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="932" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A932" s="5"/>
       <c r="B932" s="1"/>
       <c r="C932" s="1"/>
     </row>
-    <row r="933" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="933" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A933" s="5"/>
       <c r="B933" s="1"/>
       <c r="C933" s="1"/>
     </row>
-    <row r="934" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="934" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A934" s="5"/>
       <c r="B934" s="1"/>
       <c r="C934" s="1"/>
     </row>
-    <row r="935" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="935" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A935" s="5"/>
       <c r="B935" s="1"/>
       <c r="C935" s="1"/>
     </row>
-    <row r="936" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="936" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A936" s="5"/>
       <c r="B936" s="1"/>
       <c r="C936" s="1"/>
     </row>
-    <row r="937" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="937" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A937" s="5"/>
       <c r="B937" s="1"/>
       <c r="C937" s="1"/>
     </row>
-    <row r="938" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="938" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A938" s="5"/>
       <c r="B938" s="1"/>
       <c r="C938" s="1"/>
     </row>
-    <row r="939" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="939" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A939" s="5"/>
       <c r="B939" s="1"/>
       <c r="C939" s="1"/>
     </row>
-    <row r="940" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="940" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A940" s="5"/>
       <c r="B940" s="1"/>
       <c r="C940" s="1"/>
     </row>
-    <row r="941" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="941" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A941" s="5"/>
       <c r="B941" s="1"/>
       <c r="C941" s="1"/>
     </row>
-    <row r="942" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="942" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A942" s="5"/>
       <c r="B942" s="1"/>
       <c r="C942" s="1"/>
     </row>
-    <row r="943" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="943" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A943" s="5"/>
       <c r="B943" s="1"/>
       <c r="C943" s="1"/>
     </row>
-    <row r="944" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="944" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A944" s="5"/>
       <c r="B944" s="1"/>
       <c r="C944" s="1"/>
     </row>
-    <row r="945" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="945" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A945" s="5"/>
       <c r="B945" s="1"/>
       <c r="C945" s="1"/>
     </row>
-    <row r="946" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="946" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A946" s="5"/>
       <c r="B946" s="1"/>
       <c r="C946" s="1"/>
     </row>
-    <row r="947" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="947" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A947" s="5"/>
       <c r="B947" s="1"/>
       <c r="C947" s="1"/>
     </row>
-    <row r="948" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="948" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A948" s="5"/>
       <c r="B948" s="1"/>
       <c r="C948" s="1"/>
     </row>
-    <row r="949" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="949" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A949" s="5"/>
       <c r="B949" s="1"/>
       <c r="C949" s="1"/>
     </row>
-    <row r="950" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="950" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A950" s="5"/>
       <c r="B950" s="1"/>
       <c r="C950" s="1"/>
     </row>
-    <row r="951" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="951" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A951" s="5"/>
       <c r="B951" s="1"/>
       <c r="C951" s="1"/>
     </row>
-    <row r="952" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="952" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A952" s="5"/>
       <c r="B952" s="1"/>
       <c r="C952" s="1"/>
     </row>
-    <row r="953" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="953" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A953" s="5"/>
       <c r="B953" s="1"/>
       <c r="C953" s="1"/>
     </row>
-    <row r="954" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="954" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A954" s="5"/>
       <c r="B954" s="1"/>
       <c r="C954" s="1"/>
     </row>
-    <row r="955" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="955" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A955" s="5"/>
       <c r="B955" s="1"/>
       <c r="C955" s="1"/>
     </row>
-    <row r="956" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="956" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A956" s="5"/>
       <c r="B956" s="1"/>
       <c r="C956" s="1"/>
     </row>
-    <row r="957" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="957" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A957" s="5"/>
       <c r="B957" s="1"/>
       <c r="C957" s="1"/>
     </row>
-    <row r="958" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="958" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A958" s="5"/>
       <c r="B958" s="1"/>
       <c r="C958" s="1"/>
     </row>
-    <row r="959" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="959" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A959" s="5"/>
       <c r="B959" s="1"/>
       <c r="C959" s="1"/>
     </row>
-    <row r="960" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="960" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A960" s="5"/>
       <c r="B960" s="1"/>
       <c r="C960" s="1"/>
     </row>
-    <row r="961" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="961" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A961" s="5"/>
       <c r="B961" s="1"/>
       <c r="C961" s="1"/>
     </row>
-    <row r="962" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="962" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A962" s="5"/>
       <c r="B962" s="1"/>
       <c r="C962" s="1"/>
     </row>
-    <row r="963" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="963" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A963" s="5"/>
       <c r="B963" s="1"/>
       <c r="C963" s="1"/>
     </row>
-    <row r="964" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="964" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A964" s="5"/>
       <c r="B964" s="1"/>
       <c r="C964" s="1"/>
     </row>
-    <row r="965" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="965" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A965" s="5"/>
       <c r="B965" s="1"/>
       <c r="C965" s="1"/>
     </row>
-    <row r="966" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="966" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A966" s="5"/>
       <c r="B966" s="1"/>
       <c r="C966" s="1"/>
     </row>
-    <row r="967" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="967" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A967" s="5"/>
       <c r="B967" s="1"/>
       <c r="C967" s="1"/>
     </row>
-    <row r="968" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="968" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A968" s="5"/>
       <c r="B968" s="1"/>
       <c r="C968" s="1"/>
     </row>
-    <row r="969" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="969" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A969" s="5"/>
       <c r="B969" s="1"/>
       <c r="C969" s="1"/>
     </row>
-    <row r="970" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="970" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A970" s="5"/>
       <c r="B970" s="1"/>
       <c r="C970" s="1"/>
     </row>
-    <row r="971" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="971" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A971" s="5"/>
       <c r="B971" s="1"/>
       <c r="C971" s="1"/>
     </row>
-    <row r="972" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="972" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A972" s="5"/>
       <c r="B972" s="1"/>
       <c r="C972" s="1"/>
     </row>
-    <row r="973" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="973" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A973" s="5"/>
       <c r="B973" s="1"/>
       <c r="C973" s="1"/>
     </row>
-    <row r="974" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="974" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A974" s="5"/>
       <c r="B974" s="1"/>
       <c r="C974" s="1"/>
     </row>
-    <row r="975" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="975" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A975" s="5"/>
       <c r="B975" s="1"/>
       <c r="C975" s="1"/>
     </row>
-    <row r="976" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="976" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A976" s="5"/>
       <c r="B976" s="1"/>
       <c r="C976" s="1"/>
     </row>
-    <row r="977" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="977" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A977" s="5"/>
       <c r="B977" s="1"/>
       <c r="C977" s="1"/>
     </row>
-    <row r="978" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="978" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A978" s="5"/>
       <c r="B978" s="1"/>
       <c r="C978" s="1"/>
     </row>
-    <row r="979" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="979" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A979" s="5"/>
       <c r="B979" s="1"/>
       <c r="C979" s="1"/>
     </row>
-    <row r="980" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="980" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A980" s="5"/>
       <c r="B980" s="1"/>
       <c r="C980" s="1"/>
     </row>
-    <row r="981" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="981" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A981" s="5"/>
       <c r="B981" s="1"/>
       <c r="C981" s="1"/>
     </row>
-    <row r="982" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="982" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A982" s="5"/>
       <c r="B982" s="1"/>
       <c r="C982" s="1"/>
     </row>
-    <row r="983" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="983" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A983" s="5"/>
       <c r="B983" s="1"/>
       <c r="C983" s="1"/>
     </row>
-    <row r="984" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="984" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A984" s="5"/>
       <c r="B984" s="1"/>
       <c r="C984" s="1"/>
     </row>
-    <row r="985" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="985" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A985" s="5"/>
       <c r="B985" s="1"/>
       <c r="C985" s="1"/>
     </row>
-    <row r="986" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="986" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A986" s="5"/>
       <c r="B986" s="1"/>
       <c r="C986" s="1"/>
     </row>
-    <row r="987" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="987" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A987" s="5"/>
       <c r="B987" s="1"/>
       <c r="C987" s="1"/>
     </row>
-    <row r="988" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="988" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A988" s="5"/>
       <c r="B988" s="1"/>
       <c r="C988" s="1"/>
     </row>
-    <row r="989" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="989" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A989" s="5"/>
       <c r="B989" s="1"/>
       <c r="C989" s="1"/>
     </row>
-    <row r="990" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="990" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A990" s="5"/>
       <c r="B990" s="1"/>
       <c r="C990" s="1"/>
     </row>
-    <row r="991" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="991" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A991" s="5"/>
       <c r="B991" s="1"/>
       <c r="C991" s="1"/>
     </row>
-    <row r="992" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="992" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A992" s="5"/>
       <c r="B992" s="1"/>
       <c r="C992" s="1"/>
     </row>
-    <row r="993" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="993" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A993" s="5"/>
       <c r="B993" s="1"/>
       <c r="C993" s="1"/>
     </row>
-    <row r="994" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="994" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A994" s="5"/>
       <c r="B994" s="1"/>
       <c r="C994" s="1"/>
     </row>
-    <row r="995" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="995" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A995" s="5"/>
       <c r="B995" s="1"/>
       <c r="C995" s="1"/>
     </row>
-    <row r="996" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="996" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A996" s="5"/>
       <c r="B996" s="1"/>
       <c r="C996" s="1"/>
     </row>
-    <row r="997" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="997" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A997" s="5"/>
       <c r="B997" s="1"/>
       <c r="C997" s="1"/>
     </row>
-    <row r="998" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="998" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A998" s="5"/>
       <c r="B998" s="1"/>
       <c r="C998" s="1"/>
     </row>
-    <row r="999" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="999" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A999" s="5"/>
       <c r="B999" s="1"/>
       <c r="C999" s="1"/>
     </row>
-    <row r="1000" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1000" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1000" s="5"/>
       <c r="B1000" s="1"/>
       <c r="C1000" s="1"/>
     </row>
-    <row r="1001" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1001" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1001" s="5"/>
       <c r="B1001" s="1"/>
       <c r="C1001" s="1"/>
     </row>
-    <row r="1002" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1002" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1002" s="5"/>
       <c r="B1002" s="1"/>
       <c r="C1002" s="1"/>
@@ -67166,10 +67153,6 @@
       <c r="A33" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="1"/>
-      <c r="C33" s="8">
-        <v>1</v>
-      </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" s="11" t="s">
@@ -67183,7 +67166,9 @@
         <v>41</v>
       </c>
       <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
+      <c r="C35" s="8">
+        <v>1</v>
+      </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="11" t="s">

--- a/hspa-test.xlsx
+++ b/hspa-test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jonas.grabbe\tafi_test-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20FA06A3-F869-465F-87ED-55B29F23F5D4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEAE7354-A715-4610-A9DE-2474B683F379}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28770" windowHeight="12030" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28770" windowHeight="12030" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Amud" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5836" uniqueCount="665">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5836" uniqueCount="664">
   <si>
     <t>Amud I</t>
   </si>
@@ -1774,12 +1774,6 @@
     <t>Ochoz II</t>
   </si>
   <si>
-    <t>Ochoz 1</t>
-  </si>
-  <si>
-    <t>Ochoz 2</t>
-  </si>
-  <si>
     <t>Švédův stůl Cave</t>
   </si>
   <si>
@@ -2024,6 +2018,9 @@
   </si>
   <si>
     <t>rib_12</t>
+  </si>
+  <si>
+    <t>Ochoz</t>
   </si>
 </sst>
 </file>
@@ -2391,7 +2388,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -2422,13 +2419,13 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
+        <v>598</v>
+      </c>
+      <c r="C3" t="s">
+        <v>599</v>
+      </c>
+      <c r="D3" t="s">
         <v>600</v>
-      </c>
-      <c r="C3" t="s">
-        <v>601</v>
-      </c>
-      <c r="D3" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2475,7 +2472,7 @@
     </row>
     <row r="7" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>10</v>
@@ -2489,7 +2486,7 @@
     </row>
     <row r="8" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>11</v>
@@ -2503,7 +2500,7 @@
     </row>
     <row r="9" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>12</v>
@@ -2517,7 +2514,7 @@
     </row>
     <row r="10" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B10" s="8">
         <v>70000</v>
@@ -2531,7 +2528,7 @@
     </row>
     <row r="11" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B11" s="8">
         <v>50000</v>
@@ -2545,7 +2542,7 @@
     </row>
     <row r="12" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B12" s="9">
         <v>46115</v>
@@ -2559,7 +2556,7 @@
     </row>
     <row r="13" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>13</v>
@@ -2573,7 +2570,7 @@
     </row>
     <row r="14" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>14</v>
@@ -2587,7 +2584,7 @@
     </row>
     <row r="15" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>14</v>
@@ -2601,7 +2598,7 @@
     </row>
     <row r="16" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>14</v>
@@ -2671,7 +2668,7 @@
     </row>
     <row r="21" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B21" s="8">
         <v>0</v>
@@ -2685,7 +2682,7 @@
     </row>
     <row r="22" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B22" s="8">
         <v>0</v>
@@ -2741,7 +2738,7 @@
     </row>
     <row r="26" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>29</v>
@@ -2755,7 +2752,7 @@
     </row>
     <row r="27" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>30</v>
@@ -2769,7 +2766,7 @@
     </row>
     <row r="28" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>31</v>
@@ -2783,7 +2780,7 @@
     </row>
     <row r="29" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>32</v>
@@ -2817,7 +2814,7 @@
         <v>36</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="D31" s="1"/>
     </row>
@@ -3186,7 +3183,7 @@
     </row>
     <row r="76" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="10" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -4606,7 +4603,7 @@
     </row>
     <row r="247" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A247" s="4" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -4614,7 +4611,7 @@
     </row>
     <row r="248" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A248" s="4" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -4622,7 +4619,7 @@
     </row>
     <row r="249" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A249" s="4" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -4654,7 +4651,7 @@
     </row>
     <row r="252" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A252" s="4" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -4686,7 +4683,7 @@
     </row>
     <row r="255" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A255" s="4" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -4718,7 +4715,7 @@
     </row>
     <row r="258" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A258" s="4" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -4750,7 +4747,7 @@
     </row>
     <row r="261" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A261" s="4" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -4782,7 +4779,7 @@
     </row>
     <row r="264" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A264" s="4" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -4814,7 +4811,7 @@
     </row>
     <row r="267" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A267" s="4" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -4842,7 +4839,7 @@
     </row>
     <row r="270" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A270" s="4" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -4870,7 +4867,7 @@
     </row>
     <row r="273" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A273" s="4" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -4900,7 +4897,7 @@
     </row>
     <row r="276" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A276" s="4" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -4930,7 +4927,7 @@
     </row>
     <row r="279" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A279" s="4" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -4960,7 +4957,7 @@
     </row>
     <row r="282" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A282" s="4" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -5580,7 +5577,7 @@
     </row>
     <row r="351" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A351" s="4" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -5708,7 +5705,7 @@
     </row>
     <row r="367" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A367" s="4" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
@@ -6698,7 +6695,7 @@
     </row>
     <row r="482" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A482" s="4" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B482" s="1"/>
       <c r="C482" s="1"/>
@@ -6830,7 +6827,7 @@
     </row>
     <row r="498" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A498" s="4" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B498" s="1"/>
       <c r="C498" s="1"/>
@@ -9954,13 +9951,13 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
@@ -9979,10 +9976,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
@@ -9990,10 +9987,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
@@ -10020,7 +10017,7 @@
     </row>
     <row r="7" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>535</v>
@@ -10031,7 +10028,7 @@
     </row>
     <row r="8" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>536</v>
@@ -10042,18 +10039,18 @@
     </row>
     <row r="9" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B10" s="8">
         <v>4000</v>
@@ -10064,7 +10061,7 @@
     </row>
     <row r="11" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B11" s="8">
         <v>3500</v>
@@ -10075,7 +10072,7 @@
     </row>
     <row r="12" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B12" s="8">
         <v>1</v>
@@ -10086,7 +10083,7 @@
     </row>
     <row r="13" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>13</v>
@@ -10097,7 +10094,7 @@
     </row>
     <row r="14" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>14</v>
@@ -10108,7 +10105,7 @@
     </row>
     <row r="15" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>14</v>
@@ -10119,7 +10116,7 @@
     </row>
     <row r="16" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>14</v>
@@ -10174,7 +10171,7 @@
     </row>
     <row r="21" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B21" s="8">
         <v>0</v>
@@ -10185,7 +10182,7 @@
     </row>
     <row r="22" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="11" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B22" s="8">
         <v>0</v>
@@ -10229,7 +10226,7 @@
     </row>
     <row r="26" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="11" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>29</v>
@@ -10240,18 +10237,18 @@
     </row>
     <row r="27" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="11" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="11" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>14</v>
@@ -10262,7 +10259,7 @@
     </row>
     <row r="29" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="11" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>14</v>
@@ -10294,10 +10291,10 @@
         <v>37</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
@@ -10625,7 +10622,7 @@
     </row>
     <row r="76" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="11" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -11912,21 +11909,21 @@
     </row>
     <row r="247" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A247" s="11" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
     </row>
     <row r="248" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A248" s="11" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
     </row>
     <row r="249" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A249" s="11" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -11955,7 +11952,7 @@
     </row>
     <row r="252" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A252" s="11" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -11984,7 +11981,7 @@
     </row>
     <row r="255" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A255" s="11" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -12013,7 +12010,7 @@
     </row>
     <row r="258" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A258" s="11" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -12042,7 +12039,7 @@
     </row>
     <row r="261" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A261" s="11" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -12071,7 +12068,7 @@
     </row>
     <row r="264" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A264" s="11" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -12100,7 +12097,7 @@
     </row>
     <row r="267" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A267" s="11" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -12129,7 +12126,7 @@
     </row>
     <row r="270" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A270" s="11" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -12158,7 +12155,7 @@
     </row>
     <row r="273" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A273" s="11" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -12187,7 +12184,7 @@
     </row>
     <row r="276" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A276" s="11" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -12216,7 +12213,7 @@
     </row>
     <row r="279" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A279" s="11" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -12245,7 +12242,7 @@
     </row>
     <row r="282" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A282" s="11" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -12836,7 +12833,7 @@
     </row>
     <row r="351" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A351" s="11" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -12974,7 +12971,7 @@
     </row>
     <row r="367" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A367" s="11" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
@@ -13909,7 +13906,7 @@
     </row>
     <row r="482" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A482" s="11" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B482" s="1"/>
       <c r="C482" s="1"/>
@@ -14031,7 +14028,7 @@
     </row>
     <row r="498" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A498" s="11" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B498" s="1"/>
       <c r="C498" s="1"/>
@@ -16646,7 +16643,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B1" s="12" t="s">
         <v>514</v>
@@ -16665,7 +16662,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -16694,7 +16691,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>10</v>
@@ -16702,7 +16699,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>515</v>
@@ -16710,7 +16707,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>516</v>
@@ -16718,7 +16715,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B10" s="8">
         <v>31000</v>
@@ -16726,7 +16723,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B11" s="8">
         <v>23000</v>
@@ -16734,7 +16731,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B12" s="8">
         <v>3</v>
@@ -16742,7 +16739,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>14</v>
@@ -16750,7 +16747,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>14</v>
@@ -16758,7 +16755,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>517</v>
@@ -16766,7 +16763,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>14</v>
@@ -16806,7 +16803,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B21" s="8">
         <v>0</v>
@@ -16814,7 +16811,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="11" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B22" s="8">
         <v>0</v>
@@ -16846,7 +16843,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="11" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>29</v>
@@ -16854,7 +16851,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="11" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>30</v>
@@ -16862,7 +16859,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="11" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>520</v>
@@ -16870,7 +16867,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="11" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>14</v>
@@ -17163,7 +17160,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A76" s="11" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B76" s="1"/>
     </row>
@@ -18191,19 +18188,19 @@
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A247" s="11" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B247" s="8"/>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A248" s="11" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B248" s="1"/>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A249" s="11" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B249" s="1"/>
     </row>
@@ -18221,7 +18218,7 @@
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A252" s="11" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B252" s="1"/>
     </row>
@@ -18239,7 +18236,7 @@
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A255" s="11" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B255" s="1"/>
     </row>
@@ -18257,7 +18254,7 @@
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A258" s="11" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B258" s="1"/>
     </row>
@@ -18275,7 +18272,7 @@
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A261" s="11" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B261" s="1"/>
     </row>
@@ -18293,7 +18290,7 @@
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A264" s="11" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B264" s="1"/>
     </row>
@@ -18311,7 +18308,7 @@
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A267" s="11" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B267" s="1"/>
     </row>
@@ -18329,7 +18326,7 @@
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A270" s="11" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B270" s="1"/>
     </row>
@@ -18347,7 +18344,7 @@
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A273" s="11" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B273" s="1"/>
     </row>
@@ -18365,7 +18362,7 @@
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A276" s="11" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B276" s="1"/>
     </row>
@@ -18383,7 +18380,7 @@
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A279" s="11" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B279" s="1"/>
     </row>
@@ -18401,7 +18398,7 @@
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A282" s="11" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B282" s="1"/>
     </row>
@@ -18821,7 +18818,7 @@
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A351" s="11" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B351" s="1"/>
     </row>
@@ -18917,7 +18914,7 @@
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A367" s="11" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B367" s="1"/>
     </row>
@@ -19609,7 +19606,7 @@
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A482" s="11" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B482" s="1"/>
     </row>
@@ -19705,7 +19702,7 @@
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A498" s="11" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B498" s="1"/>
     </row>
@@ -21802,7 +21799,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B1" s="12" t="s">
         <v>524</v>
@@ -21839,16 +21836,16 @@
         <v>4</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>595</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>594</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>596</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>597</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>596</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>598</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -21904,7 +21901,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>10</v>
@@ -21921,7 +21918,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>515</v>
@@ -21938,7 +21935,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>516</v>
@@ -21955,7 +21952,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B10" s="8">
         <v>30000</v>
@@ -21972,7 +21969,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B11" s="8">
         <v>20000</v>
@@ -21989,7 +21986,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B12" s="8">
         <v>3</v>
@@ -22006,7 +22003,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>14</v>
@@ -22023,7 +22020,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>14</v>
@@ -22040,7 +22037,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>529</v>
@@ -22057,7 +22054,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>14</v>
@@ -22142,7 +22139,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B21" s="8">
         <v>0</v>
@@ -22159,7 +22156,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="11" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B22" s="8">
         <v>0</v>
@@ -22227,7 +22224,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="11" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>29</v>
@@ -22244,7 +22241,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="11" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>530</v>
@@ -22261,7 +22258,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="11" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>31</v>
@@ -22278,7 +22275,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="11" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>14</v>
@@ -22737,7 +22734,7 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" s="11" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -24442,7 +24439,7 @@
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A247" s="11" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -24451,7 +24448,7 @@
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A248" s="11" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -24460,7 +24457,7 @@
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A249" s="11" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -24499,7 +24496,7 @@
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A252" s="11" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -24538,7 +24535,7 @@
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A255" s="11" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -24577,7 +24574,7 @@
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A258" s="11" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -24616,7 +24613,7 @@
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A261" s="11" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -24655,7 +24652,7 @@
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A264" s="11" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -24694,7 +24691,7 @@
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A267" s="11" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -24733,7 +24730,7 @@
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A270" s="11" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -24772,7 +24769,7 @@
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A273" s="11" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -24811,7 +24808,7 @@
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A276" s="11" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -24850,7 +24847,7 @@
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A279" s="11" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -24889,7 +24886,7 @@
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A282" s="11" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -25670,7 +25667,7 @@
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A351" s="11" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -25850,7 +25847,7 @@
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A367" s="11" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
@@ -27109,7 +27106,7 @@
     </row>
     <row r="482" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A482" s="11" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B482" s="1"/>
       <c r="C482" s="1"/>
@@ -27267,7 +27264,7 @@
     </row>
     <row r="498" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A498" s="11" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B498" s="1"/>
       <c r="C498" s="1"/>
@@ -30895,10 +30892,10 @@
   <sheetData>
     <row r="1" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -30914,7 +30911,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -30922,7 +30919,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -30930,7 +30927,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -30943,7 +30940,7 @@
     </row>
     <row r="7" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>10</v>
@@ -30951,7 +30948,7 @@
     </row>
     <row r="8" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>515</v>
@@ -30959,15 +30956,15 @@
     </row>
     <row r="9" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B10" s="18">
         <v>19000</v>
@@ -30975,7 +30972,7 @@
     </row>
     <row r="11" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B11" s="18">
         <v>14400</v>
@@ -30983,7 +30980,7 @@
     </row>
     <row r="12" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B12" s="18">
         <v>2</v>
@@ -30991,7 +30988,7 @@
     </row>
     <row r="13" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B13" s="16" t="s">
         <v>13</v>
@@ -30999,15 +30996,15 @@
     </row>
     <row r="14" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B15" s="16" t="s">
         <v>14</v>
@@ -31015,7 +31012,7 @@
     </row>
     <row r="16" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B16" s="16" t="s">
         <v>14</v>
@@ -31055,7 +31052,7 @@
     </row>
     <row r="21" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B21" s="18">
         <v>0</v>
@@ -31063,7 +31060,7 @@
     </row>
     <row r="22" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B22" s="18">
         <v>0</v>
@@ -31095,7 +31092,7 @@
     </row>
     <row r="26" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B26" s="16" t="s">
         <v>29</v>
@@ -31103,7 +31100,7 @@
     </row>
     <row r="27" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B27" s="16" t="s">
         <v>30</v>
@@ -31111,7 +31108,7 @@
     </row>
     <row r="28" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B28" s="16" t="s">
         <v>31</v>
@@ -31119,7 +31116,7 @@
     </row>
     <row r="29" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B29" s="16" t="s">
         <v>32</v>
@@ -31138,7 +31135,7 @@
         <v>35</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -31146,7 +31143,7 @@
         <v>37</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -31411,7 +31408,7 @@
     </row>
     <row r="76" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A76" s="11" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B76" s="14"/>
     </row>
@@ -32467,19 +32464,19 @@
     </row>
     <row r="247" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A247" s="11" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B247" s="14"/>
     </row>
     <row r="248" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A248" s="11" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B248" s="14"/>
     </row>
     <row r="249" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A249" s="11" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B249" s="14"/>
     </row>
@@ -32501,7 +32498,7 @@
     </row>
     <row r="252" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A252" s="11" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B252" s="14"/>
     </row>
@@ -32521,7 +32518,7 @@
     </row>
     <row r="255" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A255" s="11" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B255" s="14"/>
     </row>
@@ -32541,7 +32538,7 @@
     </row>
     <row r="258" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A258" s="11" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B258" s="14"/>
     </row>
@@ -32563,7 +32560,7 @@
     </row>
     <row r="261" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A261" s="11" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B261" s="14"/>
     </row>
@@ -32581,7 +32578,7 @@
     </row>
     <row r="264" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A264" s="11" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B264" s="14"/>
     </row>
@@ -32601,7 +32598,7 @@
     </row>
     <row r="267" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A267" s="11" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B267" s="14"/>
     </row>
@@ -32623,7 +32620,7 @@
     </row>
     <row r="270" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A270" s="11" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B270" s="14"/>
     </row>
@@ -32641,7 +32638,7 @@
     </row>
     <row r="273" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A273" s="11" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B273" s="14"/>
     </row>
@@ -32661,7 +32658,7 @@
     </row>
     <row r="276" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A276" s="11" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B276" s="14"/>
     </row>
@@ -32681,7 +32678,7 @@
     </row>
     <row r="279" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A279" s="11" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B279" s="14"/>
     </row>
@@ -32703,7 +32700,7 @@
     </row>
     <row r="282" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A282" s="11" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B282" s="14"/>
     </row>
@@ -33145,7 +33142,7 @@
     </row>
     <row r="351" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A351" s="11" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B351" s="14"/>
     </row>
@@ -33247,7 +33244,7 @@
     </row>
     <row r="367" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A367" s="11" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B367" s="14"/>
     </row>
@@ -34001,7 +33998,7 @@
     </row>
     <row r="482" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A482" s="11" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B482" s="14"/>
     </row>
@@ -34109,7 +34106,7 @@
     </row>
     <row r="498" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A498" s="11" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B498" s="14"/>
     </row>
@@ -36236,7 +36233,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B1" s="12" t="s">
         <v>534</v>
@@ -36255,7 +36252,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -36284,7 +36281,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>535</v>
@@ -36292,7 +36289,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>536</v>
@@ -36300,7 +36297,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>14</v>
@@ -36308,7 +36305,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B10" s="8">
         <v>4000</v>
@@ -36316,7 +36313,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B11" s="8">
         <v>3500</v>
@@ -36324,7 +36321,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B12" s="8">
         <v>1</v>
@@ -36332,7 +36329,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>13</v>
@@ -36340,7 +36337,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>14</v>
@@ -36348,7 +36345,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>14</v>
@@ -36356,7 +36353,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>14</v>
@@ -36396,7 +36393,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B21" s="8">
         <v>0</v>
@@ -36404,7 +36401,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="11" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B22" s="8">
         <v>1</v>
@@ -36436,7 +36433,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="11" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>538</v>
@@ -36444,7 +36441,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="11" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>14</v>
@@ -36452,7 +36449,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="11" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>14</v>
@@ -36460,7 +36457,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="11" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>14</v>
@@ -36751,7 +36748,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A76" s="11" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B76" s="1"/>
     </row>
@@ -37781,18 +37778,18 @@
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A247" s="11" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A248" s="11" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B248" s="8"/>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A249" s="11" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B249" s="1"/>
     </row>
@@ -37810,7 +37807,7 @@
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A252" s="11" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B252" s="1"/>
     </row>
@@ -37828,7 +37825,7 @@
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A255" s="11" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B255" s="1"/>
     </row>
@@ -37846,7 +37843,7 @@
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A258" s="11" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B258" s="1"/>
     </row>
@@ -37864,7 +37861,7 @@
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A261" s="11" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B261" s="1"/>
     </row>
@@ -37882,7 +37879,7 @@
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A264" s="11" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B264" s="1"/>
     </row>
@@ -37900,7 +37897,7 @@
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A267" s="11" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B267" s="1"/>
     </row>
@@ -37918,7 +37915,7 @@
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A270" s="11" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B270" s="1"/>
     </row>
@@ -37936,7 +37933,7 @@
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A273" s="11" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B273" s="1"/>
     </row>
@@ -37954,7 +37951,7 @@
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A276" s="11" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B276" s="1"/>
     </row>
@@ -37972,7 +37969,7 @@
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A279" s="11" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B279" s="1"/>
     </row>
@@ -37990,7 +37987,7 @@
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A282" s="11" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B282" s="1"/>
     </row>
@@ -38416,7 +38413,7 @@
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A351" s="11" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B351" s="1"/>
     </row>
@@ -38512,7 +38509,7 @@
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A367" s="11" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B367" s="1"/>
     </row>
@@ -39212,7 +39209,7 @@
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A482" s="11" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B482" s="1"/>
     </row>
@@ -39308,7 +39305,7 @@
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A498" s="11" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B498" s="1"/>
     </row>
@@ -41405,7 +41402,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B1" s="12" t="s">
         <v>541</v>
@@ -41460,25 +41457,25 @@
         <v>4</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>604</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>605</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>606</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>607</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>608</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>609</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>610</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -41561,7 +41558,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>10</v>
@@ -41587,7 +41584,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>515</v>
@@ -41613,7 +41610,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>549</v>
@@ -41639,7 +41636,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B10" s="8">
         <v>14700</v>
@@ -41665,7 +41662,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B11" s="8">
         <v>14700</v>
@@ -41691,7 +41688,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B12" s="8">
         <v>2</v>
@@ -41717,7 +41714,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>13</v>
@@ -41743,7 +41740,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>14</v>
@@ -41769,7 +41766,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>14</v>
@@ -41795,7 +41792,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>14</v>
@@ -41925,7 +41922,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B21" s="8">
         <v>1</v>
@@ -41951,7 +41948,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="11" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B22" s="8">
         <v>0</v>
@@ -42055,7 +42052,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="11" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>553</v>
@@ -42081,7 +42078,7 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="11" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>14</v>
@@ -42107,7 +42104,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="11" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>31</v>
@@ -42133,7 +42130,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="11" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>554</v>
@@ -42746,7 +42743,7 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="11" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -44804,7 +44801,7 @@
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A247" s="11" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -44815,7 +44812,7 @@
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A248" s="11" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -44827,7 +44824,7 @@
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A249" s="11" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -44867,7 +44864,7 @@
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A252" s="11" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -44911,7 +44908,7 @@
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A255" s="11" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -44953,7 +44950,7 @@
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A258" s="11" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -44997,7 +44994,7 @@
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A261" s="11" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -45043,7 +45040,7 @@
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A264" s="11" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -45089,7 +45086,7 @@
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A267" s="11" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -45129,7 +45126,7 @@
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A270" s="11" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -45171,7 +45168,7 @@
     </row>
     <row r="273" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A273" s="11" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -45209,7 +45206,7 @@
     </row>
     <row r="276" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A276" s="11" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -45247,7 +45244,7 @@
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A279" s="11" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -45285,7 +45282,7 @@
     </row>
     <row r="282" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A282" s="11" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -46141,7 +46138,7 @@
     </row>
     <row r="351" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A351" s="11" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -46333,7 +46330,7 @@
     </row>
     <row r="367" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A367" s="11" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
@@ -47743,7 +47740,7 @@
     </row>
     <row r="482" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A482" s="11" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B482" s="1"/>
       <c r="C482" s="1"/>
@@ -47935,7 +47932,7 @@
     </row>
     <row r="498" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A498" s="11" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B498" s="1"/>
       <c r="C498" s="1"/>
@@ -53068,7 +53065,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B1" s="12" t="s">
         <v>559</v>
@@ -53099,13 +53096,13 @@
         <v>4</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>610</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>611</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>612</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -53152,7 +53149,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>535</v>
@@ -53166,7 +53163,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>564</v>
@@ -53180,7 +53177,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>565</v>
@@ -53194,7 +53191,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B10" s="8">
         <v>7250</v>
@@ -53208,7 +53205,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B11" s="8">
         <v>6900</v>
@@ -53222,7 +53219,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B12" s="8">
         <v>1</v>
@@ -53236,7 +53233,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>14</v>
@@ -53250,7 +53247,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>14</v>
@@ -53264,7 +53261,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>517</v>
@@ -53278,7 +53275,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>566</v>
@@ -53348,7 +53345,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B21" s="8">
         <v>0</v>
@@ -53362,7 +53359,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="11" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B22" s="8">
         <v>0</v>
@@ -53418,7 +53415,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="11" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>553</v>
@@ -53432,7 +53429,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="11" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>14</v>
@@ -53446,7 +53443,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="11" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>31</v>
@@ -53460,7 +53457,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="11" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>32</v>
@@ -53865,7 +53862,7 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" s="11" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -55251,13 +55248,13 @@
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A247" s="11" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="D247" s="1"/>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A248" s="11" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B248" s="8"/>
       <c r="C248" s="8"/>
@@ -55265,7 +55262,7 @@
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A249" s="11" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -55289,7 +55286,7 @@
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A252" s="11" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -55313,7 +55310,7 @@
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A255" s="11" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -55337,7 +55334,7 @@
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A258" s="11" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -55361,7 +55358,7 @@
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A261" s="11" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -55385,7 +55382,7 @@
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A264" s="11" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -55409,7 +55406,7 @@
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A267" s="11" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -55433,7 +55430,7 @@
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A270" s="11" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -55457,7 +55454,7 @@
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A273" s="11" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -55481,7 +55478,7 @@
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A276" s="11" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -55505,7 +55502,7 @@
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A279" s="11" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -55529,7 +55526,7 @@
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A282" s="11" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -56111,7 +56108,7 @@
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A351" s="11" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -56239,7 +56236,7 @@
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A367" s="11" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
@@ -57189,7 +57186,7 @@
     </row>
     <row r="482" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A482" s="11" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B482" s="1"/>
       <c r="C482" s="1"/>
@@ -57317,7 +57314,7 @@
     </row>
     <row r="498" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A498" s="11" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B498" s="1"/>
       <c r="C498" s="1"/>
@@ -60426,7 +60423,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B1" s="12" t="s">
         <v>570</v>
@@ -60451,10 +60448,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
@@ -60492,7 +60489,7 @@
     </row>
     <row r="7" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>10</v>
@@ -60503,7 +60500,7 @@
     </row>
     <row r="8" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>11</v>
@@ -60514,7 +60511,7 @@
     </row>
     <row r="9" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>574</v>
@@ -60525,7 +60522,7 @@
     </row>
     <row r="10" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B10" s="8">
         <v>70000</v>
@@ -60536,7 +60533,7 @@
     </row>
     <row r="11" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B11" s="8">
         <v>35000</v>
@@ -60547,7 +60544,7 @@
     </row>
     <row r="12" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B12" s="9">
         <v>46115</v>
@@ -60558,7 +60555,7 @@
     </row>
     <row r="13" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>13</v>
@@ -60569,7 +60566,7 @@
     </row>
     <row r="14" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>14</v>
@@ -60580,7 +60577,7 @@
     </row>
     <row r="15" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>14</v>
@@ -60591,7 +60588,7 @@
     </row>
     <row r="16" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>14</v>
@@ -60646,7 +60643,7 @@
     </row>
     <row r="21" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B21" s="8">
         <v>0</v>
@@ -60657,7 +60654,7 @@
     </row>
     <row r="22" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="11" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B22" s="8">
         <v>0</v>
@@ -60701,7 +60698,7 @@
     </row>
     <row r="26" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="11" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>29</v>
@@ -60712,7 +60709,7 @@
     </row>
     <row r="27" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="11" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>30</v>
@@ -60723,7 +60720,7 @@
     </row>
     <row r="28" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="11" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>31</v>
@@ -60734,7 +60731,7 @@
     </row>
     <row r="29" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="11" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>14</v>
@@ -61077,7 +61074,7 @@
     </row>
     <row r="76" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="11" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -62277,21 +62274,21 @@
     </row>
     <row r="247" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A247" s="11" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B247" s="1"/>
       <c r="C247" s="8"/>
     </row>
     <row r="248" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A248" s="11" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
     </row>
     <row r="249" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A249" s="11" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -62312,7 +62309,7 @@
     </row>
     <row r="252" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A252" s="11" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -62333,7 +62330,7 @@
     </row>
     <row r="255" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A255" s="11" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -62354,7 +62351,7 @@
     </row>
     <row r="258" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A258" s="11" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -62375,7 +62372,7 @@
     </row>
     <row r="261" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A261" s="11" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -62396,7 +62393,7 @@
     </row>
     <row r="264" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A264" s="11" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -62417,7 +62414,7 @@
     </row>
     <row r="267" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A267" s="11" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -62438,7 +62435,7 @@
     </row>
     <row r="270" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A270" s="11" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -62459,7 +62456,7 @@
     </row>
     <row r="273" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A273" s="11" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -62480,7 +62477,7 @@
     </row>
     <row r="276" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A276" s="11" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -62501,7 +62498,7 @@
     </row>
     <row r="279" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A279" s="11" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -62522,7 +62519,7 @@
     </row>
     <row r="282" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A282" s="11" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -63039,7 +63036,7 @@
     </row>
     <row r="351" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A351" s="11" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -63155,7 +63152,7 @@
     </row>
     <row r="367" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A367" s="11" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B367" s="8"/>
       <c r="C367" s="1"/>
@@ -64034,7 +64031,7 @@
     </row>
     <row r="482" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A482" s="11" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B482" s="1"/>
       <c r="C482" s="1"/>
@@ -64166,7 +64163,7 @@
     </row>
     <row r="498" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A498" s="11" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B498" s="1"/>
       <c r="C498" s="1"/>
@@ -66803,7 +66800,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B1" s="12" t="s">
         <v>579</v>
@@ -66828,10 +66825,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -66839,10 +66836,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>581</v>
+        <v>663</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>582</v>
+        <v>663</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -66850,10 +66847,10 @@
         <v>7</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -66869,7 +66866,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>10</v>
@@ -66880,18 +66877,18 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>12</v>
@@ -66902,7 +66899,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>14</v>
@@ -66913,7 +66910,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>14</v>
@@ -66924,7 +66921,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B12" s="8">
         <v>5</v>
@@ -66935,7 +66932,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>13</v>
@@ -66946,18 +66943,18 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>14</v>
@@ -66968,7 +66965,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>14</v>
@@ -67023,7 +67020,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B21" s="8">
         <v>0</v>
@@ -67034,7 +67031,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="11" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B22" s="8">
         <v>0</v>
@@ -67078,18 +67075,18 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="11" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="11" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>14</v>
@@ -67100,7 +67097,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="11" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>14</v>
@@ -67111,7 +67108,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="11" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>14</v>
@@ -67137,7 +67134,7 @@
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="4" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -67145,7 +67142,7 @@
         <v>37</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="C32" s="1"/>
     </row>
@@ -67456,7 +67453,7 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A76" s="11" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -68653,21 +68650,21 @@
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A247" s="11" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A248" s="11" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A249" s="11" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -68688,7 +68685,7 @@
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A252" s="11" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -68709,7 +68706,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="11" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -68730,7 +68727,7 @@
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A258" s="11" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -68751,7 +68748,7 @@
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A261" s="11" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -68772,7 +68769,7 @@
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A264" s="11" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -68793,7 +68790,7 @@
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A267" s="11" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -68814,7 +68811,7 @@
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A270" s="11" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -68835,7 +68832,7 @@
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A273" s="11" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -68856,7 +68853,7 @@
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A276" s="11" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -68877,7 +68874,7 @@
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A279" s="11" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -68898,7 +68895,7 @@
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A282" s="11" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -69381,7 +69378,7 @@
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A351" s="11" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -69493,7 +69490,7 @@
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A367" s="11" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
@@ -70298,7 +70295,7 @@
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A482" s="11" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B482" s="1"/>
       <c r="C482" s="1"/>
@@ -70410,7 +70407,7 @@
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A498" s="11" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B498" s="1"/>
       <c r="C498" s="1"/>

--- a/hspa-test.xlsx
+++ b/hspa-test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jonas.grabbe\tafi_test-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEAE7354-A715-4610-A9DE-2474B683F379}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBA8C2A3-2CF7-446A-8F97-C28952C50C96}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28770" windowHeight="12030" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28770" windowHeight="12030" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Amud" sheetId="1" r:id="rId1"/>
@@ -2385,6 +2385,9 @@
   </sheetPr>
   <dimension ref="A1:D1003"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="34.28515625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -23960,18 +23963,10 @@
       <c r="A212" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="B212" s="1">
-        <v>1</v>
-      </c>
-      <c r="C212" s="1">
-        <v>1</v>
-      </c>
-      <c r="D212" s="1">
-        <v>1</v>
-      </c>
-      <c r="E212" s="1">
-        <v>1</v>
-      </c>
+      <c r="B212" s="1"/>
+      <c r="C212" s="1"/>
+      <c r="D212" s="1"/>
+      <c r="E212" s="1"/>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A213" s="11" t="s">
@@ -41891,7 +41886,7 @@
         <v>1</v>
       </c>
       <c r="H19" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
